--- a/datos_liga.xlsx
+++ b/datos_liga.xlsx
@@ -2958,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>701</v>
+        <v>501</v>
       </c>
       <c r="F19" t="s" s="23">
         <v>40</v>
@@ -3162,7 +3162,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="22">
-        <v>701</v>
+        <v>501</v>
       </c>
       <c r="F22" t="s" s="23">
         <v>40</v>
@@ -3298,7 +3298,7 @@
         <v>1</v>
       </c>
       <c r="E24" s="22">
-        <v>701</v>
+        <v>501</v>
       </c>
       <c r="F24" t="s" s="23">
         <v>41</v>
@@ -3502,7 +3502,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="22">
-        <v>701</v>
+        <v>501</v>
       </c>
       <c r="F27" t="s" s="23">
         <v>41</v>

--- a/datos_liga.xlsx
+++ b/datos_liga.xlsx
@@ -13198,7 +13198,7 @@
         <v>23</v>
       </c>
       <c r="B162" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C162" s="22">
         <v>1</v>
@@ -13266,7 +13266,7 @@
         <v>23</v>
       </c>
       <c r="B163" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C163" s="22">
         <v>1</v>
@@ -13334,7 +13334,7 @@
         <v>23</v>
       </c>
       <c r="B164" s="21">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C164" s="26">
         <v>1</v>
@@ -13402,7 +13402,7 @@
         <v>23</v>
       </c>
       <c r="B165" s="25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C165" s="32">
         <v>1</v>
@@ -13470,7 +13470,7 @@
         <v>23</v>
       </c>
       <c r="B166" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C166" s="32">
         <v>1</v>
@@ -13538,7 +13538,7 @@
         <v>23</v>
       </c>
       <c r="B167" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C167" s="15">
         <v>2</v>
@@ -13606,7 +13606,7 @@
         <v>23</v>
       </c>
       <c r="B168" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C168" s="22">
         <v>2</v>
@@ -13674,7 +13674,7 @@
         <v>23</v>
       </c>
       <c r="B169" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C169" s="22">
         <v>2</v>
@@ -13742,7 +13742,7 @@
         <v>23</v>
       </c>
       <c r="B170" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C170" s="22">
         <v>2</v>
@@ -13810,7 +13810,7 @@
         <v>23</v>
       </c>
       <c r="B171" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C171" s="22">
         <v>3</v>
@@ -13878,7 +13878,7 @@
         <v>23</v>
       </c>
       <c r="B172" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C172" s="22">
         <v>3</v>
@@ -13946,7 +13946,7 @@
         <v>23</v>
       </c>
       <c r="B173" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C173" s="22">
         <v>3</v>
@@ -14014,7 +14014,7 @@
         <v>23</v>
       </c>
       <c r="B174" s="30">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C174" s="22">
         <v>3</v>
@@ -14082,7 +14082,7 @@
         <v>23</v>
       </c>
       <c r="B175" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C175" s="22">
         <v>3</v>

--- a/datos_liga.xlsx
+++ b/datos_liga.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="294">
   <si>
     <t>Tabla 1</t>
   </si>
@@ -740,6 +740,96 @@
     <t>46.73</t>
   </si>
   <si>
+    <t>25.89</t>
+  </si>
+  <si>
+    <t>2.93</t>
+  </si>
+  <si>
+    <t>2.88</t>
+  </si>
+  <si>
+    <t>31.31</t>
+  </si>
+  <si>
+    <t>23.44</t>
+  </si>
+  <si>
+    <t>20.88</t>
+  </si>
+  <si>
+    <t>22.90</t>
+  </si>
+  <si>
+    <t>2.68</t>
+  </si>
+  <si>
+    <t>2.65</t>
+  </si>
+  <si>
+    <t>25.08</t>
+  </si>
+  <si>
+    <t>33.40</t>
+  </si>
+  <si>
+    <t>23.88</t>
+  </si>
+  <si>
+    <t>38.54</t>
+  </si>
+  <si>
+    <t>2.17</t>
+  </si>
+  <si>
+    <t>23.22</t>
+  </si>
+  <si>
+    <t>1.22</t>
+  </si>
+  <si>
+    <t>30.73</t>
+  </si>
+  <si>
+    <t>3.17</t>
+  </si>
+  <si>
+    <t>26.71</t>
+  </si>
+  <si>
+    <t>2.91</t>
+  </si>
+  <si>
+    <t>23.23</t>
+  </si>
+  <si>
+    <t>3.86</t>
+  </si>
+  <si>
+    <t>2.86</t>
+  </si>
+  <si>
+    <t>4.29</t>
+  </si>
+  <si>
+    <t>27.13</t>
+  </si>
+  <si>
+    <t>2.46</t>
+  </si>
+  <si>
+    <t>2.92</t>
+  </si>
+  <si>
+    <t>24.67</t>
+  </si>
+  <si>
+    <t>21.21</t>
+  </si>
+  <si>
+    <t>4.60</t>
+  </si>
+  <si>
     <t>Jornada 1</t>
   </si>
   <si>
@@ -1311,16 +1401,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1355,9 +1448,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
@@ -2420,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:V469"/>
+  <dimension ref="A1:V466"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="10.5" style="1" customWidth="1"/>
@@ -14897,16 +14987,16 @@
       <c r="A187" t="s" s="24">
         <v>23</v>
       </c>
-      <c r="B187" s="21">
+      <c r="B187" s="25">
         <v>3</v>
       </c>
-      <c r="C187" s="22">
-        <v>2</v>
-      </c>
-      <c r="D187" s="22">
+      <c r="C187" s="26">
+        <v>2</v>
+      </c>
+      <c r="D187" s="26">
         <v>3</v>
       </c>
-      <c r="E187" t="s" s="23">
+      <c r="E187" t="s" s="27">
         <v>24</v>
       </c>
       <c r="F187" t="s" s="23">
@@ -14962,21 +15052,41 @@
       </c>
     </row>
     <row r="188" ht="20.05" customHeight="1">
-      <c r="A188" s="33"/>
-      <c r="B188" s="34"/>
-      <c r="C188" s="35"/>
-      <c r="D188" s="35"/>
-      <c r="E188" s="35"/>
-      <c r="F188" s="35"/>
-      <c r="G188" s="35"/>
-      <c r="H188" s="35"/>
-      <c r="I188" s="35"/>
-      <c r="J188" s="35"/>
+      <c r="A188" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B188" s="30">
+        <v>4</v>
+      </c>
+      <c r="C188" s="15">
+        <v>1</v>
+      </c>
+      <c r="D188" s="15">
+        <v>1</v>
+      </c>
+      <c r="E188" s="15">
+        <v>501</v>
+      </c>
+      <c r="F188" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G188" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H188" t="s" s="23">
+        <v>242</v>
+      </c>
+      <c r="I188" t="s" s="23">
+        <v>175</v>
+      </c>
+      <c r="J188" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K188" s="17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L188" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M188" s="18">
         <v>0</v>
@@ -15010,16 +15120,36 @@
       </c>
     </row>
     <row r="189" ht="20.05" customHeight="1">
-      <c r="A189" s="36"/>
-      <c r="B189" s="34"/>
-      <c r="C189" s="35"/>
-      <c r="D189" s="35"/>
-      <c r="E189" s="35"/>
-      <c r="F189" s="35"/>
-      <c r="G189" s="35"/>
-      <c r="H189" s="35"/>
-      <c r="I189" s="35"/>
-      <c r="J189" s="35"/>
+      <c r="A189" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B189" s="30">
+        <v>4</v>
+      </c>
+      <c r="C189" s="22">
+        <v>1</v>
+      </c>
+      <c r="D189" s="22">
+        <v>2</v>
+      </c>
+      <c r="E189" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F189" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G189" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H189" t="s" s="23">
+        <v>243</v>
+      </c>
+      <c r="I189" t="s" s="23">
+        <v>232</v>
+      </c>
+      <c r="J189" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K189" s="17">
         <v>0</v>
       </c>
@@ -15033,7 +15163,7 @@
         <v>0</v>
       </c>
       <c r="O189" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P189" s="18">
         <v>0</v>
@@ -15042,7 +15172,7 @@
         <v>0</v>
       </c>
       <c r="R189" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S189" s="18">
         <v>0</v>
@@ -15058,16 +15188,36 @@
       </c>
     </row>
     <row r="190" ht="20.05" customHeight="1">
-      <c r="A190" s="36"/>
-      <c r="B190" s="34"/>
-      <c r="C190" s="35"/>
-      <c r="D190" s="35"/>
-      <c r="E190" s="35"/>
-      <c r="F190" s="35"/>
-      <c r="G190" s="35"/>
-      <c r="H190" s="35"/>
-      <c r="I190" s="35"/>
-      <c r="J190" s="35"/>
+      <c r="A190" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B190" s="30">
+        <v>4</v>
+      </c>
+      <c r="C190" s="22">
+        <v>1</v>
+      </c>
+      <c r="D190" s="22">
+        <v>3</v>
+      </c>
+      <c r="E190" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F190" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G190" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H190" t="s" s="23">
+        <v>218</v>
+      </c>
+      <c r="I190" t="s" s="23">
+        <v>244</v>
+      </c>
+      <c r="J190" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K190" s="17">
         <v>0</v>
       </c>
@@ -15081,7 +15231,7 @@
         <v>0</v>
       </c>
       <c r="O190" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P190" s="18">
         <v>0</v>
@@ -15106,24 +15256,44 @@
       </c>
     </row>
     <row r="191" ht="20.05" customHeight="1">
-      <c r="A191" s="36"/>
-      <c r="B191" s="34"/>
-      <c r="C191" s="35"/>
-      <c r="D191" s="35"/>
-      <c r="E191" s="35"/>
-      <c r="F191" s="35"/>
-      <c r="G191" s="35"/>
-      <c r="H191" s="35"/>
-      <c r="I191" s="35"/>
-      <c r="J191" s="35"/>
+      <c r="A191" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B191" s="30">
+        <v>4</v>
+      </c>
+      <c r="C191" s="22">
+        <v>1</v>
+      </c>
+      <c r="D191" s="22">
+        <v>4</v>
+      </c>
+      <c r="E191" s="22">
+        <v>501</v>
+      </c>
+      <c r="F191" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G191" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H191" t="s" s="23">
+        <v>245</v>
+      </c>
+      <c r="I191" t="s" s="23">
+        <v>246</v>
+      </c>
+      <c r="J191" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K191" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L191" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M191" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N191" s="18">
         <v>0</v>
@@ -15154,21 +15324,41 @@
       </c>
     </row>
     <row r="192" ht="20.05" customHeight="1">
-      <c r="A192" s="36"/>
-      <c r="B192" s="34"/>
-      <c r="C192" s="35"/>
-      <c r="D192" s="35"/>
-      <c r="E192" s="35"/>
-      <c r="F192" s="35"/>
-      <c r="G192" s="35"/>
-      <c r="H192" s="35"/>
-      <c r="I192" s="35"/>
-      <c r="J192" s="35"/>
+      <c r="A192" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B192" s="30">
+        <v>4</v>
+      </c>
+      <c r="C192" s="22">
+        <v>2</v>
+      </c>
+      <c r="D192" s="22">
+        <v>1</v>
+      </c>
+      <c r="E192" s="22">
+        <v>501</v>
+      </c>
+      <c r="F192" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G192" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H192" t="s" s="23">
+        <v>247</v>
+      </c>
+      <c r="I192" t="s" s="23">
+        <v>248</v>
+      </c>
+      <c r="J192" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K192" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L192" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M192" s="18">
         <v>0</v>
@@ -15202,16 +15392,36 @@
       </c>
     </row>
     <row r="193" ht="20.05" customHeight="1">
-      <c r="A193" s="36"/>
-      <c r="B193" s="34"/>
-      <c r="C193" s="35"/>
-      <c r="D193" s="35"/>
-      <c r="E193" s="35"/>
-      <c r="F193" s="35"/>
-      <c r="G193" s="35"/>
-      <c r="H193" s="35"/>
-      <c r="I193" s="35"/>
-      <c r="J193" s="35"/>
+      <c r="A193" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B193" s="30">
+        <v>4</v>
+      </c>
+      <c r="C193" s="22">
+        <v>2</v>
+      </c>
+      <c r="D193" s="22">
+        <v>2</v>
+      </c>
+      <c r="E193" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F193" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G193" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H193" t="s" s="23">
+        <v>249</v>
+      </c>
+      <c r="I193" t="s" s="23">
+        <v>250</v>
+      </c>
+      <c r="J193" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K193" s="17">
         <v>0</v>
       </c>
@@ -15243,23 +15453,43 @@
         <v>0</v>
       </c>
       <c r="U193" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V193" s="19">
         <v>0</v>
       </c>
     </row>
     <row r="194" ht="20.05" customHeight="1">
-      <c r="A194" s="36"/>
-      <c r="B194" s="34"/>
-      <c r="C194" s="35"/>
-      <c r="D194" s="35"/>
-      <c r="E194" s="35"/>
-      <c r="F194" s="35"/>
-      <c r="G194" s="35"/>
-      <c r="H194" s="35"/>
-      <c r="I194" s="35"/>
-      <c r="J194" s="35"/>
+      <c r="A194" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B194" s="30">
+        <v>4</v>
+      </c>
+      <c r="C194" s="22">
+        <v>2</v>
+      </c>
+      <c r="D194" s="22">
+        <v>3</v>
+      </c>
+      <c r="E194" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F194" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G194" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H194" t="s" s="23">
+        <v>51</v>
+      </c>
+      <c r="I194" t="s" s="23">
+        <v>109</v>
+      </c>
+      <c r="J194" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K194" s="17">
         <v>0</v>
       </c>
@@ -15276,13 +15506,13 @@
         <v>0</v>
       </c>
       <c r="P194" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q194" s="18">
         <v>0</v>
       </c>
       <c r="R194" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S194" s="18">
         <v>0</v>
@@ -15298,21 +15528,41 @@
       </c>
     </row>
     <row r="195" ht="20.05" customHeight="1">
-      <c r="A195" s="36"/>
-      <c r="B195" s="34"/>
-      <c r="C195" s="35"/>
-      <c r="D195" s="35"/>
-      <c r="E195" s="35"/>
-      <c r="F195" s="35"/>
-      <c r="G195" s="35"/>
-      <c r="H195" s="35"/>
-      <c r="I195" s="35"/>
-      <c r="J195" s="35"/>
+      <c r="A195" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B195" s="30">
+        <v>4</v>
+      </c>
+      <c r="C195" s="22">
+        <v>2</v>
+      </c>
+      <c r="D195" s="22">
+        <v>4</v>
+      </c>
+      <c r="E195" s="22">
+        <v>501</v>
+      </c>
+      <c r="F195" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G195" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H195" t="s" s="23">
+        <v>251</v>
+      </c>
+      <c r="I195" t="s" s="23">
+        <v>252</v>
+      </c>
+      <c r="J195" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K195" s="17">
         <v>0</v>
       </c>
       <c r="L195" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M195" s="18">
         <v>0</v>
@@ -15346,24 +15596,44 @@
       </c>
     </row>
     <row r="196" ht="20.05" customHeight="1">
-      <c r="A196" s="36"/>
-      <c r="B196" s="34"/>
-      <c r="C196" s="35"/>
-      <c r="D196" s="35"/>
-      <c r="E196" s="35"/>
-      <c r="F196" s="35"/>
-      <c r="G196" s="35"/>
-      <c r="H196" s="35"/>
-      <c r="I196" s="35"/>
-      <c r="J196" s="35"/>
+      <c r="A196" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B196" s="30">
+        <v>9</v>
+      </c>
+      <c r="C196" s="22">
+        <v>1</v>
+      </c>
+      <c r="D196" s="22">
+        <v>1</v>
+      </c>
+      <c r="E196" s="22">
+        <v>501</v>
+      </c>
+      <c r="F196" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G196" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H196" t="s" s="23">
+        <v>253</v>
+      </c>
+      <c r="I196" t="s" s="23">
+        <v>43</v>
+      </c>
+      <c r="J196" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K196" s="17">
         <v>0</v>
       </c>
       <c r="L196" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M196" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N196" s="18">
         <v>0</v>
@@ -15394,16 +15664,36 @@
       </c>
     </row>
     <row r="197" ht="20.05" customHeight="1">
-      <c r="A197" s="36"/>
-      <c r="B197" s="34"/>
-      <c r="C197" s="35"/>
-      <c r="D197" s="35"/>
-      <c r="E197" s="35"/>
-      <c r="F197" s="35"/>
-      <c r="G197" s="35"/>
-      <c r="H197" s="35"/>
-      <c r="I197" s="35"/>
-      <c r="J197" s="35"/>
+      <c r="A197" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B197" s="30">
+        <v>9</v>
+      </c>
+      <c r="C197" s="22">
+        <v>1</v>
+      </c>
+      <c r="D197" s="22">
+        <v>2</v>
+      </c>
+      <c r="E197" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F197" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G197" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H197" t="s" s="23">
+        <v>218</v>
+      </c>
+      <c r="I197" t="s" s="23">
+        <v>103</v>
+      </c>
+      <c r="J197" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K197" s="17">
         <v>0</v>
       </c>
@@ -15423,10 +15713,10 @@
         <v>0</v>
       </c>
       <c r="Q197" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R197" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S197" s="18">
         <v>0</v>
@@ -15442,16 +15732,36 @@
       </c>
     </row>
     <row r="198" ht="20.05" customHeight="1">
-      <c r="A198" s="36"/>
-      <c r="B198" s="34"/>
-      <c r="C198" s="35"/>
-      <c r="D198" s="35"/>
-      <c r="E198" s="35"/>
-      <c r="F198" s="35"/>
-      <c r="G198" s="35"/>
-      <c r="H198" s="35"/>
-      <c r="I198" s="35"/>
-      <c r="J198" s="35"/>
+      <c r="A198" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B198" s="30">
+        <v>9</v>
+      </c>
+      <c r="C198" s="22">
+        <v>1</v>
+      </c>
+      <c r="D198" s="22">
+        <v>3</v>
+      </c>
+      <c r="E198" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F198" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G198" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H198" t="s" s="23">
+        <v>243</v>
+      </c>
+      <c r="I198" t="s" s="23">
+        <v>66</v>
+      </c>
+      <c r="J198" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K198" s="17">
         <v>0</v>
       </c>
@@ -15465,7 +15775,7 @@
         <v>0</v>
       </c>
       <c r="O198" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P198" s="18">
         <v>0</v>
@@ -15490,27 +15800,47 @@
       </c>
     </row>
     <row r="199" ht="20.05" customHeight="1">
-      <c r="A199" s="36"/>
-      <c r="B199" s="34"/>
-      <c r="C199" s="35"/>
-      <c r="D199" s="35"/>
-      <c r="E199" s="35"/>
-      <c r="F199" s="35"/>
-      <c r="G199" s="35"/>
-      <c r="H199" s="35"/>
-      <c r="I199" s="35"/>
-      <c r="J199" s="35"/>
+      <c r="A199" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B199" s="30">
+        <v>9</v>
+      </c>
+      <c r="C199" s="22">
+        <v>1</v>
+      </c>
+      <c r="D199" s="22">
+        <v>4</v>
+      </c>
+      <c r="E199" s="22">
+        <v>501</v>
+      </c>
+      <c r="F199" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G199" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H199" t="s" s="23">
+        <v>254</v>
+      </c>
+      <c r="I199" t="s" s="23">
+        <v>235</v>
+      </c>
+      <c r="J199" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K199" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L199" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M199" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N199" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O199" s="18">
         <v>0</v>
@@ -15538,16 +15868,36 @@
       </c>
     </row>
     <row r="200" ht="20.05" customHeight="1">
-      <c r="A200" s="36"/>
-      <c r="B200" s="34"/>
-      <c r="C200" s="35"/>
-      <c r="D200" s="35"/>
-      <c r="E200" s="35"/>
-      <c r="F200" s="35"/>
-      <c r="G200" s="35"/>
-      <c r="H200" s="35"/>
-      <c r="I200" s="35"/>
-      <c r="J200" s="35"/>
+      <c r="A200" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B200" s="30">
+        <v>9</v>
+      </c>
+      <c r="C200" s="26">
+        <v>1</v>
+      </c>
+      <c r="D200" s="26">
+        <v>5</v>
+      </c>
+      <c r="E200" t="s" s="27">
+        <v>24</v>
+      </c>
+      <c r="F200" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="G200" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="H200" t="s" s="23">
+        <v>255</v>
+      </c>
+      <c r="I200" t="s" s="23">
+        <v>109</v>
+      </c>
+      <c r="J200" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K200" s="17">
         <v>0</v>
       </c>
@@ -15564,7 +15914,7 @@
         <v>0</v>
       </c>
       <c r="P200" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q200" s="18">
         <v>0</v>
@@ -15586,21 +15936,41 @@
       </c>
     </row>
     <row r="201" ht="20.05" customHeight="1">
-      <c r="A201" s="36"/>
-      <c r="B201" s="34"/>
-      <c r="C201" s="35"/>
-      <c r="D201" s="35"/>
-      <c r="E201" s="35"/>
-      <c r="F201" s="35"/>
-      <c r="G201" s="35"/>
-      <c r="H201" s="35"/>
-      <c r="I201" s="35"/>
-      <c r="J201" s="35"/>
+      <c r="A201" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B201" s="30">
+        <v>9</v>
+      </c>
+      <c r="C201" s="15">
+        <v>2</v>
+      </c>
+      <c r="D201" s="15">
+        <v>1</v>
+      </c>
+      <c r="E201" s="15">
+        <v>501</v>
+      </c>
+      <c r="F201" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G201" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H201" t="s" s="23">
+        <v>256</v>
+      </c>
+      <c r="I201" t="s" s="23">
+        <v>175</v>
+      </c>
+      <c r="J201" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K201" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L201" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M201" s="18">
         <v>0</v>
@@ -15634,16 +16004,36 @@
       </c>
     </row>
     <row r="202" ht="20.05" customHeight="1">
-      <c r="A202" s="36"/>
-      <c r="B202" s="34"/>
-      <c r="C202" s="35"/>
-      <c r="D202" s="35"/>
-      <c r="E202" s="35"/>
-      <c r="F202" s="35"/>
-      <c r="G202" s="35"/>
-      <c r="H202" s="35"/>
-      <c r="I202" s="35"/>
-      <c r="J202" s="35"/>
+      <c r="A202" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B202" s="30">
+        <v>9</v>
+      </c>
+      <c r="C202" s="22">
+        <v>2</v>
+      </c>
+      <c r="D202" s="22">
+        <v>2</v>
+      </c>
+      <c r="E202" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F202" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G202" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H202" t="s" s="23">
+        <v>103</v>
+      </c>
+      <c r="I202" t="s" s="23">
+        <v>257</v>
+      </c>
+      <c r="J202" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K202" s="17">
         <v>0</v>
       </c>
@@ -15682,16 +16072,36 @@
       </c>
     </row>
     <row r="203" ht="20.05" customHeight="1">
-      <c r="A203" s="36"/>
-      <c r="B203" s="34"/>
-      <c r="C203" s="35"/>
-      <c r="D203" s="35"/>
-      <c r="E203" s="35"/>
-      <c r="F203" s="35"/>
-      <c r="G203" s="35"/>
-      <c r="H203" s="35"/>
-      <c r="I203" s="35"/>
-      <c r="J203" s="35"/>
+      <c r="A203" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B203" s="30">
+        <v>9</v>
+      </c>
+      <c r="C203" s="22">
+        <v>2</v>
+      </c>
+      <c r="D203" s="22">
+        <v>3</v>
+      </c>
+      <c r="E203" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F203" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G203" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H203" t="s" s="23">
+        <v>29</v>
+      </c>
+      <c r="I203" t="s" s="23">
+        <v>51</v>
+      </c>
+      <c r="J203" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K203" s="17">
         <v>0</v>
       </c>
@@ -15705,7 +16115,7 @@
         <v>0</v>
       </c>
       <c r="O203" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P203" s="18">
         <v>0</v>
@@ -15730,27 +16140,47 @@
       </c>
     </row>
     <row r="204" ht="20.05" customHeight="1">
-      <c r="A204" s="36"/>
-      <c r="B204" s="34"/>
-      <c r="C204" s="35"/>
-      <c r="D204" s="35"/>
-      <c r="E204" s="35"/>
-      <c r="F204" s="35"/>
-      <c r="G204" s="35"/>
-      <c r="H204" s="35"/>
-      <c r="I204" s="35"/>
-      <c r="J204" s="35"/>
+      <c r="A204" t="s" s="29">
+        <v>39</v>
+      </c>
+      <c r="B204" s="30">
+        <v>9</v>
+      </c>
+      <c r="C204" s="22">
+        <v>2</v>
+      </c>
+      <c r="D204" s="22">
+        <v>4</v>
+      </c>
+      <c r="E204" s="22">
+        <v>501</v>
+      </c>
+      <c r="F204" t="s" s="23">
+        <v>158</v>
+      </c>
+      <c r="G204" t="s" s="23">
+        <v>41</v>
+      </c>
+      <c r="H204" t="s" s="23">
+        <v>258</v>
+      </c>
+      <c r="I204" t="s" s="23">
+        <v>52</v>
+      </c>
+      <c r="J204" t="s" s="23">
+        <v>41</v>
+      </c>
       <c r="K204" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L204" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M204" s="18">
         <v>0</v>
       </c>
       <c r="N204" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O204" s="18">
         <v>0</v>
@@ -15778,16 +16208,36 @@
       </c>
     </row>
     <row r="205" ht="20.05" customHeight="1">
-      <c r="A205" s="36"/>
-      <c r="B205" s="34"/>
-      <c r="C205" s="35"/>
-      <c r="D205" s="35"/>
-      <c r="E205" s="35"/>
-      <c r="F205" s="35"/>
-      <c r="G205" s="35"/>
-      <c r="H205" s="35"/>
-      <c r="I205" s="35"/>
-      <c r="J205" s="35"/>
+      <c r="A205" t="s" s="13">
+        <v>39</v>
+      </c>
+      <c r="B205" s="30">
+        <v>9</v>
+      </c>
+      <c r="C205" s="26">
+        <v>2</v>
+      </c>
+      <c r="D205" s="26">
+        <v>5</v>
+      </c>
+      <c r="E205" t="s" s="27">
+        <v>24</v>
+      </c>
+      <c r="F205" t="s" s="27">
+        <v>158</v>
+      </c>
+      <c r="G205" t="s" s="27">
+        <v>41</v>
+      </c>
+      <c r="H205" t="s" s="23">
+        <v>259</v>
+      </c>
+      <c r="I205" t="s" s="23">
+        <v>56</v>
+      </c>
+      <c r="J205" t="s" s="23">
+        <v>158</v>
+      </c>
       <c r="K205" s="17">
         <v>0</v>
       </c>
@@ -15795,7 +16245,7 @@
         <v>0</v>
       </c>
       <c r="M205" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N205" s="18">
         <v>0</v>
@@ -15804,10 +16254,10 @@
         <v>0</v>
       </c>
       <c r="P205" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q205" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R205" s="18">
         <v>0</v>
@@ -15826,24 +16276,44 @@
       </c>
     </row>
     <row r="206" ht="20.05" customHeight="1">
-      <c r="A206" s="36"/>
-      <c r="B206" s="34"/>
-      <c r="C206" s="35"/>
-      <c r="D206" s="35"/>
-      <c r="E206" s="35"/>
-      <c r="F206" s="35"/>
-      <c r="G206" s="35"/>
-      <c r="H206" s="35"/>
-      <c r="I206" s="35"/>
-      <c r="J206" s="35"/>
+      <c r="A206" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B206" s="30">
+        <v>6</v>
+      </c>
+      <c r="C206" s="15">
+        <v>1</v>
+      </c>
+      <c r="D206" s="15">
+        <v>1</v>
+      </c>
+      <c r="E206" s="15">
+        <v>701</v>
+      </c>
+      <c r="F206" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="H206" t="s" s="23">
+        <v>260</v>
+      </c>
+      <c r="I206" t="s" s="23">
+        <v>27</v>
+      </c>
+      <c r="J206" t="s" s="23">
+        <v>25</v>
+      </c>
       <c r="K206" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L206" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M206" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N206" s="18">
         <v>0</v>
@@ -15874,16 +16344,36 @@
       </c>
     </row>
     <row r="207" ht="20.05" customHeight="1">
-      <c r="A207" s="36"/>
-      <c r="B207" s="34"/>
-      <c r="C207" s="35"/>
-      <c r="D207" s="35"/>
-      <c r="E207" s="35"/>
-      <c r="F207" s="35"/>
-      <c r="G207" s="35"/>
-      <c r="H207" s="35"/>
-      <c r="I207" s="35"/>
-      <c r="J207" s="35"/>
+      <c r="A207" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B207" s="30">
+        <v>6</v>
+      </c>
+      <c r="C207" s="22">
+        <v>1</v>
+      </c>
+      <c r="D207" s="22">
+        <v>2</v>
+      </c>
+      <c r="E207" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F207" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="H207" t="s" s="23">
+        <v>261</v>
+      </c>
+      <c r="I207" t="s" s="23">
+        <v>66</v>
+      </c>
+      <c r="J207" t="s" s="27">
+        <v>26</v>
+      </c>
       <c r="K207" s="17">
         <v>0</v>
       </c>
@@ -15891,7 +16381,7 @@
         <v>0</v>
       </c>
       <c r="M207" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N207" s="18">
         <v>0</v>
@@ -15903,7 +16393,7 @@
         <v>0</v>
       </c>
       <c r="Q207" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R207" s="18">
         <v>0</v>
@@ -15922,16 +16412,36 @@
       </c>
     </row>
     <row r="208" ht="20.05" customHeight="1">
-      <c r="A208" s="36"/>
-      <c r="B208" s="34"/>
-      <c r="C208" s="35"/>
-      <c r="D208" s="35"/>
-      <c r="E208" s="35"/>
-      <c r="F208" s="35"/>
-      <c r="G208" s="35"/>
-      <c r="H208" s="35"/>
-      <c r="I208" s="35"/>
-      <c r="J208" s="35"/>
+      <c r="A208" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B208" s="30">
+        <v>6</v>
+      </c>
+      <c r="C208" s="22">
+        <v>1</v>
+      </c>
+      <c r="D208" s="22">
+        <v>3</v>
+      </c>
+      <c r="E208" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F208" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="H208" t="s" s="23">
+        <v>238</v>
+      </c>
+      <c r="I208" t="s" s="23">
+        <v>35</v>
+      </c>
+      <c r="J208" t="s" s="28">
+        <v>26</v>
+      </c>
       <c r="K208" s="17">
         <v>0</v>
       </c>
@@ -15970,27 +16480,47 @@
       </c>
     </row>
     <row r="209" ht="20.05" customHeight="1">
-      <c r="A209" s="36"/>
-      <c r="B209" s="34"/>
-      <c r="C209" s="35"/>
-      <c r="D209" s="35"/>
-      <c r="E209" s="35"/>
-      <c r="F209" s="35"/>
-      <c r="G209" s="35"/>
-      <c r="H209" s="35"/>
-      <c r="I209" s="35"/>
-      <c r="J209" s="35"/>
+      <c r="A209" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B209" s="30">
+        <v>6</v>
+      </c>
+      <c r="C209" s="22">
+        <v>1</v>
+      </c>
+      <c r="D209" s="22">
+        <v>4</v>
+      </c>
+      <c r="E209" s="26">
+        <v>701</v>
+      </c>
+      <c r="F209" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="G209" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="H209" t="s" s="23">
+        <v>89</v>
+      </c>
+      <c r="I209" t="s" s="23">
+        <v>144</v>
+      </c>
+      <c r="J209" t="s" s="28">
+        <v>26</v>
+      </c>
       <c r="K209" s="17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L209" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M209" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N209" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O209" s="18">
         <v>0</v>
@@ -16018,27 +16548,47 @@
       </c>
     </row>
     <row r="210" ht="20.05" customHeight="1">
-      <c r="A210" s="36"/>
-      <c r="B210" s="34"/>
-      <c r="C210" s="35"/>
-      <c r="D210" s="35"/>
-      <c r="E210" s="35"/>
-      <c r="F210" s="35"/>
-      <c r="G210" s="35"/>
-      <c r="H210" s="35"/>
-      <c r="I210" s="35"/>
-      <c r="J210" s="35"/>
+      <c r="A210" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B210" s="30">
+        <v>6</v>
+      </c>
+      <c r="C210" s="22">
+        <v>2</v>
+      </c>
+      <c r="D210" s="22">
+        <v>1</v>
+      </c>
+      <c r="E210" s="15">
+        <v>701</v>
+      </c>
+      <c r="F210" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="G210" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="H210" t="s" s="23">
+        <v>262</v>
+      </c>
+      <c r="I210" t="s" s="23">
+        <v>122</v>
+      </c>
+      <c r="J210" t="s" s="28">
+        <v>26</v>
+      </c>
       <c r="K210" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L210" s="18">
         <v>0</v>
       </c>
       <c r="M210" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N210" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O210" s="18">
         <v>0</v>
@@ -16066,16 +16616,36 @@
       </c>
     </row>
     <row r="211" ht="20.05" customHeight="1">
-      <c r="A211" s="36"/>
-      <c r="B211" s="34"/>
-      <c r="C211" s="35"/>
-      <c r="D211" s="35"/>
-      <c r="E211" s="35"/>
-      <c r="F211" s="35"/>
-      <c r="G211" s="35"/>
-      <c r="H211" s="35"/>
-      <c r="I211" s="35"/>
-      <c r="J211" s="35"/>
+      <c r="A211" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B211" s="30">
+        <v>6</v>
+      </c>
+      <c r="C211" s="22">
+        <v>2</v>
+      </c>
+      <c r="D211" s="22">
+        <v>2</v>
+      </c>
+      <c r="E211" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F211" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="G211" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="H211" t="s" s="23">
+        <v>92</v>
+      </c>
+      <c r="I211" t="s" s="23">
+        <v>263</v>
+      </c>
+      <c r="J211" t="s" s="28">
+        <v>26</v>
+      </c>
       <c r="K211" s="17">
         <v>0</v>
       </c>
@@ -16095,10 +16665,10 @@
         <v>0</v>
       </c>
       <c r="Q211" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R211" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S211" s="18">
         <v>0</v>
@@ -16114,16 +16684,36 @@
       </c>
     </row>
     <row r="212" ht="20.05" customHeight="1">
-      <c r="A212" s="36"/>
-      <c r="B212" s="34"/>
-      <c r="C212" s="35"/>
-      <c r="D212" s="35"/>
-      <c r="E212" s="35"/>
-      <c r="F212" s="35"/>
-      <c r="G212" s="35"/>
-      <c r="H212" s="35"/>
-      <c r="I212" s="35"/>
-      <c r="J212" s="35"/>
+      <c r="A212" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B212" s="30">
+        <v>6</v>
+      </c>
+      <c r="C212" s="26">
+        <v>2</v>
+      </c>
+      <c r="D212" s="26">
+        <v>3</v>
+      </c>
+      <c r="E212" t="s" s="27">
+        <v>24</v>
+      </c>
+      <c r="F212" t="s" s="28">
+        <v>25</v>
+      </c>
+      <c r="G212" t="s" s="28">
+        <v>26</v>
+      </c>
+      <c r="H212" t="s" s="23">
+        <v>264</v>
+      </c>
+      <c r="I212" t="s" s="23">
+        <v>265</v>
+      </c>
+      <c r="J212" t="s" s="28">
+        <v>26</v>
+      </c>
       <c r="K212" s="17">
         <v>0</v>
       </c>
@@ -16143,10 +16733,10 @@
         <v>0</v>
       </c>
       <c r="Q212" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R212" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S212" s="18">
         <v>0</v>
@@ -16162,24 +16752,44 @@
       </c>
     </row>
     <row r="213" ht="20.05" customHeight="1">
-      <c r="A213" s="36"/>
-      <c r="B213" s="34"/>
-      <c r="C213" s="35"/>
-      <c r="D213" s="35"/>
-      <c r="E213" s="35"/>
-      <c r="F213" s="35"/>
-      <c r="G213" s="35"/>
-      <c r="H213" s="35"/>
-      <c r="I213" s="35"/>
-      <c r="J213" s="35"/>
+      <c r="A213" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B213" s="30">
+        <v>6</v>
+      </c>
+      <c r="C213" s="15">
+        <v>1</v>
+      </c>
+      <c r="D213" s="15">
+        <v>1</v>
+      </c>
+      <c r="E213" s="15">
+        <v>701</v>
+      </c>
+      <c r="F213" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="G213" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="H213" t="s" s="23">
+        <v>121</v>
+      </c>
+      <c r="I213" t="s" s="23">
+        <v>266</v>
+      </c>
+      <c r="J213" t="s" s="16">
+        <v>76</v>
+      </c>
       <c r="K213" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L213" s="18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M213" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N213" s="18">
         <v>0</v>
@@ -16210,16 +16820,36 @@
       </c>
     </row>
     <row r="214" ht="20.05" customHeight="1">
-      <c r="A214" s="36"/>
-      <c r="B214" s="34"/>
-      <c r="C214" s="35"/>
-      <c r="D214" s="35"/>
-      <c r="E214" s="35"/>
-      <c r="F214" s="35"/>
-      <c r="G214" s="35"/>
-      <c r="H214" s="35"/>
-      <c r="I214" s="35"/>
-      <c r="J214" s="35"/>
+      <c r="A214" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B214" s="30">
+        <v>6</v>
+      </c>
+      <c r="C214" s="22">
+        <v>1</v>
+      </c>
+      <c r="D214" s="22">
+        <v>2</v>
+      </c>
+      <c r="E214" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F214" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="G214" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="H214" t="s" s="23">
+        <v>92</v>
+      </c>
+      <c r="I214" t="s" s="23">
+        <v>38</v>
+      </c>
+      <c r="J214" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K214" s="17">
         <v>0</v>
       </c>
@@ -16233,16 +16863,16 @@
         <v>0</v>
       </c>
       <c r="O214" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P214" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q214" s="18">
         <v>0</v>
       </c>
       <c r="R214" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S214" s="18">
         <v>0</v>
@@ -16258,16 +16888,36 @@
       </c>
     </row>
     <row r="215" ht="20.05" customHeight="1">
-      <c r="A215" s="36"/>
-      <c r="B215" s="34"/>
-      <c r="C215" s="35"/>
-      <c r="D215" s="35"/>
-      <c r="E215" s="35"/>
-      <c r="F215" s="35"/>
-      <c r="G215" s="35"/>
-      <c r="H215" s="35"/>
-      <c r="I215" s="35"/>
-      <c r="J215" s="35"/>
+      <c r="A215" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B215" s="30">
+        <v>6</v>
+      </c>
+      <c r="C215" s="22">
+        <v>1</v>
+      </c>
+      <c r="D215" s="22">
+        <v>3</v>
+      </c>
+      <c r="E215" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F215" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="G215" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="H215" t="s" s="23">
+        <v>267</v>
+      </c>
+      <c r="I215" t="s" s="23">
+        <v>268</v>
+      </c>
+      <c r="J215" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K215" s="17">
         <v>0</v>
       </c>
@@ -16290,7 +16940,7 @@
         <v>0</v>
       </c>
       <c r="R215" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S215" s="18">
         <v>0</v>
@@ -16306,21 +16956,41 @@
       </c>
     </row>
     <row r="216" ht="20.05" customHeight="1">
-      <c r="A216" s="36"/>
-      <c r="B216" s="34"/>
-      <c r="C216" s="35"/>
-      <c r="D216" s="35"/>
-      <c r="E216" s="35"/>
-      <c r="F216" s="35"/>
-      <c r="G216" s="35"/>
-      <c r="H216" s="35"/>
-      <c r="I216" s="35"/>
-      <c r="J216" s="35"/>
+      <c r="A216" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B216" s="30">
+        <v>6</v>
+      </c>
+      <c r="C216" s="22">
+        <v>1</v>
+      </c>
+      <c r="D216" s="22">
+        <v>4</v>
+      </c>
+      <c r="E216" s="26">
+        <v>701</v>
+      </c>
+      <c r="F216" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="G216" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="H216" t="s" s="23">
+        <v>269</v>
+      </c>
+      <c r="I216" t="s" s="23">
+        <v>28</v>
+      </c>
+      <c r="J216" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K216" s="17">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L216" s="18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M216" s="18">
         <v>0</v>
@@ -16354,24 +17024,44 @@
       </c>
     </row>
     <row r="217" ht="20.05" customHeight="1">
-      <c r="A217" s="36"/>
-      <c r="B217" s="34"/>
-      <c r="C217" s="35"/>
-      <c r="D217" s="35"/>
-      <c r="E217" s="35"/>
-      <c r="F217" s="35"/>
-      <c r="G217" s="35"/>
-      <c r="H217" s="35"/>
-      <c r="I217" s="35"/>
-      <c r="J217" s="35"/>
+      <c r="A217" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B217" s="30">
+        <v>6</v>
+      </c>
+      <c r="C217" s="22">
+        <v>2</v>
+      </c>
+      <c r="D217" s="22">
+        <v>1</v>
+      </c>
+      <c r="E217" s="15">
+        <v>701</v>
+      </c>
+      <c r="F217" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="G217" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="H217" t="s" s="23">
+        <v>126</v>
+      </c>
+      <c r="I217" t="s" s="23">
+        <v>270</v>
+      </c>
+      <c r="J217" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K217" s="17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L217" s="18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M217" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N217" s="18">
         <v>0</v>
@@ -16402,16 +17092,36 @@
       </c>
     </row>
     <row r="218" ht="20.05" customHeight="1">
-      <c r="A218" s="36"/>
-      <c r="B218" s="34"/>
-      <c r="C218" s="35"/>
-      <c r="D218" s="35"/>
-      <c r="E218" s="35"/>
-      <c r="F218" s="35"/>
-      <c r="G218" s="35"/>
-      <c r="H218" s="35"/>
-      <c r="I218" s="35"/>
-      <c r="J218" s="35"/>
+      <c r="A218" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B218" s="30">
+        <v>6</v>
+      </c>
+      <c r="C218" s="22">
+        <v>2</v>
+      </c>
+      <c r="D218" s="22">
+        <v>2</v>
+      </c>
+      <c r="E218" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F218" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="G218" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s" s="23">
+        <v>29</v>
+      </c>
+      <c r="I218" t="s" s="23">
+        <v>56</v>
+      </c>
+      <c r="J218" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K218" s="17">
         <v>0</v>
       </c>
@@ -16425,13 +17135,13 @@
         <v>0</v>
       </c>
       <c r="O218" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P218" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q218" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R218" s="18">
         <v>0</v>
@@ -16450,16 +17160,36 @@
       </c>
     </row>
     <row r="219" ht="20.05" customHeight="1">
-      <c r="A219" s="36"/>
-      <c r="B219" s="34"/>
-      <c r="C219" s="35"/>
-      <c r="D219" s="35"/>
-      <c r="E219" s="35"/>
-      <c r="F219" s="35"/>
-      <c r="G219" s="35"/>
-      <c r="H219" s="35"/>
-      <c r="I219" s="35"/>
-      <c r="J219" s="35"/>
+      <c r="A219" t="s" s="20">
+        <v>23</v>
+      </c>
+      <c r="B219" s="30">
+        <v>6</v>
+      </c>
+      <c r="C219" s="22">
+        <v>2</v>
+      </c>
+      <c r="D219" s="22">
+        <v>3</v>
+      </c>
+      <c r="E219" t="s" s="23">
+        <v>24</v>
+      </c>
+      <c r="F219" t="s" s="28">
+        <v>75</v>
+      </c>
+      <c r="G219" t="s" s="28">
+        <v>76</v>
+      </c>
+      <c r="H219" t="s" s="23">
+        <v>271</v>
+      </c>
+      <c r="I219" t="s" s="23">
+        <v>56</v>
+      </c>
+      <c r="J219" t="s" s="23">
+        <v>75</v>
+      </c>
       <c r="K219" s="17">
         <v>0</v>
       </c>
@@ -16473,13 +17203,13 @@
         <v>0</v>
       </c>
       <c r="O219" s="18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P219" s="18">
         <v>0</v>
       </c>
       <c r="Q219" s="18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R219" s="18">
         <v>0</v>
@@ -16498,13 +17228,13 @@
       </c>
     </row>
     <row r="220" ht="20.05" customHeight="1">
-      <c r="A220" s="36"/>
+      <c r="A220" s="33"/>
       <c r="B220" s="34"/>
       <c r="C220" s="35"/>
       <c r="D220" s="35"/>
       <c r="E220" s="35"/>
-      <c r="F220" s="35"/>
-      <c r="G220" s="35"/>
+      <c r="F220" s="36"/>
+      <c r="G220" s="36"/>
       <c r="H220" s="35"/>
       <c r="I220" s="35"/>
       <c r="J220" s="35"/>
@@ -16546,8 +17276,8 @@
       </c>
     </row>
     <row r="221" ht="20.05" customHeight="1">
-      <c r="A221" s="36"/>
-      <c r="B221" s="34"/>
+      <c r="A221" s="33"/>
+      <c r="B221" s="37"/>
       <c r="C221" s="35"/>
       <c r="D221" s="35"/>
       <c r="E221" s="35"/>
@@ -16594,8 +17324,8 @@
       </c>
     </row>
     <row r="222" ht="20.05" customHeight="1">
-      <c r="A222" s="36"/>
-      <c r="B222" s="34"/>
+      <c r="A222" s="33"/>
+      <c r="B222" s="37"/>
       <c r="C222" s="35"/>
       <c r="D222" s="35"/>
       <c r="E222" s="35"/>
@@ -16642,8 +17372,8 @@
       </c>
     </row>
     <row r="223" ht="20.05" customHeight="1">
-      <c r="A223" s="36"/>
-      <c r="B223" s="34"/>
+      <c r="A223" s="33"/>
+      <c r="B223" s="37"/>
       <c r="C223" s="35"/>
       <c r="D223" s="35"/>
       <c r="E223" s="35"/>
@@ -16690,8 +17420,8 @@
       </c>
     </row>
     <row r="224" ht="20.05" customHeight="1">
-      <c r="A224" s="36"/>
-      <c r="B224" s="34"/>
+      <c r="A224" s="33"/>
+      <c r="B224" s="37"/>
       <c r="C224" s="35"/>
       <c r="D224" s="35"/>
       <c r="E224" s="35"/>
@@ -16738,8 +17468,8 @@
       </c>
     </row>
     <row r="225" ht="20.05" customHeight="1">
-      <c r="A225" s="36"/>
-      <c r="B225" s="34"/>
+      <c r="A225" s="33"/>
+      <c r="B225" s="37"/>
       <c r="C225" s="35"/>
       <c r="D225" s="35"/>
       <c r="E225" s="35"/>
@@ -16786,8 +17516,8 @@
       </c>
     </row>
     <row r="226" ht="20.05" customHeight="1">
-      <c r="A226" s="36"/>
-      <c r="B226" s="34"/>
+      <c r="A226" s="33"/>
+      <c r="B226" s="37"/>
       <c r="C226" s="35"/>
       <c r="D226" s="35"/>
       <c r="E226" s="35"/>
@@ -16834,8 +17564,8 @@
       </c>
     </row>
     <row r="227" ht="20.05" customHeight="1">
-      <c r="A227" s="36"/>
-      <c r="B227" s="34"/>
+      <c r="A227" s="33"/>
+      <c r="B227" s="37"/>
       <c r="C227" s="35"/>
       <c r="D227" s="35"/>
       <c r="E227" s="35"/>
@@ -16882,8 +17612,8 @@
       </c>
     </row>
     <row r="228" ht="20.05" customHeight="1">
-      <c r="A228" s="36"/>
-      <c r="B228" s="34"/>
+      <c r="A228" s="33"/>
+      <c r="B228" s="37"/>
       <c r="C228" s="35"/>
       <c r="D228" s="35"/>
       <c r="E228" s="35"/>
@@ -16930,8 +17660,8 @@
       </c>
     </row>
     <row r="229" ht="20.05" customHeight="1">
-      <c r="A229" s="36"/>
-      <c r="B229" s="34"/>
+      <c r="A229" s="33"/>
+      <c r="B229" s="37"/>
       <c r="C229" s="35"/>
       <c r="D229" s="35"/>
       <c r="E229" s="35"/>
@@ -16978,8 +17708,8 @@
       </c>
     </row>
     <row r="230" ht="20.05" customHeight="1">
-      <c r="A230" s="36"/>
-      <c r="B230" s="34"/>
+      <c r="A230" s="33"/>
+      <c r="B230" s="37"/>
       <c r="C230" s="35"/>
       <c r="D230" s="35"/>
       <c r="E230" s="35"/>
@@ -17026,8 +17756,8 @@
       </c>
     </row>
     <row r="231" ht="20.05" customHeight="1">
-      <c r="A231" s="36"/>
-      <c r="B231" s="34"/>
+      <c r="A231" s="33"/>
+      <c r="B231" s="37"/>
       <c r="C231" s="35"/>
       <c r="D231" s="35"/>
       <c r="E231" s="35"/>
@@ -17074,8 +17804,8 @@
       </c>
     </row>
     <row r="232" ht="20.05" customHeight="1">
-      <c r="A232" s="36"/>
-      <c r="B232" s="34"/>
+      <c r="A232" s="33"/>
+      <c r="B232" s="37"/>
       <c r="C232" s="35"/>
       <c r="D232" s="35"/>
       <c r="E232" s="35"/>
@@ -17122,8 +17852,8 @@
       </c>
     </row>
     <row r="233" ht="20.05" customHeight="1">
-      <c r="A233" s="36"/>
-      <c r="B233" s="34"/>
+      <c r="A233" s="33"/>
+      <c r="B233" s="37"/>
       <c r="C233" s="35"/>
       <c r="D233" s="35"/>
       <c r="E233" s="35"/>
@@ -17170,8 +17900,8 @@
       </c>
     </row>
     <row r="234" ht="20.05" customHeight="1">
-      <c r="A234" s="36"/>
-      <c r="B234" s="34"/>
+      <c r="A234" s="33"/>
+      <c r="B234" s="37"/>
       <c r="C234" s="35"/>
       <c r="D234" s="35"/>
       <c r="E234" s="35"/>
@@ -17218,8 +17948,8 @@
       </c>
     </row>
     <row r="235" ht="20.05" customHeight="1">
-      <c r="A235" s="36"/>
-      <c r="B235" s="34"/>
+      <c r="A235" s="33"/>
+      <c r="B235" s="37"/>
       <c r="C235" s="35"/>
       <c r="D235" s="35"/>
       <c r="E235" s="35"/>
@@ -17266,8 +17996,8 @@
       </c>
     </row>
     <row r="236" ht="20.05" customHeight="1">
-      <c r="A236" s="36"/>
-      <c r="B236" s="34"/>
+      <c r="A236" s="33"/>
+      <c r="B236" s="37"/>
       <c r="C236" s="35"/>
       <c r="D236" s="35"/>
       <c r="E236" s="35"/>
@@ -17314,8 +18044,8 @@
       </c>
     </row>
     <row r="237" ht="20.05" customHeight="1">
-      <c r="A237" s="36"/>
-      <c r="B237" s="34"/>
+      <c r="A237" s="33"/>
+      <c r="B237" s="37"/>
       <c r="C237" s="35"/>
       <c r="D237" s="35"/>
       <c r="E237" s="35"/>
@@ -17362,8 +18092,8 @@
       </c>
     </row>
     <row r="238" ht="20.05" customHeight="1">
-      <c r="A238" s="36"/>
-      <c r="B238" s="34"/>
+      <c r="A238" s="33"/>
+      <c r="B238" s="37"/>
       <c r="C238" s="35"/>
       <c r="D238" s="35"/>
       <c r="E238" s="35"/>
@@ -17410,8 +18140,8 @@
       </c>
     </row>
     <row r="239" ht="20.05" customHeight="1">
-      <c r="A239" s="36"/>
-      <c r="B239" s="34"/>
+      <c r="A239" s="33"/>
+      <c r="B239" s="37"/>
       <c r="C239" s="35"/>
       <c r="D239" s="35"/>
       <c r="E239" s="35"/>
@@ -17458,8 +18188,8 @@
       </c>
     </row>
     <row r="240" ht="20.05" customHeight="1">
-      <c r="A240" s="36"/>
-      <c r="B240" s="34"/>
+      <c r="A240" s="33"/>
+      <c r="B240" s="37"/>
       <c r="C240" s="35"/>
       <c r="D240" s="35"/>
       <c r="E240" s="35"/>
@@ -17506,8 +18236,8 @@
       </c>
     </row>
     <row r="241" ht="20.05" customHeight="1">
-      <c r="A241" s="36"/>
-      <c r="B241" s="34"/>
+      <c r="A241" s="33"/>
+      <c r="B241" s="37"/>
       <c r="C241" s="35"/>
       <c r="D241" s="35"/>
       <c r="E241" s="35"/>
@@ -17554,8 +18284,8 @@
       </c>
     </row>
     <row r="242" ht="20.05" customHeight="1">
-      <c r="A242" s="36"/>
-      <c r="B242" s="34"/>
+      <c r="A242" s="33"/>
+      <c r="B242" s="37"/>
       <c r="C242" s="35"/>
       <c r="D242" s="35"/>
       <c r="E242" s="35"/>
@@ -17602,8 +18332,8 @@
       </c>
     </row>
     <row r="243" ht="20.05" customHeight="1">
-      <c r="A243" s="36"/>
-      <c r="B243" s="34"/>
+      <c r="A243" s="33"/>
+      <c r="B243" s="37"/>
       <c r="C243" s="35"/>
       <c r="D243" s="35"/>
       <c r="E243" s="35"/>
@@ -17650,8 +18380,8 @@
       </c>
     </row>
     <row r="244" ht="20.05" customHeight="1">
-      <c r="A244" s="36"/>
-      <c r="B244" s="34"/>
+      <c r="A244" s="33"/>
+      <c r="B244" s="37"/>
       <c r="C244" s="35"/>
       <c r="D244" s="35"/>
       <c r="E244" s="35"/>
@@ -17698,8 +18428,8 @@
       </c>
     </row>
     <row r="245" ht="20.05" customHeight="1">
-      <c r="A245" s="36"/>
-      <c r="B245" s="34"/>
+      <c r="A245" s="33"/>
+      <c r="B245" s="37"/>
       <c r="C245" s="35"/>
       <c r="D245" s="35"/>
       <c r="E245" s="35"/>
@@ -17746,8 +18476,8 @@
       </c>
     </row>
     <row r="246" ht="20.05" customHeight="1">
-      <c r="A246" s="36"/>
-      <c r="B246" s="34"/>
+      <c r="A246" s="33"/>
+      <c r="B246" s="37"/>
       <c r="C246" s="35"/>
       <c r="D246" s="35"/>
       <c r="E246" s="35"/>
@@ -17794,8 +18524,8 @@
       </c>
     </row>
     <row r="247" ht="20.05" customHeight="1">
-      <c r="A247" s="36"/>
-      <c r="B247" s="34"/>
+      <c r="A247" s="33"/>
+      <c r="B247" s="37"/>
       <c r="C247" s="35"/>
       <c r="D247" s="35"/>
       <c r="E247" s="35"/>
@@ -17842,8 +18572,8 @@
       </c>
     </row>
     <row r="248" ht="20.05" customHeight="1">
-      <c r="A248" s="36"/>
-      <c r="B248" s="34"/>
+      <c r="A248" s="33"/>
+      <c r="B248" s="37"/>
       <c r="C248" s="35"/>
       <c r="D248" s="35"/>
       <c r="E248" s="35"/>
@@ -17890,8 +18620,8 @@
       </c>
     </row>
     <row r="249" ht="20.05" customHeight="1">
-      <c r="A249" s="36"/>
-      <c r="B249" s="34"/>
+      <c r="A249" s="33"/>
+      <c r="B249" s="37"/>
       <c r="C249" s="35"/>
       <c r="D249" s="35"/>
       <c r="E249" s="35"/>
@@ -17938,8 +18668,8 @@
       </c>
     </row>
     <row r="250" ht="20.05" customHeight="1">
-      <c r="A250" s="36"/>
-      <c r="B250" s="34"/>
+      <c r="A250" s="33"/>
+      <c r="B250" s="37"/>
       <c r="C250" s="35"/>
       <c r="D250" s="35"/>
       <c r="E250" s="35"/>
@@ -17986,8 +18716,8 @@
       </c>
     </row>
     <row r="251" ht="20.05" customHeight="1">
-      <c r="A251" s="36"/>
-      <c r="B251" s="34"/>
+      <c r="A251" s="33"/>
+      <c r="B251" s="37"/>
       <c r="C251" s="35"/>
       <c r="D251" s="35"/>
       <c r="E251" s="35"/>
@@ -18034,8 +18764,8 @@
       </c>
     </row>
     <row r="252" ht="20.05" customHeight="1">
-      <c r="A252" s="36"/>
-      <c r="B252" s="34"/>
+      <c r="A252" s="33"/>
+      <c r="B252" s="37"/>
       <c r="C252" s="35"/>
       <c r="D252" s="35"/>
       <c r="E252" s="35"/>
@@ -18082,8 +18812,8 @@
       </c>
     </row>
     <row r="253" ht="20.05" customHeight="1">
-      <c r="A253" s="36"/>
-      <c r="B253" s="34"/>
+      <c r="A253" s="33"/>
+      <c r="B253" s="37"/>
       <c r="C253" s="35"/>
       <c r="D253" s="35"/>
       <c r="E253" s="35"/>
@@ -18130,8 +18860,8 @@
       </c>
     </row>
     <row r="254" ht="20.05" customHeight="1">
-      <c r="A254" s="36"/>
-      <c r="B254" s="34"/>
+      <c r="A254" s="33"/>
+      <c r="B254" s="37"/>
       <c r="C254" s="35"/>
       <c r="D254" s="35"/>
       <c r="E254" s="35"/>
@@ -18178,8 +18908,8 @@
       </c>
     </row>
     <row r="255" ht="20.05" customHeight="1">
-      <c r="A255" s="36"/>
-      <c r="B255" s="34"/>
+      <c r="A255" s="33"/>
+      <c r="B255" s="37"/>
       <c r="C255" s="35"/>
       <c r="D255" s="35"/>
       <c r="E255" s="35"/>
@@ -18226,8 +18956,8 @@
       </c>
     </row>
     <row r="256" ht="20.05" customHeight="1">
-      <c r="A256" s="36"/>
-      <c r="B256" s="34"/>
+      <c r="A256" s="33"/>
+      <c r="B256" s="37"/>
       <c r="C256" s="35"/>
       <c r="D256" s="35"/>
       <c r="E256" s="35"/>
@@ -18274,8 +19004,8 @@
       </c>
     </row>
     <row r="257" ht="20.05" customHeight="1">
-      <c r="A257" s="36"/>
-      <c r="B257" s="34"/>
+      <c r="A257" s="33"/>
+      <c r="B257" s="37"/>
       <c r="C257" s="35"/>
       <c r="D257" s="35"/>
       <c r="E257" s="35"/>
@@ -18322,8 +19052,8 @@
       </c>
     </row>
     <row r="258" ht="20.05" customHeight="1">
-      <c r="A258" s="36"/>
-      <c r="B258" s="34"/>
+      <c r="A258" s="33"/>
+      <c r="B258" s="37"/>
       <c r="C258" s="35"/>
       <c r="D258" s="35"/>
       <c r="E258" s="35"/>
@@ -18370,8 +19100,8 @@
       </c>
     </row>
     <row r="259" ht="20.05" customHeight="1">
-      <c r="A259" s="36"/>
-      <c r="B259" s="34"/>
+      <c r="A259" s="33"/>
+      <c r="B259" s="37"/>
       <c r="C259" s="35"/>
       <c r="D259" s="35"/>
       <c r="E259" s="35"/>
@@ -18418,8 +19148,8 @@
       </c>
     </row>
     <row r="260" ht="20.05" customHeight="1">
-      <c r="A260" s="36"/>
-      <c r="B260" s="34"/>
+      <c r="A260" s="33"/>
+      <c r="B260" s="37"/>
       <c r="C260" s="35"/>
       <c r="D260" s="35"/>
       <c r="E260" s="35"/>
@@ -18466,8 +19196,8 @@
       </c>
     </row>
     <row r="261" ht="20.05" customHeight="1">
-      <c r="A261" s="36"/>
-      <c r="B261" s="34"/>
+      <c r="A261" s="33"/>
+      <c r="B261" s="37"/>
       <c r="C261" s="35"/>
       <c r="D261" s="35"/>
       <c r="E261" s="35"/>
@@ -18514,8 +19244,8 @@
       </c>
     </row>
     <row r="262" ht="20.05" customHeight="1">
-      <c r="A262" s="36"/>
-      <c r="B262" s="34"/>
+      <c r="A262" s="33"/>
+      <c r="B262" s="37"/>
       <c r="C262" s="35"/>
       <c r="D262" s="35"/>
       <c r="E262" s="35"/>
@@ -18562,8 +19292,8 @@
       </c>
     </row>
     <row r="263" ht="20.05" customHeight="1">
-      <c r="A263" s="36"/>
-      <c r="B263" s="34"/>
+      <c r="A263" s="33"/>
+      <c r="B263" s="37"/>
       <c r="C263" s="35"/>
       <c r="D263" s="35"/>
       <c r="E263" s="35"/>
@@ -18610,8 +19340,8 @@
       </c>
     </row>
     <row r="264" ht="20.05" customHeight="1">
-      <c r="A264" s="36"/>
-      <c r="B264" s="34"/>
+      <c r="A264" s="33"/>
+      <c r="B264" s="37"/>
       <c r="C264" s="35"/>
       <c r="D264" s="35"/>
       <c r="E264" s="35"/>
@@ -18658,8 +19388,8 @@
       </c>
     </row>
     <row r="265" ht="20.05" customHeight="1">
-      <c r="A265" s="36"/>
-      <c r="B265" s="34"/>
+      <c r="A265" s="33"/>
+      <c r="B265" s="37"/>
       <c r="C265" s="35"/>
       <c r="D265" s="35"/>
       <c r="E265" s="35"/>
@@ -18706,8 +19436,8 @@
       </c>
     </row>
     <row r="266" ht="20.05" customHeight="1">
-      <c r="A266" s="36"/>
-      <c r="B266" s="34"/>
+      <c r="A266" s="33"/>
+      <c r="B266" s="37"/>
       <c r="C266" s="35"/>
       <c r="D266" s="35"/>
       <c r="E266" s="35"/>
@@ -18754,8 +19484,8 @@
       </c>
     </row>
     <row r="267" ht="20.05" customHeight="1">
-      <c r="A267" s="36"/>
-      <c r="B267" s="34"/>
+      <c r="A267" s="33"/>
+      <c r="B267" s="37"/>
       <c r="C267" s="35"/>
       <c r="D267" s="35"/>
       <c r="E267" s="35"/>
@@ -18802,8 +19532,8 @@
       </c>
     </row>
     <row r="268" ht="20.05" customHeight="1">
-      <c r="A268" s="36"/>
-      <c r="B268" s="34"/>
+      <c r="A268" s="33"/>
+      <c r="B268" s="37"/>
       <c r="C268" s="35"/>
       <c r="D268" s="35"/>
       <c r="E268" s="35"/>
@@ -18850,8 +19580,8 @@
       </c>
     </row>
     <row r="269" ht="20.05" customHeight="1">
-      <c r="A269" s="36"/>
-      <c r="B269" s="34"/>
+      <c r="A269" s="33"/>
+      <c r="B269" s="37"/>
       <c r="C269" s="35"/>
       <c r="D269" s="35"/>
       <c r="E269" s="35"/>
@@ -18898,8 +19628,8 @@
       </c>
     </row>
     <row r="270" ht="20.05" customHeight="1">
-      <c r="A270" s="36"/>
-      <c r="B270" s="34"/>
+      <c r="A270" s="33"/>
+      <c r="B270" s="37"/>
       <c r="C270" s="35"/>
       <c r="D270" s="35"/>
       <c r="E270" s="35"/>
@@ -18946,8 +19676,8 @@
       </c>
     </row>
     <row r="271" ht="20.05" customHeight="1">
-      <c r="A271" s="36"/>
-      <c r="B271" s="34"/>
+      <c r="A271" s="33"/>
+      <c r="B271" s="37"/>
       <c r="C271" s="35"/>
       <c r="D271" s="35"/>
       <c r="E271" s="35"/>
@@ -18994,8 +19724,8 @@
       </c>
     </row>
     <row r="272" ht="20.05" customHeight="1">
-      <c r="A272" s="36"/>
-      <c r="B272" s="34"/>
+      <c r="A272" s="33"/>
+      <c r="B272" s="37"/>
       <c r="C272" s="35"/>
       <c r="D272" s="35"/>
       <c r="E272" s="35"/>
@@ -19042,8 +19772,8 @@
       </c>
     </row>
     <row r="273" ht="20.05" customHeight="1">
-      <c r="A273" s="36"/>
-      <c r="B273" s="34"/>
+      <c r="A273" s="33"/>
+      <c r="B273" s="37"/>
       <c r="C273" s="35"/>
       <c r="D273" s="35"/>
       <c r="E273" s="35"/>
@@ -19090,8 +19820,8 @@
       </c>
     </row>
     <row r="274" ht="20.05" customHeight="1">
-      <c r="A274" s="36"/>
-      <c r="B274" s="34"/>
+      <c r="A274" s="33"/>
+      <c r="B274" s="37"/>
       <c r="C274" s="35"/>
       <c r="D274" s="35"/>
       <c r="E274" s="35"/>
@@ -19138,8 +19868,8 @@
       </c>
     </row>
     <row r="275" ht="20.05" customHeight="1">
-      <c r="A275" s="36"/>
-      <c r="B275" s="34"/>
+      <c r="A275" s="33"/>
+      <c r="B275" s="37"/>
       <c r="C275" s="35"/>
       <c r="D275" s="35"/>
       <c r="E275" s="35"/>
@@ -19186,8 +19916,8 @@
       </c>
     </row>
     <row r="276" ht="20.05" customHeight="1">
-      <c r="A276" s="36"/>
-      <c r="B276" s="34"/>
+      <c r="A276" s="33"/>
+      <c r="B276" s="37"/>
       <c r="C276" s="35"/>
       <c r="D276" s="35"/>
       <c r="E276" s="35"/>
@@ -19234,8 +19964,8 @@
       </c>
     </row>
     <row r="277" ht="20.05" customHeight="1">
-      <c r="A277" s="36"/>
-      <c r="B277" s="34"/>
+      <c r="A277" s="33"/>
+      <c r="B277" s="37"/>
       <c r="C277" s="35"/>
       <c r="D277" s="35"/>
       <c r="E277" s="35"/>
@@ -19282,8 +20012,8 @@
       </c>
     </row>
     <row r="278" ht="20.05" customHeight="1">
-      <c r="A278" s="36"/>
-      <c r="B278" s="34"/>
+      <c r="A278" s="33"/>
+      <c r="B278" s="37"/>
       <c r="C278" s="35"/>
       <c r="D278" s="35"/>
       <c r="E278" s="35"/>
@@ -19330,8 +20060,8 @@
       </c>
     </row>
     <row r="279" ht="20.05" customHeight="1">
-      <c r="A279" s="36"/>
-      <c r="B279" s="34"/>
+      <c r="A279" s="33"/>
+      <c r="B279" s="37"/>
       <c r="C279" s="35"/>
       <c r="D279" s="35"/>
       <c r="E279" s="35"/>
@@ -19378,8 +20108,8 @@
       </c>
     </row>
     <row r="280" ht="20.05" customHeight="1">
-      <c r="A280" s="36"/>
-      <c r="B280" s="34"/>
+      <c r="A280" s="33"/>
+      <c r="B280" s="37"/>
       <c r="C280" s="35"/>
       <c r="D280" s="35"/>
       <c r="E280" s="35"/>
@@ -19426,8 +20156,8 @@
       </c>
     </row>
     <row r="281" ht="20.05" customHeight="1">
-      <c r="A281" s="36"/>
-      <c r="B281" s="34"/>
+      <c r="A281" s="33"/>
+      <c r="B281" s="37"/>
       <c r="C281" s="35"/>
       <c r="D281" s="35"/>
       <c r="E281" s="35"/>
@@ -19474,8 +20204,8 @@
       </c>
     </row>
     <row r="282" ht="20.05" customHeight="1">
-      <c r="A282" s="36"/>
-      <c r="B282" s="34"/>
+      <c r="A282" s="33"/>
+      <c r="B282" s="37"/>
       <c r="C282" s="35"/>
       <c r="D282" s="35"/>
       <c r="E282" s="35"/>
@@ -19522,8 +20252,8 @@
       </c>
     </row>
     <row r="283" ht="20.05" customHeight="1">
-      <c r="A283" s="36"/>
-      <c r="B283" s="34"/>
+      <c r="A283" s="33"/>
+      <c r="B283" s="37"/>
       <c r="C283" s="35"/>
       <c r="D283" s="35"/>
       <c r="E283" s="35"/>
@@ -19570,8 +20300,8 @@
       </c>
     </row>
     <row r="284" ht="20.05" customHeight="1">
-      <c r="A284" s="36"/>
-      <c r="B284" s="34"/>
+      <c r="A284" s="33"/>
+      <c r="B284" s="37"/>
       <c r="C284" s="35"/>
       <c r="D284" s="35"/>
       <c r="E284" s="35"/>
@@ -19618,8 +20348,8 @@
       </c>
     </row>
     <row r="285" ht="20.05" customHeight="1">
-      <c r="A285" s="36"/>
-      <c r="B285" s="34"/>
+      <c r="A285" s="33"/>
+      <c r="B285" s="37"/>
       <c r="C285" s="35"/>
       <c r="D285" s="35"/>
       <c r="E285" s="35"/>
@@ -19666,8 +20396,8 @@
       </c>
     </row>
     <row r="286" ht="20.05" customHeight="1">
-      <c r="A286" s="36"/>
-      <c r="B286" s="34"/>
+      <c r="A286" s="33"/>
+      <c r="B286" s="37"/>
       <c r="C286" s="35"/>
       <c r="D286" s="35"/>
       <c r="E286" s="35"/>
@@ -19714,8 +20444,8 @@
       </c>
     </row>
     <row r="287" ht="20.05" customHeight="1">
-      <c r="A287" s="36"/>
-      <c r="B287" s="34"/>
+      <c r="A287" s="33"/>
+      <c r="B287" s="37"/>
       <c r="C287" s="35"/>
       <c r="D287" s="35"/>
       <c r="E287" s="35"/>
@@ -19762,8 +20492,8 @@
       </c>
     </row>
     <row r="288" ht="20.05" customHeight="1">
-      <c r="A288" s="36"/>
-      <c r="B288" s="34"/>
+      <c r="A288" s="33"/>
+      <c r="B288" s="37"/>
       <c r="C288" s="35"/>
       <c r="D288" s="35"/>
       <c r="E288" s="35"/>
@@ -19810,8 +20540,8 @@
       </c>
     </row>
     <row r="289" ht="20.05" customHeight="1">
-      <c r="A289" s="36"/>
-      <c r="B289" s="34"/>
+      <c r="A289" s="33"/>
+      <c r="B289" s="37"/>
       <c r="C289" s="35"/>
       <c r="D289" s="35"/>
       <c r="E289" s="35"/>
@@ -19858,8 +20588,8 @@
       </c>
     </row>
     <row r="290" ht="20.05" customHeight="1">
-      <c r="A290" s="36"/>
-      <c r="B290" s="34"/>
+      <c r="A290" s="33"/>
+      <c r="B290" s="37"/>
       <c r="C290" s="35"/>
       <c r="D290" s="35"/>
       <c r="E290" s="35"/>
@@ -19906,8 +20636,8 @@
       </c>
     </row>
     <row r="291" ht="20.05" customHeight="1">
-      <c r="A291" s="36"/>
-      <c r="B291" s="34"/>
+      <c r="A291" s="33"/>
+      <c r="B291" s="37"/>
       <c r="C291" s="35"/>
       <c r="D291" s="35"/>
       <c r="E291" s="35"/>
@@ -19954,8 +20684,8 @@
       </c>
     </row>
     <row r="292" ht="20.05" customHeight="1">
-      <c r="A292" s="36"/>
-      <c r="B292" s="34"/>
+      <c r="A292" s="33"/>
+      <c r="B292" s="37"/>
       <c r="C292" s="35"/>
       <c r="D292" s="35"/>
       <c r="E292" s="35"/>
@@ -20002,8 +20732,8 @@
       </c>
     </row>
     <row r="293" ht="20.05" customHeight="1">
-      <c r="A293" s="36"/>
-      <c r="B293" s="34"/>
+      <c r="A293" s="33"/>
+      <c r="B293" s="37"/>
       <c r="C293" s="35"/>
       <c r="D293" s="35"/>
       <c r="E293" s="35"/>
@@ -20050,8 +20780,8 @@
       </c>
     </row>
     <row r="294" ht="20.05" customHeight="1">
-      <c r="A294" s="36"/>
-      <c r="B294" s="34"/>
+      <c r="A294" s="33"/>
+      <c r="B294" s="37"/>
       <c r="C294" s="35"/>
       <c r="D294" s="35"/>
       <c r="E294" s="35"/>
@@ -20098,8 +20828,8 @@
       </c>
     </row>
     <row r="295" ht="20.05" customHeight="1">
-      <c r="A295" s="36"/>
-      <c r="B295" s="34"/>
+      <c r="A295" s="33"/>
+      <c r="B295" s="37"/>
       <c r="C295" s="35"/>
       <c r="D295" s="35"/>
       <c r="E295" s="35"/>
@@ -20146,8 +20876,8 @@
       </c>
     </row>
     <row r="296" ht="20.05" customHeight="1">
-      <c r="A296" s="36"/>
-      <c r="B296" s="34"/>
+      <c r="A296" s="33"/>
+      <c r="B296" s="37"/>
       <c r="C296" s="35"/>
       <c r="D296" s="35"/>
       <c r="E296" s="35"/>
@@ -20194,8 +20924,8 @@
       </c>
     </row>
     <row r="297" ht="20.05" customHeight="1">
-      <c r="A297" s="36"/>
-      <c r="B297" s="34"/>
+      <c r="A297" s="33"/>
+      <c r="B297" s="37"/>
       <c r="C297" s="35"/>
       <c r="D297" s="35"/>
       <c r="E297" s="35"/>
@@ -20242,8 +20972,8 @@
       </c>
     </row>
     <row r="298" ht="20.05" customHeight="1">
-      <c r="A298" s="36"/>
-      <c r="B298" s="34"/>
+      <c r="A298" s="33"/>
+      <c r="B298" s="37"/>
       <c r="C298" s="35"/>
       <c r="D298" s="35"/>
       <c r="E298" s="35"/>
@@ -20290,8 +21020,8 @@
       </c>
     </row>
     <row r="299" ht="20.05" customHeight="1">
-      <c r="A299" s="36"/>
-      <c r="B299" s="34"/>
+      <c r="A299" s="33"/>
+      <c r="B299" s="37"/>
       <c r="C299" s="35"/>
       <c r="D299" s="35"/>
       <c r="E299" s="35"/>
@@ -20338,8 +21068,8 @@
       </c>
     </row>
     <row r="300" ht="20.05" customHeight="1">
-      <c r="A300" s="36"/>
-      <c r="B300" s="34"/>
+      <c r="A300" s="33"/>
+      <c r="B300" s="37"/>
       <c r="C300" s="35"/>
       <c r="D300" s="35"/>
       <c r="E300" s="35"/>
@@ -20386,8 +21116,8 @@
       </c>
     </row>
     <row r="301" ht="20.05" customHeight="1">
-      <c r="A301" s="36"/>
-      <c r="B301" s="34"/>
+      <c r="A301" s="33"/>
+      <c r="B301" s="37"/>
       <c r="C301" s="35"/>
       <c r="D301" s="35"/>
       <c r="E301" s="35"/>
@@ -20434,8 +21164,8 @@
       </c>
     </row>
     <row r="302" ht="20.05" customHeight="1">
-      <c r="A302" s="36"/>
-      <c r="B302" s="34"/>
+      <c r="A302" s="33"/>
+      <c r="B302" s="37"/>
       <c r="C302" s="35"/>
       <c r="D302" s="35"/>
       <c r="E302" s="35"/>
@@ -20482,8 +21212,8 @@
       </c>
     </row>
     <row r="303" ht="20.05" customHeight="1">
-      <c r="A303" s="36"/>
-      <c r="B303" s="34"/>
+      <c r="A303" s="33"/>
+      <c r="B303" s="37"/>
       <c r="C303" s="35"/>
       <c r="D303" s="35"/>
       <c r="E303" s="35"/>
@@ -20530,8 +21260,8 @@
       </c>
     </row>
     <row r="304" ht="20.05" customHeight="1">
-      <c r="A304" s="36"/>
-      <c r="B304" s="34"/>
+      <c r="A304" s="33"/>
+      <c r="B304" s="37"/>
       <c r="C304" s="35"/>
       <c r="D304" s="35"/>
       <c r="E304" s="35"/>
@@ -20578,8 +21308,8 @@
       </c>
     </row>
     <row r="305" ht="20.05" customHeight="1">
-      <c r="A305" s="36"/>
-      <c r="B305" s="34"/>
+      <c r="A305" s="33"/>
+      <c r="B305" s="37"/>
       <c r="C305" s="35"/>
       <c r="D305" s="35"/>
       <c r="E305" s="35"/>
@@ -20626,8 +21356,8 @@
       </c>
     </row>
     <row r="306" ht="20.05" customHeight="1">
-      <c r="A306" s="36"/>
-      <c r="B306" s="34"/>
+      <c r="A306" s="33"/>
+      <c r="B306" s="37"/>
       <c r="C306" s="35"/>
       <c r="D306" s="35"/>
       <c r="E306" s="35"/>
@@ -20674,8 +21404,8 @@
       </c>
     </row>
     <row r="307" ht="20.05" customHeight="1">
-      <c r="A307" s="36"/>
-      <c r="B307" s="34"/>
+      <c r="A307" s="33"/>
+      <c r="B307" s="37"/>
       <c r="C307" s="35"/>
       <c r="D307" s="35"/>
       <c r="E307" s="35"/>
@@ -20722,8 +21452,8 @@
       </c>
     </row>
     <row r="308" ht="20.05" customHeight="1">
-      <c r="A308" s="36"/>
-      <c r="B308" s="34"/>
+      <c r="A308" s="33"/>
+      <c r="B308" s="37"/>
       <c r="C308" s="35"/>
       <c r="D308" s="35"/>
       <c r="E308" s="35"/>
@@ -20770,8 +21500,8 @@
       </c>
     </row>
     <row r="309" ht="20.05" customHeight="1">
-      <c r="A309" s="36"/>
-      <c r="B309" s="34"/>
+      <c r="A309" s="33"/>
+      <c r="B309" s="37"/>
       <c r="C309" s="35"/>
       <c r="D309" s="35"/>
       <c r="E309" s="35"/>
@@ -20818,8 +21548,8 @@
       </c>
     </row>
     <row r="310" ht="20.05" customHeight="1">
-      <c r="A310" s="36"/>
-      <c r="B310" s="34"/>
+      <c r="A310" s="33"/>
+      <c r="B310" s="37"/>
       <c r="C310" s="35"/>
       <c r="D310" s="35"/>
       <c r="E310" s="35"/>
@@ -20866,8 +21596,8 @@
       </c>
     </row>
     <row r="311" ht="20.05" customHeight="1">
-      <c r="A311" s="36"/>
-      <c r="B311" s="34"/>
+      <c r="A311" s="33"/>
+      <c r="B311" s="37"/>
       <c r="C311" s="35"/>
       <c r="D311" s="35"/>
       <c r="E311" s="35"/>
@@ -20914,8 +21644,8 @@
       </c>
     </row>
     <row r="312" ht="20.05" customHeight="1">
-      <c r="A312" s="36"/>
-      <c r="B312" s="34"/>
+      <c r="A312" s="33"/>
+      <c r="B312" s="37"/>
       <c r="C312" s="35"/>
       <c r="D312" s="35"/>
       <c r="E312" s="35"/>
@@ -20962,8 +21692,8 @@
       </c>
     </row>
     <row r="313" ht="20.05" customHeight="1">
-      <c r="A313" s="36"/>
-      <c r="B313" s="34"/>
+      <c r="A313" s="33"/>
+      <c r="B313" s="37"/>
       <c r="C313" s="35"/>
       <c r="D313" s="35"/>
       <c r="E313" s="35"/>
@@ -21010,8 +21740,8 @@
       </c>
     </row>
     <row r="314" ht="20.05" customHeight="1">
-      <c r="A314" s="36"/>
-      <c r="B314" s="34"/>
+      <c r="A314" s="33"/>
+      <c r="B314" s="37"/>
       <c r="C314" s="35"/>
       <c r="D314" s="35"/>
       <c r="E314" s="35"/>
@@ -21058,8 +21788,8 @@
       </c>
     </row>
     <row r="315" ht="20.05" customHeight="1">
-      <c r="A315" s="36"/>
-      <c r="B315" s="34"/>
+      <c r="A315" s="33"/>
+      <c r="B315" s="37"/>
       <c r="C315" s="35"/>
       <c r="D315" s="35"/>
       <c r="E315" s="35"/>
@@ -21106,8 +21836,8 @@
       </c>
     </row>
     <row r="316" ht="20.05" customHeight="1">
-      <c r="A316" s="36"/>
-      <c r="B316" s="34"/>
+      <c r="A316" s="33"/>
+      <c r="B316" s="37"/>
       <c r="C316" s="35"/>
       <c r="D316" s="35"/>
       <c r="E316" s="35"/>
@@ -21154,8 +21884,8 @@
       </c>
     </row>
     <row r="317" ht="20.05" customHeight="1">
-      <c r="A317" s="36"/>
-      <c r="B317" s="34"/>
+      <c r="A317" s="33"/>
+      <c r="B317" s="37"/>
       <c r="C317" s="35"/>
       <c r="D317" s="35"/>
       <c r="E317" s="35"/>
@@ -21202,8 +21932,8 @@
       </c>
     </row>
     <row r="318" ht="20.05" customHeight="1">
-      <c r="A318" s="36"/>
-      <c r="B318" s="34"/>
+      <c r="A318" s="33"/>
+      <c r="B318" s="37"/>
       <c r="C318" s="35"/>
       <c r="D318" s="35"/>
       <c r="E318" s="35"/>
@@ -21250,8 +21980,8 @@
       </c>
     </row>
     <row r="319" ht="20.05" customHeight="1">
-      <c r="A319" s="36"/>
-      <c r="B319" s="34"/>
+      <c r="A319" s="33"/>
+      <c r="B319" s="37"/>
       <c r="C319" s="35"/>
       <c r="D319" s="35"/>
       <c r="E319" s="35"/>
@@ -21298,8 +22028,8 @@
       </c>
     </row>
     <row r="320" ht="20.05" customHeight="1">
-      <c r="A320" s="36"/>
-      <c r="B320" s="34"/>
+      <c r="A320" s="33"/>
+      <c r="B320" s="37"/>
       <c r="C320" s="35"/>
       <c r="D320" s="35"/>
       <c r="E320" s="35"/>
@@ -21346,8 +22076,8 @@
       </c>
     </row>
     <row r="321" ht="20.05" customHeight="1">
-      <c r="A321" s="36"/>
-      <c r="B321" s="34"/>
+      <c r="A321" s="33"/>
+      <c r="B321" s="37"/>
       <c r="C321" s="35"/>
       <c r="D321" s="35"/>
       <c r="E321" s="35"/>
@@ -21394,8 +22124,8 @@
       </c>
     </row>
     <row r="322" ht="20.05" customHeight="1">
-      <c r="A322" s="36"/>
-      <c r="B322" s="34"/>
+      <c r="A322" s="33"/>
+      <c r="B322" s="37"/>
       <c r="C322" s="35"/>
       <c r="D322" s="35"/>
       <c r="E322" s="35"/>
@@ -21442,8 +22172,8 @@
       </c>
     </row>
     <row r="323" ht="20.05" customHeight="1">
-      <c r="A323" s="36"/>
-      <c r="B323" s="34"/>
+      <c r="A323" s="33"/>
+      <c r="B323" s="37"/>
       <c r="C323" s="35"/>
       <c r="D323" s="35"/>
       <c r="E323" s="35"/>
@@ -21490,8 +22220,8 @@
       </c>
     </row>
     <row r="324" ht="20.05" customHeight="1">
-      <c r="A324" s="36"/>
-      <c r="B324" s="34"/>
+      <c r="A324" s="33"/>
+      <c r="B324" s="37"/>
       <c r="C324" s="35"/>
       <c r="D324" s="35"/>
       <c r="E324" s="35"/>
@@ -21538,8 +22268,8 @@
       </c>
     </row>
     <row r="325" ht="20.05" customHeight="1">
-      <c r="A325" s="36"/>
-      <c r="B325" s="34"/>
+      <c r="A325" s="33"/>
+      <c r="B325" s="37"/>
       <c r="C325" s="35"/>
       <c r="D325" s="35"/>
       <c r="E325" s="35"/>
@@ -21586,8 +22316,8 @@
       </c>
     </row>
     <row r="326" ht="20.05" customHeight="1">
-      <c r="A326" s="36"/>
-      <c r="B326" s="34"/>
+      <c r="A326" s="33"/>
+      <c r="B326" s="37"/>
       <c r="C326" s="35"/>
       <c r="D326" s="35"/>
       <c r="E326" s="35"/>
@@ -21634,8 +22364,8 @@
       </c>
     </row>
     <row r="327" ht="20.05" customHeight="1">
-      <c r="A327" s="36"/>
-      <c r="B327" s="34"/>
+      <c r="A327" s="33"/>
+      <c r="B327" s="37"/>
       <c r="C327" s="35"/>
       <c r="D327" s="35"/>
       <c r="E327" s="35"/>
@@ -21682,8 +22412,8 @@
       </c>
     </row>
     <row r="328" ht="20.05" customHeight="1">
-      <c r="A328" s="36"/>
-      <c r="B328" s="34"/>
+      <c r="A328" s="33"/>
+      <c r="B328" s="37"/>
       <c r="C328" s="35"/>
       <c r="D328" s="35"/>
       <c r="E328" s="35"/>
@@ -21730,8 +22460,8 @@
       </c>
     </row>
     <row r="329" ht="20.05" customHeight="1">
-      <c r="A329" s="36"/>
-      <c r="B329" s="34"/>
+      <c r="A329" s="33"/>
+      <c r="B329" s="37"/>
       <c r="C329" s="35"/>
       <c r="D329" s="35"/>
       <c r="E329" s="35"/>
@@ -21778,8 +22508,8 @@
       </c>
     </row>
     <row r="330" ht="20.05" customHeight="1">
-      <c r="A330" s="36"/>
-      <c r="B330" s="34"/>
+      <c r="A330" s="33"/>
+      <c r="B330" s="37"/>
       <c r="C330" s="35"/>
       <c r="D330" s="35"/>
       <c r="E330" s="35"/>
@@ -21826,8 +22556,8 @@
       </c>
     </row>
     <row r="331" ht="20.05" customHeight="1">
-      <c r="A331" s="36"/>
-      <c r="B331" s="34"/>
+      <c r="A331" s="33"/>
+      <c r="B331" s="37"/>
       <c r="C331" s="35"/>
       <c r="D331" s="35"/>
       <c r="E331" s="35"/>
@@ -21874,8 +22604,8 @@
       </c>
     </row>
     <row r="332" ht="20.05" customHeight="1">
-      <c r="A332" s="36"/>
-      <c r="B332" s="34"/>
+      <c r="A332" s="33"/>
+      <c r="B332" s="37"/>
       <c r="C332" s="35"/>
       <c r="D332" s="35"/>
       <c r="E332" s="35"/>
@@ -21922,8 +22652,8 @@
       </c>
     </row>
     <row r="333" ht="20.05" customHeight="1">
-      <c r="A333" s="36"/>
-      <c r="B333" s="34"/>
+      <c r="A333" s="33"/>
+      <c r="B333" s="37"/>
       <c r="C333" s="35"/>
       <c r="D333" s="35"/>
       <c r="E333" s="35"/>
@@ -21970,8 +22700,8 @@
       </c>
     </row>
     <row r="334" ht="20.05" customHeight="1">
-      <c r="A334" s="36"/>
-      <c r="B334" s="34"/>
+      <c r="A334" s="33"/>
+      <c r="B334" s="37"/>
       <c r="C334" s="35"/>
       <c r="D334" s="35"/>
       <c r="E334" s="35"/>
@@ -22018,8 +22748,8 @@
       </c>
     </row>
     <row r="335" ht="20.05" customHeight="1">
-      <c r="A335" s="36"/>
-      <c r="B335" s="34"/>
+      <c r="A335" s="33"/>
+      <c r="B335" s="37"/>
       <c r="C335" s="35"/>
       <c r="D335" s="35"/>
       <c r="E335" s="35"/>
@@ -22066,8 +22796,8 @@
       </c>
     </row>
     <row r="336" ht="20.05" customHeight="1">
-      <c r="A336" s="36"/>
-      <c r="B336" s="34"/>
+      <c r="A336" s="33"/>
+      <c r="B336" s="37"/>
       <c r="C336" s="35"/>
       <c r="D336" s="35"/>
       <c r="E336" s="35"/>
@@ -22114,8 +22844,8 @@
       </c>
     </row>
     <row r="337" ht="20.05" customHeight="1">
-      <c r="A337" s="36"/>
-      <c r="B337" s="34"/>
+      <c r="A337" s="33"/>
+      <c r="B337" s="37"/>
       <c r="C337" s="35"/>
       <c r="D337" s="35"/>
       <c r="E337" s="35"/>
@@ -22162,8 +22892,8 @@
       </c>
     </row>
     <row r="338" ht="20.05" customHeight="1">
-      <c r="A338" s="36"/>
-      <c r="B338" s="34"/>
+      <c r="A338" s="33"/>
+      <c r="B338" s="37"/>
       <c r="C338" s="35"/>
       <c r="D338" s="35"/>
       <c r="E338" s="35"/>
@@ -22210,8 +22940,8 @@
       </c>
     </row>
     <row r="339" ht="20.05" customHeight="1">
-      <c r="A339" s="36"/>
-      <c r="B339" s="34"/>
+      <c r="A339" s="33"/>
+      <c r="B339" s="37"/>
       <c r="C339" s="35"/>
       <c r="D339" s="35"/>
       <c r="E339" s="35"/>
@@ -22258,8 +22988,8 @@
       </c>
     </row>
     <row r="340" ht="20.05" customHeight="1">
-      <c r="A340" s="36"/>
-      <c r="B340" s="34"/>
+      <c r="A340" s="33"/>
+      <c r="B340" s="37"/>
       <c r="C340" s="35"/>
       <c r="D340" s="35"/>
       <c r="E340" s="35"/>
@@ -22306,8 +23036,8 @@
       </c>
     </row>
     <row r="341" ht="20.05" customHeight="1">
-      <c r="A341" s="36"/>
-      <c r="B341" s="34"/>
+      <c r="A341" s="33"/>
+      <c r="B341" s="37"/>
       <c r="C341" s="35"/>
       <c r="D341" s="35"/>
       <c r="E341" s="35"/>
@@ -22354,8 +23084,8 @@
       </c>
     </row>
     <row r="342" ht="20.05" customHeight="1">
-      <c r="A342" s="36"/>
-      <c r="B342" s="34"/>
+      <c r="A342" s="33"/>
+      <c r="B342" s="37"/>
       <c r="C342" s="35"/>
       <c r="D342" s="35"/>
       <c r="E342" s="35"/>
@@ -22402,8 +23132,8 @@
       </c>
     </row>
     <row r="343" ht="20.05" customHeight="1">
-      <c r="A343" s="36"/>
-      <c r="B343" s="34"/>
+      <c r="A343" s="33"/>
+      <c r="B343" s="37"/>
       <c r="C343" s="35"/>
       <c r="D343" s="35"/>
       <c r="E343" s="35"/>
@@ -22450,8 +23180,8 @@
       </c>
     </row>
     <row r="344" ht="20.05" customHeight="1">
-      <c r="A344" s="36"/>
-      <c r="B344" s="34"/>
+      <c r="A344" s="33"/>
+      <c r="B344" s="37"/>
       <c r="C344" s="35"/>
       <c r="D344" s="35"/>
       <c r="E344" s="35"/>
@@ -22498,8 +23228,8 @@
       </c>
     </row>
     <row r="345" ht="20.05" customHeight="1">
-      <c r="A345" s="36"/>
-      <c r="B345" s="34"/>
+      <c r="A345" s="33"/>
+      <c r="B345" s="37"/>
       <c r="C345" s="35"/>
       <c r="D345" s="35"/>
       <c r="E345" s="35"/>
@@ -22546,8 +23276,8 @@
       </c>
     </row>
     <row r="346" ht="20.05" customHeight="1">
-      <c r="A346" s="36"/>
-      <c r="B346" s="34"/>
+      <c r="A346" s="33"/>
+      <c r="B346" s="37"/>
       <c r="C346" s="35"/>
       <c r="D346" s="35"/>
       <c r="E346" s="35"/>
@@ -22594,8 +23324,8 @@
       </c>
     </row>
     <row r="347" ht="20.05" customHeight="1">
-      <c r="A347" s="36"/>
-      <c r="B347" s="34"/>
+      <c r="A347" s="33"/>
+      <c r="B347" s="37"/>
       <c r="C347" s="35"/>
       <c r="D347" s="35"/>
       <c r="E347" s="35"/>
@@ -22642,8 +23372,8 @@
       </c>
     </row>
     <row r="348" ht="20.05" customHeight="1">
-      <c r="A348" s="36"/>
-      <c r="B348" s="34"/>
+      <c r="A348" s="33"/>
+      <c r="B348" s="37"/>
       <c r="C348" s="35"/>
       <c r="D348" s="35"/>
       <c r="E348" s="35"/>
@@ -22690,8 +23420,8 @@
       </c>
     </row>
     <row r="349" ht="20.05" customHeight="1">
-      <c r="A349" s="36"/>
-      <c r="B349" s="34"/>
+      <c r="A349" s="33"/>
+      <c r="B349" s="37"/>
       <c r="C349" s="35"/>
       <c r="D349" s="35"/>
       <c r="E349" s="35"/>
@@ -22738,8 +23468,8 @@
       </c>
     </row>
     <row r="350" ht="20.05" customHeight="1">
-      <c r="A350" s="36"/>
-      <c r="B350" s="34"/>
+      <c r="A350" s="33"/>
+      <c r="B350" s="37"/>
       <c r="C350" s="35"/>
       <c r="D350" s="35"/>
       <c r="E350" s="35"/>
@@ -22786,8 +23516,8 @@
       </c>
     </row>
     <row r="351" ht="20.05" customHeight="1">
-      <c r="A351" s="36"/>
-      <c r="B351" s="34"/>
+      <c r="A351" s="33"/>
+      <c r="B351" s="37"/>
       <c r="C351" s="35"/>
       <c r="D351" s="35"/>
       <c r="E351" s="35"/>
@@ -22834,8 +23564,8 @@
       </c>
     </row>
     <row r="352" ht="20.05" customHeight="1">
-      <c r="A352" s="36"/>
-      <c r="B352" s="34"/>
+      <c r="A352" s="33"/>
+      <c r="B352" s="37"/>
       <c r="C352" s="35"/>
       <c r="D352" s="35"/>
       <c r="E352" s="35"/>
@@ -22882,8 +23612,8 @@
       </c>
     </row>
     <row r="353" ht="20.05" customHeight="1">
-      <c r="A353" s="36"/>
-      <c r="B353" s="34"/>
+      <c r="A353" s="33"/>
+      <c r="B353" s="37"/>
       <c r="C353" s="35"/>
       <c r="D353" s="35"/>
       <c r="E353" s="35"/>
@@ -22930,8 +23660,8 @@
       </c>
     </row>
     <row r="354" ht="20.05" customHeight="1">
-      <c r="A354" s="36"/>
-      <c r="B354" s="34"/>
+      <c r="A354" s="33"/>
+      <c r="B354" s="37"/>
       <c r="C354" s="35"/>
       <c r="D354" s="35"/>
       <c r="E354" s="35"/>
@@ -22978,8 +23708,8 @@
       </c>
     </row>
     <row r="355" ht="20.05" customHeight="1">
-      <c r="A355" s="36"/>
-      <c r="B355" s="34"/>
+      <c r="A355" s="33"/>
+      <c r="B355" s="37"/>
       <c r="C355" s="35"/>
       <c r="D355" s="35"/>
       <c r="E355" s="35"/>
@@ -23026,8 +23756,8 @@
       </c>
     </row>
     <row r="356" ht="20.05" customHeight="1">
-      <c r="A356" s="36"/>
-      <c r="B356" s="34"/>
+      <c r="A356" s="33"/>
+      <c r="B356" s="37"/>
       <c r="C356" s="35"/>
       <c r="D356" s="35"/>
       <c r="E356" s="35"/>
@@ -23074,8 +23804,8 @@
       </c>
     </row>
     <row r="357" ht="20.05" customHeight="1">
-      <c r="A357" s="36"/>
-      <c r="B357" s="34"/>
+      <c r="A357" s="33"/>
+      <c r="B357" s="37"/>
       <c r="C357" s="35"/>
       <c r="D357" s="35"/>
       <c r="E357" s="35"/>
@@ -23122,8 +23852,8 @@
       </c>
     </row>
     <row r="358" ht="20.05" customHeight="1">
-      <c r="A358" s="36"/>
-      <c r="B358" s="34"/>
+      <c r="A358" s="33"/>
+      <c r="B358" s="37"/>
       <c r="C358" s="35"/>
       <c r="D358" s="35"/>
       <c r="E358" s="35"/>
@@ -23170,8 +23900,8 @@
       </c>
     </row>
     <row r="359" ht="20.05" customHeight="1">
-      <c r="A359" s="36"/>
-      <c r="B359" s="34"/>
+      <c r="A359" s="33"/>
+      <c r="B359" s="37"/>
       <c r="C359" s="35"/>
       <c r="D359" s="35"/>
       <c r="E359" s="35"/>
@@ -23218,8 +23948,8 @@
       </c>
     </row>
     <row r="360" ht="20.05" customHeight="1">
-      <c r="A360" s="36"/>
-      <c r="B360" s="34"/>
+      <c r="A360" s="33"/>
+      <c r="B360" s="37"/>
       <c r="C360" s="35"/>
       <c r="D360" s="35"/>
       <c r="E360" s="35"/>
@@ -23266,8 +23996,8 @@
       </c>
     </row>
     <row r="361" ht="20.05" customHeight="1">
-      <c r="A361" s="36"/>
-      <c r="B361" s="34"/>
+      <c r="A361" s="33"/>
+      <c r="B361" s="37"/>
       <c r="C361" s="35"/>
       <c r="D361" s="35"/>
       <c r="E361" s="35"/>
@@ -23314,8 +24044,8 @@
       </c>
     </row>
     <row r="362" ht="20.05" customHeight="1">
-      <c r="A362" s="36"/>
-      <c r="B362" s="34"/>
+      <c r="A362" s="33"/>
+      <c r="B362" s="37"/>
       <c r="C362" s="35"/>
       <c r="D362" s="35"/>
       <c r="E362" s="35"/>
@@ -23362,8 +24092,8 @@
       </c>
     </row>
     <row r="363" ht="20.05" customHeight="1">
-      <c r="A363" s="36"/>
-      <c r="B363" s="34"/>
+      <c r="A363" s="33"/>
+      <c r="B363" s="37"/>
       <c r="C363" s="35"/>
       <c r="D363" s="35"/>
       <c r="E363" s="35"/>
@@ -23410,8 +24140,8 @@
       </c>
     </row>
     <row r="364" ht="20.05" customHeight="1">
-      <c r="A364" s="36"/>
-      <c r="B364" s="34"/>
+      <c r="A364" s="33"/>
+      <c r="B364" s="37"/>
       <c r="C364" s="35"/>
       <c r="D364" s="35"/>
       <c r="E364" s="35"/>
@@ -23458,8 +24188,8 @@
       </c>
     </row>
     <row r="365" ht="20.05" customHeight="1">
-      <c r="A365" s="36"/>
-      <c r="B365" s="34"/>
+      <c r="A365" s="33"/>
+      <c r="B365" s="37"/>
       <c r="C365" s="35"/>
       <c r="D365" s="35"/>
       <c r="E365" s="35"/>
@@ -23506,8 +24236,8 @@
       </c>
     </row>
     <row r="366" ht="20.05" customHeight="1">
-      <c r="A366" s="36"/>
-      <c r="B366" s="34"/>
+      <c r="A366" s="33"/>
+      <c r="B366" s="37"/>
       <c r="C366" s="35"/>
       <c r="D366" s="35"/>
       <c r="E366" s="35"/>
@@ -23554,8 +24284,8 @@
       </c>
     </row>
     <row r="367" ht="20.05" customHeight="1">
-      <c r="A367" s="36"/>
-      <c r="B367" s="34"/>
+      <c r="A367" s="33"/>
+      <c r="B367" s="37"/>
       <c r="C367" s="35"/>
       <c r="D367" s="35"/>
       <c r="E367" s="35"/>
@@ -23602,8 +24332,8 @@
       </c>
     </row>
     <row r="368" ht="20.05" customHeight="1">
-      <c r="A368" s="36"/>
-      <c r="B368" s="34"/>
+      <c r="A368" s="33"/>
+      <c r="B368" s="37"/>
       <c r="C368" s="35"/>
       <c r="D368" s="35"/>
       <c r="E368" s="35"/>
@@ -23650,8 +24380,8 @@
       </c>
     </row>
     <row r="369" ht="20.05" customHeight="1">
-      <c r="A369" s="36"/>
-      <c r="B369" s="34"/>
+      <c r="A369" s="33"/>
+      <c r="B369" s="37"/>
       <c r="C369" s="35"/>
       <c r="D369" s="35"/>
       <c r="E369" s="35"/>
@@ -23698,8 +24428,8 @@
       </c>
     </row>
     <row r="370" ht="20.05" customHeight="1">
-      <c r="A370" s="36"/>
-      <c r="B370" s="34"/>
+      <c r="A370" s="33"/>
+      <c r="B370" s="37"/>
       <c r="C370" s="35"/>
       <c r="D370" s="35"/>
       <c r="E370" s="35"/>
@@ -23746,8 +24476,8 @@
       </c>
     </row>
     <row r="371" ht="20.05" customHeight="1">
-      <c r="A371" s="36"/>
-      <c r="B371" s="34"/>
+      <c r="A371" s="33"/>
+      <c r="B371" s="37"/>
       <c r="C371" s="35"/>
       <c r="D371" s="35"/>
       <c r="E371" s="35"/>
@@ -23794,8 +24524,8 @@
       </c>
     </row>
     <row r="372" ht="20.05" customHeight="1">
-      <c r="A372" s="36"/>
-      <c r="B372" s="34"/>
+      <c r="A372" s="33"/>
+      <c r="B372" s="37"/>
       <c r="C372" s="35"/>
       <c r="D372" s="35"/>
       <c r="E372" s="35"/>
@@ -23842,8 +24572,8 @@
       </c>
     </row>
     <row r="373" ht="20.05" customHeight="1">
-      <c r="A373" s="36"/>
-      <c r="B373" s="34"/>
+      <c r="A373" s="33"/>
+      <c r="B373" s="37"/>
       <c r="C373" s="35"/>
       <c r="D373" s="35"/>
       <c r="E373" s="35"/>
@@ -23890,8 +24620,8 @@
       </c>
     </row>
     <row r="374" ht="20.05" customHeight="1">
-      <c r="A374" s="36"/>
-      <c r="B374" s="34"/>
+      <c r="A374" s="33"/>
+      <c r="B374" s="37"/>
       <c r="C374" s="35"/>
       <c r="D374" s="35"/>
       <c r="E374" s="35"/>
@@ -23938,8 +24668,8 @@
       </c>
     </row>
     <row r="375" ht="20.05" customHeight="1">
-      <c r="A375" s="36"/>
-      <c r="B375" s="34"/>
+      <c r="A375" s="33"/>
+      <c r="B375" s="37"/>
       <c r="C375" s="35"/>
       <c r="D375" s="35"/>
       <c r="E375" s="35"/>
@@ -23986,8 +24716,8 @@
       </c>
     </row>
     <row r="376" ht="20.05" customHeight="1">
-      <c r="A376" s="36"/>
-      <c r="B376" s="34"/>
+      <c r="A376" s="33"/>
+      <c r="B376" s="37"/>
       <c r="C376" s="35"/>
       <c r="D376" s="35"/>
       <c r="E376" s="35"/>
@@ -24034,8 +24764,8 @@
       </c>
     </row>
     <row r="377" ht="20.05" customHeight="1">
-      <c r="A377" s="36"/>
-      <c r="B377" s="34"/>
+      <c r="A377" s="33"/>
+      <c r="B377" s="37"/>
       <c r="C377" s="35"/>
       <c r="D377" s="35"/>
       <c r="E377" s="35"/>
@@ -24082,8 +24812,8 @@
       </c>
     </row>
     <row r="378" ht="20.05" customHeight="1">
-      <c r="A378" s="36"/>
-      <c r="B378" s="34"/>
+      <c r="A378" s="33"/>
+      <c r="B378" s="37"/>
       <c r="C378" s="35"/>
       <c r="D378" s="35"/>
       <c r="E378" s="35"/>
@@ -24130,8 +24860,8 @@
       </c>
     </row>
     <row r="379" ht="20.05" customHeight="1">
-      <c r="A379" s="36"/>
-      <c r="B379" s="34"/>
+      <c r="A379" s="33"/>
+      <c r="B379" s="37"/>
       <c r="C379" s="35"/>
       <c r="D379" s="35"/>
       <c r="E379" s="35"/>
@@ -24178,8 +24908,8 @@
       </c>
     </row>
     <row r="380" ht="20.05" customHeight="1">
-      <c r="A380" s="36"/>
-      <c r="B380" s="34"/>
+      <c r="A380" s="33"/>
+      <c r="B380" s="37"/>
       <c r="C380" s="35"/>
       <c r="D380" s="35"/>
       <c r="E380" s="35"/>
@@ -24226,8 +24956,8 @@
       </c>
     </row>
     <row r="381" ht="20.05" customHeight="1">
-      <c r="A381" s="36"/>
-      <c r="B381" s="34"/>
+      <c r="A381" s="33"/>
+      <c r="B381" s="37"/>
       <c r="C381" s="35"/>
       <c r="D381" s="35"/>
       <c r="E381" s="35"/>
@@ -24274,8 +25004,8 @@
       </c>
     </row>
     <row r="382" ht="20.05" customHeight="1">
-      <c r="A382" s="36"/>
-      <c r="B382" s="34"/>
+      <c r="A382" s="33"/>
+      <c r="B382" s="37"/>
       <c r="C382" s="35"/>
       <c r="D382" s="35"/>
       <c r="E382" s="35"/>
@@ -24322,8 +25052,8 @@
       </c>
     </row>
     <row r="383" ht="20.05" customHeight="1">
-      <c r="A383" s="36"/>
-      <c r="B383" s="34"/>
+      <c r="A383" s="33"/>
+      <c r="B383" s="37"/>
       <c r="C383" s="35"/>
       <c r="D383" s="35"/>
       <c r="E383" s="35"/>
@@ -24370,8 +25100,8 @@
       </c>
     </row>
     <row r="384" ht="20.05" customHeight="1">
-      <c r="A384" s="36"/>
-      <c r="B384" s="34"/>
+      <c r="A384" s="33"/>
+      <c r="B384" s="37"/>
       <c r="C384" s="35"/>
       <c r="D384" s="35"/>
       <c r="E384" s="35"/>
@@ -24418,8 +25148,8 @@
       </c>
     </row>
     <row r="385" ht="20.05" customHeight="1">
-      <c r="A385" s="36"/>
-      <c r="B385" s="34"/>
+      <c r="A385" s="33"/>
+      <c r="B385" s="37"/>
       <c r="C385" s="35"/>
       <c r="D385" s="35"/>
       <c r="E385" s="35"/>
@@ -24466,8 +25196,8 @@
       </c>
     </row>
     <row r="386" ht="20.05" customHeight="1">
-      <c r="A386" s="36"/>
-      <c r="B386" s="34"/>
+      <c r="A386" s="33"/>
+      <c r="B386" s="37"/>
       <c r="C386" s="35"/>
       <c r="D386" s="35"/>
       <c r="E386" s="35"/>
@@ -24514,8 +25244,8 @@
       </c>
     </row>
     <row r="387" ht="20.05" customHeight="1">
-      <c r="A387" s="36"/>
-      <c r="B387" s="34"/>
+      <c r="A387" s="33"/>
+      <c r="B387" s="37"/>
       <c r="C387" s="35"/>
       <c r="D387" s="35"/>
       <c r="E387" s="35"/>
@@ -24562,8 +25292,8 @@
       </c>
     </row>
     <row r="388" ht="20.05" customHeight="1">
-      <c r="A388" s="36"/>
-      <c r="B388" s="34"/>
+      <c r="A388" s="33"/>
+      <c r="B388" s="37"/>
       <c r="C388" s="35"/>
       <c r="D388" s="35"/>
       <c r="E388" s="35"/>
@@ -24610,8 +25340,8 @@
       </c>
     </row>
     <row r="389" ht="20.05" customHeight="1">
-      <c r="A389" s="36"/>
-      <c r="B389" s="34"/>
+      <c r="A389" s="33"/>
+      <c r="B389" s="37"/>
       <c r="C389" s="35"/>
       <c r="D389" s="35"/>
       <c r="E389" s="35"/>
@@ -24658,8 +25388,8 @@
       </c>
     </row>
     <row r="390" ht="20.05" customHeight="1">
-      <c r="A390" s="36"/>
-      <c r="B390" s="34"/>
+      <c r="A390" s="33"/>
+      <c r="B390" s="37"/>
       <c r="C390" s="35"/>
       <c r="D390" s="35"/>
       <c r="E390" s="35"/>
@@ -24706,8 +25436,8 @@
       </c>
     </row>
     <row r="391" ht="20.05" customHeight="1">
-      <c r="A391" s="36"/>
-      <c r="B391" s="34"/>
+      <c r="A391" s="33"/>
+      <c r="B391" s="37"/>
       <c r="C391" s="35"/>
       <c r="D391" s="35"/>
       <c r="E391" s="35"/>
@@ -24754,8 +25484,8 @@
       </c>
     </row>
     <row r="392" ht="20.05" customHeight="1">
-      <c r="A392" s="36"/>
-      <c r="B392" s="34"/>
+      <c r="A392" s="33"/>
+      <c r="B392" s="37"/>
       <c r="C392" s="35"/>
       <c r="D392" s="35"/>
       <c r="E392" s="35"/>
@@ -24802,8 +25532,8 @@
       </c>
     </row>
     <row r="393" ht="20.05" customHeight="1">
-      <c r="A393" s="36"/>
-      <c r="B393" s="34"/>
+      <c r="A393" s="33"/>
+      <c r="B393" s="37"/>
       <c r="C393" s="35"/>
       <c r="D393" s="35"/>
       <c r="E393" s="35"/>
@@ -24850,8 +25580,8 @@
       </c>
     </row>
     <row r="394" ht="20.05" customHeight="1">
-      <c r="A394" s="36"/>
-      <c r="B394" s="34"/>
+      <c r="A394" s="33"/>
+      <c r="B394" s="37"/>
       <c r="C394" s="35"/>
       <c r="D394" s="35"/>
       <c r="E394" s="35"/>
@@ -24898,8 +25628,8 @@
       </c>
     </row>
     <row r="395" ht="20.05" customHeight="1">
-      <c r="A395" s="36"/>
-      <c r="B395" s="34"/>
+      <c r="A395" s="33"/>
+      <c r="B395" s="37"/>
       <c r="C395" s="35"/>
       <c r="D395" s="35"/>
       <c r="E395" s="35"/>
@@ -24946,8 +25676,8 @@
       </c>
     </row>
     <row r="396" ht="20.05" customHeight="1">
-      <c r="A396" s="36"/>
-      <c r="B396" s="34"/>
+      <c r="A396" s="33"/>
+      <c r="B396" s="37"/>
       <c r="C396" s="35"/>
       <c r="D396" s="35"/>
       <c r="E396" s="35"/>
@@ -24994,8 +25724,8 @@
       </c>
     </row>
     <row r="397" ht="20.05" customHeight="1">
-      <c r="A397" s="36"/>
-      <c r="B397" s="34"/>
+      <c r="A397" s="33"/>
+      <c r="B397" s="37"/>
       <c r="C397" s="35"/>
       <c r="D397" s="35"/>
       <c r="E397" s="35"/>
@@ -25042,8 +25772,8 @@
       </c>
     </row>
     <row r="398" ht="20.05" customHeight="1">
-      <c r="A398" s="36"/>
-      <c r="B398" s="34"/>
+      <c r="A398" s="33"/>
+      <c r="B398" s="37"/>
       <c r="C398" s="35"/>
       <c r="D398" s="35"/>
       <c r="E398" s="35"/>
@@ -25090,8 +25820,8 @@
       </c>
     </row>
     <row r="399" ht="20.05" customHeight="1">
-      <c r="A399" s="36"/>
-      <c r="B399" s="34"/>
+      <c r="A399" s="33"/>
+      <c r="B399" s="37"/>
       <c r="C399" s="35"/>
       <c r="D399" s="35"/>
       <c r="E399" s="35"/>
@@ -25138,8 +25868,8 @@
       </c>
     </row>
     <row r="400" ht="20.05" customHeight="1">
-      <c r="A400" s="36"/>
-      <c r="B400" s="34"/>
+      <c r="A400" s="33"/>
+      <c r="B400" s="37"/>
       <c r="C400" s="35"/>
       <c r="D400" s="35"/>
       <c r="E400" s="35"/>
@@ -25186,8 +25916,8 @@
       </c>
     </row>
     <row r="401" ht="20.05" customHeight="1">
-      <c r="A401" s="36"/>
-      <c r="B401" s="34"/>
+      <c r="A401" s="33"/>
+      <c r="B401" s="37"/>
       <c r="C401" s="35"/>
       <c r="D401" s="35"/>
       <c r="E401" s="35"/>
@@ -25234,8 +25964,8 @@
       </c>
     </row>
     <row r="402" ht="20.05" customHeight="1">
-      <c r="A402" s="36"/>
-      <c r="B402" s="34"/>
+      <c r="A402" s="33"/>
+      <c r="B402" s="37"/>
       <c r="C402" s="35"/>
       <c r="D402" s="35"/>
       <c r="E402" s="35"/>
@@ -25244,46 +25974,22 @@
       <c r="H402" s="35"/>
       <c r="I402" s="35"/>
       <c r="J402" s="35"/>
-      <c r="K402" s="17">
-        <v>0</v>
-      </c>
-      <c r="L402" s="18">
-        <v>0</v>
-      </c>
-      <c r="M402" s="18">
-        <v>0</v>
-      </c>
-      <c r="N402" s="18">
-        <v>0</v>
-      </c>
-      <c r="O402" s="18">
-        <v>0</v>
-      </c>
-      <c r="P402" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q402" s="18">
-        <v>0</v>
-      </c>
-      <c r="R402" s="18">
-        <v>0</v>
-      </c>
-      <c r="S402" s="18">
-        <v>0</v>
-      </c>
-      <c r="T402" s="18">
-        <v>0</v>
-      </c>
-      <c r="U402" s="18">
-        <v>0</v>
-      </c>
-      <c r="V402" s="19">
-        <v>0</v>
-      </c>
+      <c r="K402" s="38"/>
+      <c r="L402" s="39"/>
+      <c r="M402" s="39"/>
+      <c r="N402" s="39"/>
+      <c r="O402" s="39"/>
+      <c r="P402" s="39"/>
+      <c r="Q402" s="39"/>
+      <c r="R402" s="39"/>
+      <c r="S402" s="39"/>
+      <c r="T402" s="39"/>
+      <c r="U402" s="39"/>
+      <c r="V402" s="40"/>
     </row>
     <row r="403" ht="20.05" customHeight="1">
-      <c r="A403" s="36"/>
-      <c r="B403" s="34"/>
+      <c r="A403" s="33"/>
+      <c r="B403" s="37"/>
       <c r="C403" s="35"/>
       <c r="D403" s="35"/>
       <c r="E403" s="35"/>
@@ -25292,46 +25998,22 @@
       <c r="H403" s="35"/>
       <c r="I403" s="35"/>
       <c r="J403" s="35"/>
-      <c r="K403" s="17">
-        <v>0</v>
-      </c>
-      <c r="L403" s="18">
-        <v>0</v>
-      </c>
-      <c r="M403" s="18">
-        <v>0</v>
-      </c>
-      <c r="N403" s="18">
-        <v>0</v>
-      </c>
-      <c r="O403" s="18">
-        <v>0</v>
-      </c>
-      <c r="P403" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q403" s="18">
-        <v>0</v>
-      </c>
-      <c r="R403" s="18">
-        <v>0</v>
-      </c>
-      <c r="S403" s="18">
-        <v>0</v>
-      </c>
-      <c r="T403" s="18">
-        <v>0</v>
-      </c>
-      <c r="U403" s="18">
-        <v>0</v>
-      </c>
-      <c r="V403" s="19">
-        <v>0</v>
-      </c>
+      <c r="K403" s="38"/>
+      <c r="L403" s="39"/>
+      <c r="M403" s="39"/>
+      <c r="N403" s="39"/>
+      <c r="O403" s="39"/>
+      <c r="P403" s="39"/>
+      <c r="Q403" s="39"/>
+      <c r="R403" s="39"/>
+      <c r="S403" s="39"/>
+      <c r="T403" s="39"/>
+      <c r="U403" s="39"/>
+      <c r="V403" s="40"/>
     </row>
     <row r="404" ht="20.05" customHeight="1">
-      <c r="A404" s="36"/>
-      <c r="B404" s="34"/>
+      <c r="A404" s="33"/>
+      <c r="B404" s="37"/>
       <c r="C404" s="35"/>
       <c r="D404" s="35"/>
       <c r="E404" s="35"/>
@@ -25340,46 +26022,22 @@
       <c r="H404" s="35"/>
       <c r="I404" s="35"/>
       <c r="J404" s="35"/>
-      <c r="K404" s="17">
-        <v>0</v>
-      </c>
-      <c r="L404" s="18">
-        <v>0</v>
-      </c>
-      <c r="M404" s="18">
-        <v>0</v>
-      </c>
-      <c r="N404" s="18">
-        <v>0</v>
-      </c>
-      <c r="O404" s="18">
-        <v>0</v>
-      </c>
-      <c r="P404" s="18">
-        <v>0</v>
-      </c>
-      <c r="Q404" s="18">
-        <v>0</v>
-      </c>
-      <c r="R404" s="18">
-        <v>0</v>
-      </c>
-      <c r="S404" s="18">
-        <v>0</v>
-      </c>
-      <c r="T404" s="18">
-        <v>0</v>
-      </c>
-      <c r="U404" s="18">
-        <v>0</v>
-      </c>
-      <c r="V404" s="19">
-        <v>0</v>
-      </c>
+      <c r="K404" s="38"/>
+      <c r="L404" s="39"/>
+      <c r="M404" s="39"/>
+      <c r="N404" s="39"/>
+      <c r="O404" s="39"/>
+      <c r="P404" s="39"/>
+      <c r="Q404" s="39"/>
+      <c r="R404" s="39"/>
+      <c r="S404" s="39"/>
+      <c r="T404" s="39"/>
+      <c r="U404" s="39"/>
+      <c r="V404" s="40"/>
     </row>
     <row r="405" ht="20.05" customHeight="1">
-      <c r="A405" s="36"/>
-      <c r="B405" s="34"/>
+      <c r="A405" s="33"/>
+      <c r="B405" s="37"/>
       <c r="C405" s="35"/>
       <c r="D405" s="35"/>
       <c r="E405" s="35"/>
@@ -25388,22 +26046,22 @@
       <c r="H405" s="35"/>
       <c r="I405" s="35"/>
       <c r="J405" s="35"/>
-      <c r="K405" s="37"/>
-      <c r="L405" s="38"/>
-      <c r="M405" s="38"/>
-      <c r="N405" s="38"/>
-      <c r="O405" s="38"/>
-      <c r="P405" s="38"/>
-      <c r="Q405" s="38"/>
-      <c r="R405" s="38"/>
-      <c r="S405" s="38"/>
-      <c r="T405" s="38"/>
-      <c r="U405" s="38"/>
-      <c r="V405" s="39"/>
+      <c r="K405" s="38"/>
+      <c r="L405" s="39"/>
+      <c r="M405" s="39"/>
+      <c r="N405" s="39"/>
+      <c r="O405" s="39"/>
+      <c r="P405" s="39"/>
+      <c r="Q405" s="39"/>
+      <c r="R405" s="39"/>
+      <c r="S405" s="39"/>
+      <c r="T405" s="39"/>
+      <c r="U405" s="39"/>
+      <c r="V405" s="40"/>
     </row>
     <row r="406" ht="20.05" customHeight="1">
-      <c r="A406" s="36"/>
-      <c r="B406" s="34"/>
+      <c r="A406" s="33"/>
+      <c r="B406" s="37"/>
       <c r="C406" s="35"/>
       <c r="D406" s="35"/>
       <c r="E406" s="35"/>
@@ -25412,22 +26070,22 @@
       <c r="H406" s="35"/>
       <c r="I406" s="35"/>
       <c r="J406" s="35"/>
-      <c r="K406" s="37"/>
-      <c r="L406" s="38"/>
-      <c r="M406" s="38"/>
-      <c r="N406" s="38"/>
-      <c r="O406" s="38"/>
-      <c r="P406" s="38"/>
-      <c r="Q406" s="38"/>
-      <c r="R406" s="38"/>
-      <c r="S406" s="38"/>
-      <c r="T406" s="38"/>
-      <c r="U406" s="38"/>
-      <c r="V406" s="39"/>
+      <c r="K406" s="38"/>
+      <c r="L406" s="39"/>
+      <c r="M406" s="39"/>
+      <c r="N406" s="39"/>
+      <c r="O406" s="39"/>
+      <c r="P406" s="39"/>
+      <c r="Q406" s="39"/>
+      <c r="R406" s="39"/>
+      <c r="S406" s="39"/>
+      <c r="T406" s="39"/>
+      <c r="U406" s="39"/>
+      <c r="V406" s="40"/>
     </row>
     <row r="407" ht="20.05" customHeight="1">
-      <c r="A407" s="36"/>
-      <c r="B407" s="34"/>
+      <c r="A407" s="33"/>
+      <c r="B407" s="37"/>
       <c r="C407" s="35"/>
       <c r="D407" s="35"/>
       <c r="E407" s="35"/>
@@ -25436,22 +26094,22 @@
       <c r="H407" s="35"/>
       <c r="I407" s="35"/>
       <c r="J407" s="35"/>
-      <c r="K407" s="37"/>
-      <c r="L407" s="38"/>
-      <c r="M407" s="38"/>
-      <c r="N407" s="38"/>
-      <c r="O407" s="38"/>
-      <c r="P407" s="38"/>
-      <c r="Q407" s="38"/>
-      <c r="R407" s="38"/>
-      <c r="S407" s="38"/>
-      <c r="T407" s="38"/>
-      <c r="U407" s="38"/>
-      <c r="V407" s="39"/>
+      <c r="K407" s="38"/>
+      <c r="L407" s="39"/>
+      <c r="M407" s="39"/>
+      <c r="N407" s="39"/>
+      <c r="O407" s="39"/>
+      <c r="P407" s="39"/>
+      <c r="Q407" s="39"/>
+      <c r="R407" s="39"/>
+      <c r="S407" s="39"/>
+      <c r="T407" s="39"/>
+      <c r="U407" s="39"/>
+      <c r="V407" s="40"/>
     </row>
     <row r="408" ht="20.05" customHeight="1">
-      <c r="A408" s="36"/>
-      <c r="B408" s="34"/>
+      <c r="A408" s="33"/>
+      <c r="B408" s="37"/>
       <c r="C408" s="35"/>
       <c r="D408" s="35"/>
       <c r="E408" s="35"/>
@@ -25460,22 +26118,22 @@
       <c r="H408" s="35"/>
       <c r="I408" s="35"/>
       <c r="J408" s="35"/>
-      <c r="K408" s="37"/>
-      <c r="L408" s="38"/>
-      <c r="M408" s="38"/>
-      <c r="N408" s="38"/>
-      <c r="O408" s="38"/>
-      <c r="P408" s="38"/>
-      <c r="Q408" s="38"/>
-      <c r="R408" s="38"/>
-      <c r="S408" s="38"/>
-      <c r="T408" s="38"/>
-      <c r="U408" s="38"/>
-      <c r="V408" s="39"/>
+      <c r="K408" s="38"/>
+      <c r="L408" s="39"/>
+      <c r="M408" s="39"/>
+      <c r="N408" s="39"/>
+      <c r="O408" s="39"/>
+      <c r="P408" s="39"/>
+      <c r="Q408" s="39"/>
+      <c r="R408" s="39"/>
+      <c r="S408" s="39"/>
+      <c r="T408" s="39"/>
+      <c r="U408" s="39"/>
+      <c r="V408" s="40"/>
     </row>
     <row r="409" ht="20.05" customHeight="1">
-      <c r="A409" s="36"/>
-      <c r="B409" s="34"/>
+      <c r="A409" s="33"/>
+      <c r="B409" s="37"/>
       <c r="C409" s="35"/>
       <c r="D409" s="35"/>
       <c r="E409" s="35"/>
@@ -25484,22 +26142,22 @@
       <c r="H409" s="35"/>
       <c r="I409" s="35"/>
       <c r="J409" s="35"/>
-      <c r="K409" s="37"/>
-      <c r="L409" s="38"/>
-      <c r="M409" s="38"/>
-      <c r="N409" s="38"/>
-      <c r="O409" s="38"/>
-      <c r="P409" s="38"/>
-      <c r="Q409" s="38"/>
-      <c r="R409" s="38"/>
-      <c r="S409" s="38"/>
-      <c r="T409" s="38"/>
-      <c r="U409" s="38"/>
-      <c r="V409" s="39"/>
+      <c r="K409" s="38"/>
+      <c r="L409" s="39"/>
+      <c r="M409" s="39"/>
+      <c r="N409" s="39"/>
+      <c r="O409" s="39"/>
+      <c r="P409" s="39"/>
+      <c r="Q409" s="39"/>
+      <c r="R409" s="39"/>
+      <c r="S409" s="39"/>
+      <c r="T409" s="39"/>
+      <c r="U409" s="39"/>
+      <c r="V409" s="40"/>
     </row>
     <row r="410" ht="20.05" customHeight="1">
-      <c r="A410" s="36"/>
-      <c r="B410" s="34"/>
+      <c r="A410" s="33"/>
+      <c r="B410" s="37"/>
       <c r="C410" s="35"/>
       <c r="D410" s="35"/>
       <c r="E410" s="35"/>
@@ -25508,22 +26166,22 @@
       <c r="H410" s="35"/>
       <c r="I410" s="35"/>
       <c r="J410" s="35"/>
-      <c r="K410" s="37"/>
-      <c r="L410" s="38"/>
-      <c r="M410" s="38"/>
-      <c r="N410" s="38"/>
-      <c r="O410" s="38"/>
-      <c r="P410" s="38"/>
-      <c r="Q410" s="38"/>
-      <c r="R410" s="38"/>
-      <c r="S410" s="38"/>
-      <c r="T410" s="38"/>
-      <c r="U410" s="38"/>
-      <c r="V410" s="39"/>
+      <c r="K410" s="38"/>
+      <c r="L410" s="39"/>
+      <c r="M410" s="39"/>
+      <c r="N410" s="39"/>
+      <c r="O410" s="39"/>
+      <c r="P410" s="39"/>
+      <c r="Q410" s="39"/>
+      <c r="R410" s="39"/>
+      <c r="S410" s="39"/>
+      <c r="T410" s="39"/>
+      <c r="U410" s="39"/>
+      <c r="V410" s="40"/>
     </row>
     <row r="411" ht="20.05" customHeight="1">
-      <c r="A411" s="36"/>
-      <c r="B411" s="34"/>
+      <c r="A411" s="33"/>
+      <c r="B411" s="37"/>
       <c r="C411" s="35"/>
       <c r="D411" s="35"/>
       <c r="E411" s="35"/>
@@ -25532,22 +26190,22 @@
       <c r="H411" s="35"/>
       <c r="I411" s="35"/>
       <c r="J411" s="35"/>
-      <c r="K411" s="37"/>
-      <c r="L411" s="38"/>
-      <c r="M411" s="38"/>
-      <c r="N411" s="38"/>
-      <c r="O411" s="38"/>
-      <c r="P411" s="38"/>
-      <c r="Q411" s="38"/>
-      <c r="R411" s="38"/>
-      <c r="S411" s="38"/>
-      <c r="T411" s="38"/>
-      <c r="U411" s="38"/>
-      <c r="V411" s="39"/>
+      <c r="K411" s="38"/>
+      <c r="L411" s="39"/>
+      <c r="M411" s="39"/>
+      <c r="N411" s="39"/>
+      <c r="O411" s="39"/>
+      <c r="P411" s="39"/>
+      <c r="Q411" s="39"/>
+      <c r="R411" s="39"/>
+      <c r="S411" s="39"/>
+      <c r="T411" s="39"/>
+      <c r="U411" s="39"/>
+      <c r="V411" s="40"/>
     </row>
     <row r="412" ht="20.05" customHeight="1">
-      <c r="A412" s="36"/>
-      <c r="B412" s="34"/>
+      <c r="A412" s="33"/>
+      <c r="B412" s="37"/>
       <c r="C412" s="35"/>
       <c r="D412" s="35"/>
       <c r="E412" s="35"/>
@@ -25556,22 +26214,22 @@
       <c r="H412" s="35"/>
       <c r="I412" s="35"/>
       <c r="J412" s="35"/>
-      <c r="K412" s="37"/>
-      <c r="L412" s="38"/>
-      <c r="M412" s="38"/>
-      <c r="N412" s="38"/>
-      <c r="O412" s="38"/>
-      <c r="P412" s="38"/>
-      <c r="Q412" s="38"/>
-      <c r="R412" s="38"/>
-      <c r="S412" s="38"/>
-      <c r="T412" s="38"/>
-      <c r="U412" s="38"/>
-      <c r="V412" s="39"/>
+      <c r="K412" s="38"/>
+      <c r="L412" s="39"/>
+      <c r="M412" s="39"/>
+      <c r="N412" s="39"/>
+      <c r="O412" s="39"/>
+      <c r="P412" s="39"/>
+      <c r="Q412" s="39"/>
+      <c r="R412" s="39"/>
+      <c r="S412" s="39"/>
+      <c r="T412" s="39"/>
+      <c r="U412" s="39"/>
+      <c r="V412" s="40"/>
     </row>
     <row r="413" ht="20.05" customHeight="1">
-      <c r="A413" s="36"/>
-      <c r="B413" s="34"/>
+      <c r="A413" s="33"/>
+      <c r="B413" s="37"/>
       <c r="C413" s="35"/>
       <c r="D413" s="35"/>
       <c r="E413" s="35"/>
@@ -25580,22 +26238,22 @@
       <c r="H413" s="35"/>
       <c r="I413" s="35"/>
       <c r="J413" s="35"/>
-      <c r="K413" s="37"/>
-      <c r="L413" s="38"/>
-      <c r="M413" s="38"/>
-      <c r="N413" s="38"/>
-      <c r="O413" s="38"/>
-      <c r="P413" s="38"/>
-      <c r="Q413" s="38"/>
-      <c r="R413" s="38"/>
-      <c r="S413" s="38"/>
-      <c r="T413" s="38"/>
-      <c r="U413" s="38"/>
-      <c r="V413" s="39"/>
+      <c r="K413" s="38"/>
+      <c r="L413" s="39"/>
+      <c r="M413" s="39"/>
+      <c r="N413" s="39"/>
+      <c r="O413" s="39"/>
+      <c r="P413" s="39"/>
+      <c r="Q413" s="39"/>
+      <c r="R413" s="39"/>
+      <c r="S413" s="39"/>
+      <c r="T413" s="39"/>
+      <c r="U413" s="39"/>
+      <c r="V413" s="40"/>
     </row>
     <row r="414" ht="20.05" customHeight="1">
-      <c r="A414" s="36"/>
-      <c r="B414" s="34"/>
+      <c r="A414" s="33"/>
+      <c r="B414" s="37"/>
       <c r="C414" s="35"/>
       <c r="D414" s="35"/>
       <c r="E414" s="35"/>
@@ -25604,22 +26262,22 @@
       <c r="H414" s="35"/>
       <c r="I414" s="35"/>
       <c r="J414" s="35"/>
-      <c r="K414" s="37"/>
-      <c r="L414" s="38"/>
-      <c r="M414" s="38"/>
-      <c r="N414" s="38"/>
-      <c r="O414" s="38"/>
-      <c r="P414" s="38"/>
-      <c r="Q414" s="38"/>
-      <c r="R414" s="38"/>
-      <c r="S414" s="38"/>
-      <c r="T414" s="38"/>
-      <c r="U414" s="38"/>
-      <c r="V414" s="39"/>
+      <c r="K414" s="38"/>
+      <c r="L414" s="39"/>
+      <c r="M414" s="39"/>
+      <c r="N414" s="39"/>
+      <c r="O414" s="39"/>
+      <c r="P414" s="39"/>
+      <c r="Q414" s="39"/>
+      <c r="R414" s="39"/>
+      <c r="S414" s="39"/>
+      <c r="T414" s="39"/>
+      <c r="U414" s="39"/>
+      <c r="V414" s="40"/>
     </row>
     <row r="415" ht="20.05" customHeight="1">
-      <c r="A415" s="36"/>
-      <c r="B415" s="34"/>
+      <c r="A415" s="33"/>
+      <c r="B415" s="37"/>
       <c r="C415" s="35"/>
       <c r="D415" s="35"/>
       <c r="E415" s="35"/>
@@ -25628,22 +26286,22 @@
       <c r="H415" s="35"/>
       <c r="I415" s="35"/>
       <c r="J415" s="35"/>
-      <c r="K415" s="37"/>
-      <c r="L415" s="38"/>
-      <c r="M415" s="38"/>
-      <c r="N415" s="38"/>
-      <c r="O415" s="38"/>
-      <c r="P415" s="38"/>
-      <c r="Q415" s="38"/>
-      <c r="R415" s="38"/>
-      <c r="S415" s="38"/>
-      <c r="T415" s="38"/>
-      <c r="U415" s="38"/>
-      <c r="V415" s="39"/>
+      <c r="K415" s="38"/>
+      <c r="L415" s="39"/>
+      <c r="M415" s="39"/>
+      <c r="N415" s="39"/>
+      <c r="O415" s="39"/>
+      <c r="P415" s="39"/>
+      <c r="Q415" s="39"/>
+      <c r="R415" s="39"/>
+      <c r="S415" s="39"/>
+      <c r="T415" s="39"/>
+      <c r="U415" s="39"/>
+      <c r="V415" s="40"/>
     </row>
     <row r="416" ht="20.05" customHeight="1">
-      <c r="A416" s="36"/>
-      <c r="B416" s="34"/>
+      <c r="A416" s="33"/>
+      <c r="B416" s="37"/>
       <c r="C416" s="35"/>
       <c r="D416" s="35"/>
       <c r="E416" s="35"/>
@@ -25652,22 +26310,22 @@
       <c r="H416" s="35"/>
       <c r="I416" s="35"/>
       <c r="J416" s="35"/>
-      <c r="K416" s="37"/>
-      <c r="L416" s="38"/>
-      <c r="M416" s="38"/>
-      <c r="N416" s="38"/>
-      <c r="O416" s="38"/>
-      <c r="P416" s="38"/>
-      <c r="Q416" s="38"/>
-      <c r="R416" s="38"/>
-      <c r="S416" s="38"/>
-      <c r="T416" s="38"/>
-      <c r="U416" s="38"/>
-      <c r="V416" s="39"/>
+      <c r="K416" s="38"/>
+      <c r="L416" s="39"/>
+      <c r="M416" s="39"/>
+      <c r="N416" s="39"/>
+      <c r="O416" s="39"/>
+      <c r="P416" s="39"/>
+      <c r="Q416" s="39"/>
+      <c r="R416" s="39"/>
+      <c r="S416" s="39"/>
+      <c r="T416" s="39"/>
+      <c r="U416" s="39"/>
+      <c r="V416" s="40"/>
     </row>
     <row r="417" ht="20.05" customHeight="1">
-      <c r="A417" s="36"/>
-      <c r="B417" s="34"/>
+      <c r="A417" s="33"/>
+      <c r="B417" s="37"/>
       <c r="C417" s="35"/>
       <c r="D417" s="35"/>
       <c r="E417" s="35"/>
@@ -25676,22 +26334,22 @@
       <c r="H417" s="35"/>
       <c r="I417" s="35"/>
       <c r="J417" s="35"/>
-      <c r="K417" s="37"/>
-      <c r="L417" s="38"/>
-      <c r="M417" s="38"/>
-      <c r="N417" s="38"/>
-      <c r="O417" s="38"/>
-      <c r="P417" s="38"/>
-      <c r="Q417" s="38"/>
-      <c r="R417" s="38"/>
-      <c r="S417" s="38"/>
-      <c r="T417" s="38"/>
-      <c r="U417" s="38"/>
-      <c r="V417" s="39"/>
+      <c r="K417" s="38"/>
+      <c r="L417" s="39"/>
+      <c r="M417" s="39"/>
+      <c r="N417" s="39"/>
+      <c r="O417" s="39"/>
+      <c r="P417" s="39"/>
+      <c r="Q417" s="39"/>
+      <c r="R417" s="39"/>
+      <c r="S417" s="39"/>
+      <c r="T417" s="39"/>
+      <c r="U417" s="39"/>
+      <c r="V417" s="40"/>
     </row>
     <row r="418" ht="20.05" customHeight="1">
-      <c r="A418" s="36"/>
-      <c r="B418" s="34"/>
+      <c r="A418" s="33"/>
+      <c r="B418" s="37"/>
       <c r="C418" s="35"/>
       <c r="D418" s="35"/>
       <c r="E418" s="35"/>
@@ -25700,22 +26358,22 @@
       <c r="H418" s="35"/>
       <c r="I418" s="35"/>
       <c r="J418" s="35"/>
-      <c r="K418" s="37"/>
-      <c r="L418" s="38"/>
-      <c r="M418" s="38"/>
-      <c r="N418" s="38"/>
-      <c r="O418" s="38"/>
-      <c r="P418" s="38"/>
-      <c r="Q418" s="38"/>
-      <c r="R418" s="38"/>
-      <c r="S418" s="38"/>
-      <c r="T418" s="38"/>
-      <c r="U418" s="38"/>
-      <c r="V418" s="39"/>
+      <c r="K418" s="38"/>
+      <c r="L418" s="39"/>
+      <c r="M418" s="39"/>
+      <c r="N418" s="39"/>
+      <c r="O418" s="39"/>
+      <c r="P418" s="39"/>
+      <c r="Q418" s="39"/>
+      <c r="R418" s="39"/>
+      <c r="S418" s="39"/>
+      <c r="T418" s="39"/>
+      <c r="U418" s="39"/>
+      <c r="V418" s="40"/>
     </row>
     <row r="419" ht="20.05" customHeight="1">
-      <c r="A419" s="36"/>
-      <c r="B419" s="34"/>
+      <c r="A419" s="33"/>
+      <c r="B419" s="37"/>
       <c r="C419" s="35"/>
       <c r="D419" s="35"/>
       <c r="E419" s="35"/>
@@ -25724,22 +26382,22 @@
       <c r="H419" s="35"/>
       <c r="I419" s="35"/>
       <c r="J419" s="35"/>
-      <c r="K419" s="37"/>
-      <c r="L419" s="38"/>
-      <c r="M419" s="38"/>
-      <c r="N419" s="38"/>
-      <c r="O419" s="38"/>
-      <c r="P419" s="38"/>
-      <c r="Q419" s="38"/>
-      <c r="R419" s="38"/>
-      <c r="S419" s="38"/>
-      <c r="T419" s="38"/>
-      <c r="U419" s="38"/>
-      <c r="V419" s="39"/>
+      <c r="K419" s="38"/>
+      <c r="L419" s="39"/>
+      <c r="M419" s="39"/>
+      <c r="N419" s="39"/>
+      <c r="O419" s="39"/>
+      <c r="P419" s="39"/>
+      <c r="Q419" s="39"/>
+      <c r="R419" s="39"/>
+      <c r="S419" s="39"/>
+      <c r="T419" s="39"/>
+      <c r="U419" s="39"/>
+      <c r="V419" s="40"/>
     </row>
     <row r="420" ht="20.05" customHeight="1">
-      <c r="A420" s="36"/>
-      <c r="B420" s="34"/>
+      <c r="A420" s="33"/>
+      <c r="B420" s="37"/>
       <c r="C420" s="35"/>
       <c r="D420" s="35"/>
       <c r="E420" s="35"/>
@@ -25748,22 +26406,22 @@
       <c r="H420" s="35"/>
       <c r="I420" s="35"/>
       <c r="J420" s="35"/>
-      <c r="K420" s="37"/>
-      <c r="L420" s="38"/>
-      <c r="M420" s="38"/>
-      <c r="N420" s="38"/>
-      <c r="O420" s="38"/>
-      <c r="P420" s="38"/>
-      <c r="Q420" s="38"/>
-      <c r="R420" s="38"/>
-      <c r="S420" s="38"/>
-      <c r="T420" s="38"/>
-      <c r="U420" s="38"/>
-      <c r="V420" s="39"/>
+      <c r="K420" s="38"/>
+      <c r="L420" s="39"/>
+      <c r="M420" s="39"/>
+      <c r="N420" s="39"/>
+      <c r="O420" s="39"/>
+      <c r="P420" s="39"/>
+      <c r="Q420" s="39"/>
+      <c r="R420" s="39"/>
+      <c r="S420" s="39"/>
+      <c r="T420" s="39"/>
+      <c r="U420" s="39"/>
+      <c r="V420" s="40"/>
     </row>
     <row r="421" ht="20.05" customHeight="1">
-      <c r="A421" s="36"/>
-      <c r="B421" s="34"/>
+      <c r="A421" s="33"/>
+      <c r="B421" s="37"/>
       <c r="C421" s="35"/>
       <c r="D421" s="35"/>
       <c r="E421" s="35"/>
@@ -25772,22 +26430,22 @@
       <c r="H421" s="35"/>
       <c r="I421" s="35"/>
       <c r="J421" s="35"/>
-      <c r="K421" s="37"/>
-      <c r="L421" s="38"/>
-      <c r="M421" s="38"/>
-      <c r="N421" s="38"/>
-      <c r="O421" s="38"/>
-      <c r="P421" s="38"/>
-      <c r="Q421" s="38"/>
-      <c r="R421" s="38"/>
-      <c r="S421" s="38"/>
-      <c r="T421" s="38"/>
-      <c r="U421" s="38"/>
-      <c r="V421" s="39"/>
+      <c r="K421" s="38"/>
+      <c r="L421" s="39"/>
+      <c r="M421" s="39"/>
+      <c r="N421" s="39"/>
+      <c r="O421" s="39"/>
+      <c r="P421" s="39"/>
+      <c r="Q421" s="39"/>
+      <c r="R421" s="39"/>
+      <c r="S421" s="39"/>
+      <c r="T421" s="39"/>
+      <c r="U421" s="39"/>
+      <c r="V421" s="40"/>
     </row>
     <row r="422" ht="20.05" customHeight="1">
-      <c r="A422" s="36"/>
-      <c r="B422" s="34"/>
+      <c r="A422" s="33"/>
+      <c r="B422" s="37"/>
       <c r="C422" s="35"/>
       <c r="D422" s="35"/>
       <c r="E422" s="35"/>
@@ -25796,22 +26454,22 @@
       <c r="H422" s="35"/>
       <c r="I422" s="35"/>
       <c r="J422" s="35"/>
-      <c r="K422" s="37"/>
-      <c r="L422" s="38"/>
-      <c r="M422" s="38"/>
-      <c r="N422" s="38"/>
-      <c r="O422" s="38"/>
-      <c r="P422" s="38"/>
-      <c r="Q422" s="38"/>
-      <c r="R422" s="38"/>
-      <c r="S422" s="38"/>
-      <c r="T422" s="38"/>
-      <c r="U422" s="38"/>
-      <c r="V422" s="39"/>
+      <c r="K422" s="38"/>
+      <c r="L422" s="39"/>
+      <c r="M422" s="39"/>
+      <c r="N422" s="39"/>
+      <c r="O422" s="39"/>
+      <c r="P422" s="39"/>
+      <c r="Q422" s="39"/>
+      <c r="R422" s="39"/>
+      <c r="S422" s="39"/>
+      <c r="T422" s="39"/>
+      <c r="U422" s="39"/>
+      <c r="V422" s="40"/>
     </row>
     <row r="423" ht="20.05" customHeight="1">
-      <c r="A423" s="36"/>
-      <c r="B423" s="34"/>
+      <c r="A423" s="33"/>
+      <c r="B423" s="37"/>
       <c r="C423" s="35"/>
       <c r="D423" s="35"/>
       <c r="E423" s="35"/>
@@ -25820,22 +26478,22 @@
       <c r="H423" s="35"/>
       <c r="I423" s="35"/>
       <c r="J423" s="35"/>
-      <c r="K423" s="37"/>
-      <c r="L423" s="38"/>
-      <c r="M423" s="38"/>
-      <c r="N423" s="38"/>
-      <c r="O423" s="38"/>
-      <c r="P423" s="38"/>
-      <c r="Q423" s="38"/>
-      <c r="R423" s="38"/>
-      <c r="S423" s="38"/>
-      <c r="T423" s="38"/>
-      <c r="U423" s="38"/>
-      <c r="V423" s="39"/>
+      <c r="K423" s="38"/>
+      <c r="L423" s="39"/>
+      <c r="M423" s="39"/>
+      <c r="N423" s="39"/>
+      <c r="O423" s="39"/>
+      <c r="P423" s="39"/>
+      <c r="Q423" s="39"/>
+      <c r="R423" s="39"/>
+      <c r="S423" s="39"/>
+      <c r="T423" s="39"/>
+      <c r="U423" s="39"/>
+      <c r="V423" s="40"/>
     </row>
     <row r="424" ht="20.05" customHeight="1">
-      <c r="A424" s="36"/>
-      <c r="B424" s="34"/>
+      <c r="A424" s="33"/>
+      <c r="B424" s="37"/>
       <c r="C424" s="35"/>
       <c r="D424" s="35"/>
       <c r="E424" s="35"/>
@@ -25844,22 +26502,22 @@
       <c r="H424" s="35"/>
       <c r="I424" s="35"/>
       <c r="J424" s="35"/>
-      <c r="K424" s="37"/>
-      <c r="L424" s="38"/>
-      <c r="M424" s="38"/>
-      <c r="N424" s="38"/>
-      <c r="O424" s="38"/>
-      <c r="P424" s="38"/>
-      <c r="Q424" s="38"/>
-      <c r="R424" s="38"/>
-      <c r="S424" s="38"/>
-      <c r="T424" s="38"/>
-      <c r="U424" s="38"/>
-      <c r="V424" s="39"/>
+      <c r="K424" s="38"/>
+      <c r="L424" s="39"/>
+      <c r="M424" s="39"/>
+      <c r="N424" s="39"/>
+      <c r="O424" s="39"/>
+      <c r="P424" s="39"/>
+      <c r="Q424" s="39"/>
+      <c r="R424" s="39"/>
+      <c r="S424" s="39"/>
+      <c r="T424" s="39"/>
+      <c r="U424" s="39"/>
+      <c r="V424" s="40"/>
     </row>
     <row r="425" ht="20.05" customHeight="1">
-      <c r="A425" s="36"/>
-      <c r="B425" s="34"/>
+      <c r="A425" s="33"/>
+      <c r="B425" s="37"/>
       <c r="C425" s="35"/>
       <c r="D425" s="35"/>
       <c r="E425" s="35"/>
@@ -25868,22 +26526,22 @@
       <c r="H425" s="35"/>
       <c r="I425" s="35"/>
       <c r="J425" s="35"/>
-      <c r="K425" s="37"/>
-      <c r="L425" s="38"/>
-      <c r="M425" s="38"/>
-      <c r="N425" s="38"/>
-      <c r="O425" s="38"/>
-      <c r="P425" s="38"/>
-      <c r="Q425" s="38"/>
-      <c r="R425" s="38"/>
-      <c r="S425" s="38"/>
-      <c r="T425" s="38"/>
-      <c r="U425" s="38"/>
-      <c r="V425" s="39"/>
+      <c r="K425" s="38"/>
+      <c r="L425" s="39"/>
+      <c r="M425" s="39"/>
+      <c r="N425" s="39"/>
+      <c r="O425" s="39"/>
+      <c r="P425" s="39"/>
+      <c r="Q425" s="39"/>
+      <c r="R425" s="39"/>
+      <c r="S425" s="39"/>
+      <c r="T425" s="39"/>
+      <c r="U425" s="39"/>
+      <c r="V425" s="40"/>
     </row>
     <row r="426" ht="20.05" customHeight="1">
-      <c r="A426" s="36"/>
-      <c r="B426" s="34"/>
+      <c r="A426" s="33"/>
+      <c r="B426" s="37"/>
       <c r="C426" s="35"/>
       <c r="D426" s="35"/>
       <c r="E426" s="35"/>
@@ -25892,22 +26550,22 @@
       <c r="H426" s="35"/>
       <c r="I426" s="35"/>
       <c r="J426" s="35"/>
-      <c r="K426" s="37"/>
-      <c r="L426" s="38"/>
-      <c r="M426" s="38"/>
-      <c r="N426" s="38"/>
-      <c r="O426" s="38"/>
-      <c r="P426" s="38"/>
-      <c r="Q426" s="38"/>
-      <c r="R426" s="38"/>
-      <c r="S426" s="38"/>
-      <c r="T426" s="38"/>
-      <c r="U426" s="38"/>
-      <c r="V426" s="39"/>
+      <c r="K426" s="38"/>
+      <c r="L426" s="39"/>
+      <c r="M426" s="39"/>
+      <c r="N426" s="39"/>
+      <c r="O426" s="39"/>
+      <c r="P426" s="39"/>
+      <c r="Q426" s="39"/>
+      <c r="R426" s="39"/>
+      <c r="S426" s="39"/>
+      <c r="T426" s="39"/>
+      <c r="U426" s="39"/>
+      <c r="V426" s="40"/>
     </row>
     <row r="427" ht="20.05" customHeight="1">
-      <c r="A427" s="36"/>
-      <c r="B427" s="34"/>
+      <c r="A427" s="33"/>
+      <c r="B427" s="37"/>
       <c r="C427" s="35"/>
       <c r="D427" s="35"/>
       <c r="E427" s="35"/>
@@ -25916,22 +26574,22 @@
       <c r="H427" s="35"/>
       <c r="I427" s="35"/>
       <c r="J427" s="35"/>
-      <c r="K427" s="37"/>
-      <c r="L427" s="38"/>
-      <c r="M427" s="38"/>
-      <c r="N427" s="38"/>
-      <c r="O427" s="38"/>
-      <c r="P427" s="38"/>
-      <c r="Q427" s="38"/>
-      <c r="R427" s="38"/>
-      <c r="S427" s="38"/>
-      <c r="T427" s="38"/>
-      <c r="U427" s="38"/>
-      <c r="V427" s="39"/>
+      <c r="K427" s="38"/>
+      <c r="L427" s="39"/>
+      <c r="M427" s="39"/>
+      <c r="N427" s="39"/>
+      <c r="O427" s="39"/>
+      <c r="P427" s="39"/>
+      <c r="Q427" s="39"/>
+      <c r="R427" s="39"/>
+      <c r="S427" s="39"/>
+      <c r="T427" s="39"/>
+      <c r="U427" s="39"/>
+      <c r="V427" s="40"/>
     </row>
     <row r="428" ht="20.05" customHeight="1">
-      <c r="A428" s="36"/>
-      <c r="B428" s="34"/>
+      <c r="A428" s="33"/>
+      <c r="B428" s="37"/>
       <c r="C428" s="35"/>
       <c r="D428" s="35"/>
       <c r="E428" s="35"/>
@@ -25940,22 +26598,22 @@
       <c r="H428" s="35"/>
       <c r="I428" s="35"/>
       <c r="J428" s="35"/>
-      <c r="K428" s="37"/>
-      <c r="L428" s="38"/>
-      <c r="M428" s="38"/>
-      <c r="N428" s="38"/>
-      <c r="O428" s="38"/>
-      <c r="P428" s="38"/>
-      <c r="Q428" s="38"/>
-      <c r="R428" s="38"/>
-      <c r="S428" s="38"/>
-      <c r="T428" s="38"/>
-      <c r="U428" s="38"/>
-      <c r="V428" s="39"/>
+      <c r="K428" s="38"/>
+      <c r="L428" s="39"/>
+      <c r="M428" s="39"/>
+      <c r="N428" s="39"/>
+      <c r="O428" s="39"/>
+      <c r="P428" s="39"/>
+      <c r="Q428" s="39"/>
+      <c r="R428" s="39"/>
+      <c r="S428" s="39"/>
+      <c r="T428" s="39"/>
+      <c r="U428" s="39"/>
+      <c r="V428" s="40"/>
     </row>
     <row r="429" ht="20.05" customHeight="1">
-      <c r="A429" s="36"/>
-      <c r="B429" s="34"/>
+      <c r="A429" s="33"/>
+      <c r="B429" s="37"/>
       <c r="C429" s="35"/>
       <c r="D429" s="35"/>
       <c r="E429" s="35"/>
@@ -25964,22 +26622,22 @@
       <c r="H429" s="35"/>
       <c r="I429" s="35"/>
       <c r="J429" s="35"/>
-      <c r="K429" s="37"/>
-      <c r="L429" s="38"/>
-      <c r="M429" s="38"/>
-      <c r="N429" s="38"/>
-      <c r="O429" s="38"/>
-      <c r="P429" s="38"/>
-      <c r="Q429" s="38"/>
-      <c r="R429" s="38"/>
-      <c r="S429" s="38"/>
-      <c r="T429" s="38"/>
-      <c r="U429" s="38"/>
-      <c r="V429" s="39"/>
+      <c r="K429" s="38"/>
+      <c r="L429" s="39"/>
+      <c r="M429" s="39"/>
+      <c r="N429" s="39"/>
+      <c r="O429" s="39"/>
+      <c r="P429" s="39"/>
+      <c r="Q429" s="39"/>
+      <c r="R429" s="39"/>
+      <c r="S429" s="39"/>
+      <c r="T429" s="39"/>
+      <c r="U429" s="39"/>
+      <c r="V429" s="40"/>
     </row>
     <row r="430" ht="20.05" customHeight="1">
-      <c r="A430" s="36"/>
-      <c r="B430" s="34"/>
+      <c r="A430" s="33"/>
+      <c r="B430" s="37"/>
       <c r="C430" s="35"/>
       <c r="D430" s="35"/>
       <c r="E430" s="35"/>
@@ -25988,22 +26646,22 @@
       <c r="H430" s="35"/>
       <c r="I430" s="35"/>
       <c r="J430" s="35"/>
-      <c r="K430" s="37"/>
-      <c r="L430" s="38"/>
-      <c r="M430" s="38"/>
-      <c r="N430" s="38"/>
-      <c r="O430" s="38"/>
-      <c r="P430" s="38"/>
-      <c r="Q430" s="38"/>
-      <c r="R430" s="38"/>
-      <c r="S430" s="38"/>
-      <c r="T430" s="38"/>
-      <c r="U430" s="38"/>
-      <c r="V430" s="39"/>
+      <c r="K430" s="38"/>
+      <c r="L430" s="39"/>
+      <c r="M430" s="39"/>
+      <c r="N430" s="39"/>
+      <c r="O430" s="39"/>
+      <c r="P430" s="39"/>
+      <c r="Q430" s="39"/>
+      <c r="R430" s="39"/>
+      <c r="S430" s="39"/>
+      <c r="T430" s="39"/>
+      <c r="U430" s="39"/>
+      <c r="V430" s="40"/>
     </row>
     <row r="431" ht="20.05" customHeight="1">
-      <c r="A431" s="36"/>
-      <c r="B431" s="34"/>
+      <c r="A431" s="33"/>
+      <c r="B431" s="37"/>
       <c r="C431" s="35"/>
       <c r="D431" s="35"/>
       <c r="E431" s="35"/>
@@ -26012,22 +26670,22 @@
       <c r="H431" s="35"/>
       <c r="I431" s="35"/>
       <c r="J431" s="35"/>
-      <c r="K431" s="37"/>
-      <c r="L431" s="38"/>
-      <c r="M431" s="38"/>
-      <c r="N431" s="38"/>
-      <c r="O431" s="38"/>
-      <c r="P431" s="38"/>
-      <c r="Q431" s="38"/>
-      <c r="R431" s="38"/>
-      <c r="S431" s="38"/>
-      <c r="T431" s="38"/>
-      <c r="U431" s="38"/>
-      <c r="V431" s="39"/>
+      <c r="K431" s="38"/>
+      <c r="L431" s="39"/>
+      <c r="M431" s="39"/>
+      <c r="N431" s="39"/>
+      <c r="O431" s="39"/>
+      <c r="P431" s="39"/>
+      <c r="Q431" s="39"/>
+      <c r="R431" s="39"/>
+      <c r="S431" s="39"/>
+      <c r="T431" s="39"/>
+      <c r="U431" s="39"/>
+      <c r="V431" s="40"/>
     </row>
     <row r="432" ht="20.05" customHeight="1">
-      <c r="A432" s="36"/>
-      <c r="B432" s="34"/>
+      <c r="A432" s="33"/>
+      <c r="B432" s="37"/>
       <c r="C432" s="35"/>
       <c r="D432" s="35"/>
       <c r="E432" s="35"/>
@@ -26036,22 +26694,22 @@
       <c r="H432" s="35"/>
       <c r="I432" s="35"/>
       <c r="J432" s="35"/>
-      <c r="K432" s="37"/>
-      <c r="L432" s="38"/>
-      <c r="M432" s="38"/>
-      <c r="N432" s="38"/>
-      <c r="O432" s="38"/>
-      <c r="P432" s="38"/>
-      <c r="Q432" s="38"/>
-      <c r="R432" s="38"/>
-      <c r="S432" s="38"/>
-      <c r="T432" s="38"/>
-      <c r="U432" s="38"/>
-      <c r="V432" s="39"/>
+      <c r="K432" s="38"/>
+      <c r="L432" s="39"/>
+      <c r="M432" s="39"/>
+      <c r="N432" s="39"/>
+      <c r="O432" s="39"/>
+      <c r="P432" s="39"/>
+      <c r="Q432" s="39"/>
+      <c r="R432" s="39"/>
+      <c r="S432" s="39"/>
+      <c r="T432" s="39"/>
+      <c r="U432" s="39"/>
+      <c r="V432" s="40"/>
     </row>
     <row r="433" ht="20.05" customHeight="1">
-      <c r="A433" s="36"/>
-      <c r="B433" s="34"/>
+      <c r="A433" s="33"/>
+      <c r="B433" s="37"/>
       <c r="C433" s="35"/>
       <c r="D433" s="35"/>
       <c r="E433" s="35"/>
@@ -26060,22 +26718,22 @@
       <c r="H433" s="35"/>
       <c r="I433" s="35"/>
       <c r="J433" s="35"/>
-      <c r="K433" s="37"/>
-      <c r="L433" s="38"/>
-      <c r="M433" s="38"/>
-      <c r="N433" s="38"/>
-      <c r="O433" s="38"/>
-      <c r="P433" s="38"/>
-      <c r="Q433" s="38"/>
-      <c r="R433" s="38"/>
-      <c r="S433" s="38"/>
-      <c r="T433" s="38"/>
-      <c r="U433" s="38"/>
-      <c r="V433" s="39"/>
+      <c r="K433" s="38"/>
+      <c r="L433" s="39"/>
+      <c r="M433" s="39"/>
+      <c r="N433" s="39"/>
+      <c r="O433" s="39"/>
+      <c r="P433" s="39"/>
+      <c r="Q433" s="39"/>
+      <c r="R433" s="39"/>
+      <c r="S433" s="39"/>
+      <c r="T433" s="39"/>
+      <c r="U433" s="39"/>
+      <c r="V433" s="40"/>
     </row>
     <row r="434" ht="20.05" customHeight="1">
-      <c r="A434" s="36"/>
-      <c r="B434" s="34"/>
+      <c r="A434" s="33"/>
+      <c r="B434" s="37"/>
       <c r="C434" s="35"/>
       <c r="D434" s="35"/>
       <c r="E434" s="35"/>
@@ -26084,22 +26742,22 @@
       <c r="H434" s="35"/>
       <c r="I434" s="35"/>
       <c r="J434" s="35"/>
-      <c r="K434" s="37"/>
-      <c r="L434" s="38"/>
-      <c r="M434" s="38"/>
-      <c r="N434" s="38"/>
-      <c r="O434" s="38"/>
-      <c r="P434" s="38"/>
-      <c r="Q434" s="38"/>
-      <c r="R434" s="38"/>
-      <c r="S434" s="38"/>
-      <c r="T434" s="38"/>
-      <c r="U434" s="38"/>
-      <c r="V434" s="39"/>
+      <c r="K434" s="38"/>
+      <c r="L434" s="39"/>
+      <c r="M434" s="39"/>
+      <c r="N434" s="39"/>
+      <c r="O434" s="39"/>
+      <c r="P434" s="39"/>
+      <c r="Q434" s="39"/>
+      <c r="R434" s="39"/>
+      <c r="S434" s="39"/>
+      <c r="T434" s="39"/>
+      <c r="U434" s="39"/>
+      <c r="V434" s="40"/>
     </row>
     <row r="435" ht="20.05" customHeight="1">
-      <c r="A435" s="36"/>
-      <c r="B435" s="34"/>
+      <c r="A435" s="33"/>
+      <c r="B435" s="37"/>
       <c r="C435" s="35"/>
       <c r="D435" s="35"/>
       <c r="E435" s="35"/>
@@ -26108,22 +26766,22 @@
       <c r="H435" s="35"/>
       <c r="I435" s="35"/>
       <c r="J435" s="35"/>
-      <c r="K435" s="37"/>
-      <c r="L435" s="38"/>
-      <c r="M435" s="38"/>
-      <c r="N435" s="38"/>
-      <c r="O435" s="38"/>
-      <c r="P435" s="38"/>
-      <c r="Q435" s="38"/>
-      <c r="R435" s="38"/>
-      <c r="S435" s="38"/>
-      <c r="T435" s="38"/>
-      <c r="U435" s="38"/>
-      <c r="V435" s="39"/>
+      <c r="K435" s="38"/>
+      <c r="L435" s="39"/>
+      <c r="M435" s="39"/>
+      <c r="N435" s="39"/>
+      <c r="O435" s="39"/>
+      <c r="P435" s="39"/>
+      <c r="Q435" s="39"/>
+      <c r="R435" s="39"/>
+      <c r="S435" s="39"/>
+      <c r="T435" s="39"/>
+      <c r="U435" s="39"/>
+      <c r="V435" s="40"/>
     </row>
     <row r="436" ht="20.05" customHeight="1">
-      <c r="A436" s="36"/>
-      <c r="B436" s="34"/>
+      <c r="A436" s="33"/>
+      <c r="B436" s="37"/>
       <c r="C436" s="35"/>
       <c r="D436" s="35"/>
       <c r="E436" s="35"/>
@@ -26132,22 +26790,22 @@
       <c r="H436" s="35"/>
       <c r="I436" s="35"/>
       <c r="J436" s="35"/>
-      <c r="K436" s="37"/>
-      <c r="L436" s="38"/>
-      <c r="M436" s="38"/>
-      <c r="N436" s="38"/>
-      <c r="O436" s="38"/>
-      <c r="P436" s="38"/>
-      <c r="Q436" s="38"/>
-      <c r="R436" s="38"/>
-      <c r="S436" s="38"/>
-      <c r="T436" s="38"/>
-      <c r="U436" s="38"/>
-      <c r="V436" s="39"/>
+      <c r="K436" s="38"/>
+      <c r="L436" s="39"/>
+      <c r="M436" s="39"/>
+      <c r="N436" s="39"/>
+      <c r="O436" s="39"/>
+      <c r="P436" s="39"/>
+      <c r="Q436" s="39"/>
+      <c r="R436" s="39"/>
+      <c r="S436" s="39"/>
+      <c r="T436" s="39"/>
+      <c r="U436" s="39"/>
+      <c r="V436" s="40"/>
     </row>
     <row r="437" ht="20.05" customHeight="1">
-      <c r="A437" s="36"/>
-      <c r="B437" s="34"/>
+      <c r="A437" s="33"/>
+      <c r="B437" s="37"/>
       <c r="C437" s="35"/>
       <c r="D437" s="35"/>
       <c r="E437" s="35"/>
@@ -26156,22 +26814,22 @@
       <c r="H437" s="35"/>
       <c r="I437" s="35"/>
       <c r="J437" s="35"/>
-      <c r="K437" s="37"/>
-      <c r="L437" s="38"/>
-      <c r="M437" s="38"/>
-      <c r="N437" s="38"/>
-      <c r="O437" s="38"/>
-      <c r="P437" s="38"/>
-      <c r="Q437" s="38"/>
-      <c r="R437" s="38"/>
-      <c r="S437" s="38"/>
-      <c r="T437" s="38"/>
-      <c r="U437" s="38"/>
-      <c r="V437" s="39"/>
+      <c r="K437" s="38"/>
+      <c r="L437" s="39"/>
+      <c r="M437" s="39"/>
+      <c r="N437" s="39"/>
+      <c r="O437" s="39"/>
+      <c r="P437" s="39"/>
+      <c r="Q437" s="39"/>
+      <c r="R437" s="39"/>
+      <c r="S437" s="39"/>
+      <c r="T437" s="39"/>
+      <c r="U437" s="39"/>
+      <c r="V437" s="40"/>
     </row>
     <row r="438" ht="20.05" customHeight="1">
-      <c r="A438" s="36"/>
-      <c r="B438" s="34"/>
+      <c r="A438" s="33"/>
+      <c r="B438" s="37"/>
       <c r="C438" s="35"/>
       <c r="D438" s="35"/>
       <c r="E438" s="35"/>
@@ -26180,22 +26838,22 @@
       <c r="H438" s="35"/>
       <c r="I438" s="35"/>
       <c r="J438" s="35"/>
-      <c r="K438" s="37"/>
-      <c r="L438" s="38"/>
-      <c r="M438" s="38"/>
-      <c r="N438" s="38"/>
-      <c r="O438" s="38"/>
-      <c r="P438" s="38"/>
-      <c r="Q438" s="38"/>
-      <c r="R438" s="38"/>
-      <c r="S438" s="38"/>
-      <c r="T438" s="38"/>
-      <c r="U438" s="38"/>
-      <c r="V438" s="39"/>
+      <c r="K438" s="38"/>
+      <c r="L438" s="39"/>
+      <c r="M438" s="39"/>
+      <c r="N438" s="39"/>
+      <c r="O438" s="39"/>
+      <c r="P438" s="39"/>
+      <c r="Q438" s="39"/>
+      <c r="R438" s="39"/>
+      <c r="S438" s="39"/>
+      <c r="T438" s="39"/>
+      <c r="U438" s="39"/>
+      <c r="V438" s="40"/>
     </row>
     <row r="439" ht="20.05" customHeight="1">
-      <c r="A439" s="36"/>
-      <c r="B439" s="34"/>
+      <c r="A439" s="33"/>
+      <c r="B439" s="37"/>
       <c r="C439" s="35"/>
       <c r="D439" s="35"/>
       <c r="E439" s="35"/>
@@ -26204,22 +26862,22 @@
       <c r="H439" s="35"/>
       <c r="I439" s="35"/>
       <c r="J439" s="35"/>
-      <c r="K439" s="37"/>
-      <c r="L439" s="38"/>
-      <c r="M439" s="38"/>
-      <c r="N439" s="38"/>
-      <c r="O439" s="38"/>
-      <c r="P439" s="38"/>
-      <c r="Q439" s="38"/>
-      <c r="R439" s="38"/>
-      <c r="S439" s="38"/>
-      <c r="T439" s="38"/>
-      <c r="U439" s="38"/>
-      <c r="V439" s="39"/>
+      <c r="K439" s="38"/>
+      <c r="L439" s="39"/>
+      <c r="M439" s="39"/>
+      <c r="N439" s="39"/>
+      <c r="O439" s="39"/>
+      <c r="P439" s="39"/>
+      <c r="Q439" s="39"/>
+      <c r="R439" s="39"/>
+      <c r="S439" s="39"/>
+      <c r="T439" s="39"/>
+      <c r="U439" s="39"/>
+      <c r="V439" s="40"/>
     </row>
     <row r="440" ht="20.05" customHeight="1">
-      <c r="A440" s="36"/>
-      <c r="B440" s="34"/>
+      <c r="A440" s="33"/>
+      <c r="B440" s="37"/>
       <c r="C440" s="35"/>
       <c r="D440" s="35"/>
       <c r="E440" s="35"/>
@@ -26228,22 +26886,22 @@
       <c r="H440" s="35"/>
       <c r="I440" s="35"/>
       <c r="J440" s="35"/>
-      <c r="K440" s="37"/>
-      <c r="L440" s="38"/>
-      <c r="M440" s="38"/>
-      <c r="N440" s="38"/>
-      <c r="O440" s="38"/>
-      <c r="P440" s="38"/>
-      <c r="Q440" s="38"/>
-      <c r="R440" s="38"/>
-      <c r="S440" s="38"/>
-      <c r="T440" s="38"/>
-      <c r="U440" s="38"/>
-      <c r="V440" s="39"/>
+      <c r="K440" s="38"/>
+      <c r="L440" s="39"/>
+      <c r="M440" s="39"/>
+      <c r="N440" s="39"/>
+      <c r="O440" s="39"/>
+      <c r="P440" s="39"/>
+      <c r="Q440" s="39"/>
+      <c r="R440" s="39"/>
+      <c r="S440" s="39"/>
+      <c r="T440" s="39"/>
+      <c r="U440" s="39"/>
+      <c r="V440" s="40"/>
     </row>
     <row r="441" ht="20.05" customHeight="1">
-      <c r="A441" s="36"/>
-      <c r="B441" s="34"/>
+      <c r="A441" s="33"/>
+      <c r="B441" s="37"/>
       <c r="C441" s="35"/>
       <c r="D441" s="35"/>
       <c r="E441" s="35"/>
@@ -26252,22 +26910,22 @@
       <c r="H441" s="35"/>
       <c r="I441" s="35"/>
       <c r="J441" s="35"/>
-      <c r="K441" s="37"/>
-      <c r="L441" s="38"/>
-      <c r="M441" s="38"/>
-      <c r="N441" s="38"/>
-      <c r="O441" s="38"/>
-      <c r="P441" s="38"/>
-      <c r="Q441" s="38"/>
-      <c r="R441" s="38"/>
-      <c r="S441" s="38"/>
-      <c r="T441" s="38"/>
-      <c r="U441" s="38"/>
-      <c r="V441" s="39"/>
+      <c r="K441" s="38"/>
+      <c r="L441" s="39"/>
+      <c r="M441" s="39"/>
+      <c r="N441" s="39"/>
+      <c r="O441" s="39"/>
+      <c r="P441" s="39"/>
+      <c r="Q441" s="39"/>
+      <c r="R441" s="39"/>
+      <c r="S441" s="39"/>
+      <c r="T441" s="39"/>
+      <c r="U441" s="39"/>
+      <c r="V441" s="40"/>
     </row>
     <row r="442" ht="20.05" customHeight="1">
-      <c r="A442" s="36"/>
-      <c r="B442" s="34"/>
+      <c r="A442" s="33"/>
+      <c r="B442" s="37"/>
       <c r="C442" s="35"/>
       <c r="D442" s="35"/>
       <c r="E442" s="35"/>
@@ -26276,22 +26934,22 @@
       <c r="H442" s="35"/>
       <c r="I442" s="35"/>
       <c r="J442" s="35"/>
-      <c r="K442" s="37"/>
-      <c r="L442" s="38"/>
-      <c r="M442" s="38"/>
-      <c r="N442" s="38"/>
-      <c r="O442" s="38"/>
-      <c r="P442" s="38"/>
-      <c r="Q442" s="38"/>
-      <c r="R442" s="38"/>
-      <c r="S442" s="38"/>
-      <c r="T442" s="38"/>
-      <c r="U442" s="38"/>
-      <c r="V442" s="39"/>
+      <c r="K442" s="38"/>
+      <c r="L442" s="39"/>
+      <c r="M442" s="39"/>
+      <c r="N442" s="39"/>
+      <c r="O442" s="39"/>
+      <c r="P442" s="39"/>
+      <c r="Q442" s="39"/>
+      <c r="R442" s="39"/>
+      <c r="S442" s="39"/>
+      <c r="T442" s="39"/>
+      <c r="U442" s="39"/>
+      <c r="V442" s="40"/>
     </row>
     <row r="443" ht="20.05" customHeight="1">
-      <c r="A443" s="36"/>
-      <c r="B443" s="34"/>
+      <c r="A443" s="33"/>
+      <c r="B443" s="37"/>
       <c r="C443" s="35"/>
       <c r="D443" s="35"/>
       <c r="E443" s="35"/>
@@ -26300,22 +26958,22 @@
       <c r="H443" s="35"/>
       <c r="I443" s="35"/>
       <c r="J443" s="35"/>
-      <c r="K443" s="37"/>
-      <c r="L443" s="38"/>
-      <c r="M443" s="38"/>
-      <c r="N443" s="38"/>
-      <c r="O443" s="38"/>
-      <c r="P443" s="38"/>
-      <c r="Q443" s="38"/>
-      <c r="R443" s="38"/>
-      <c r="S443" s="38"/>
-      <c r="T443" s="38"/>
-      <c r="U443" s="38"/>
-      <c r="V443" s="39"/>
+      <c r="K443" s="38"/>
+      <c r="L443" s="39"/>
+      <c r="M443" s="39"/>
+      <c r="N443" s="39"/>
+      <c r="O443" s="39"/>
+      <c r="P443" s="39"/>
+      <c r="Q443" s="39"/>
+      <c r="R443" s="39"/>
+      <c r="S443" s="39"/>
+      <c r="T443" s="39"/>
+      <c r="U443" s="39"/>
+      <c r="V443" s="40"/>
     </row>
     <row r="444" ht="20.05" customHeight="1">
-      <c r="A444" s="36"/>
-      <c r="B444" s="34"/>
+      <c r="A444" s="33"/>
+      <c r="B444" s="37"/>
       <c r="C444" s="35"/>
       <c r="D444" s="35"/>
       <c r="E444" s="35"/>
@@ -26324,22 +26982,22 @@
       <c r="H444" s="35"/>
       <c r="I444" s="35"/>
       <c r="J444" s="35"/>
-      <c r="K444" s="37"/>
-      <c r="L444" s="38"/>
-      <c r="M444" s="38"/>
-      <c r="N444" s="38"/>
-      <c r="O444" s="38"/>
-      <c r="P444" s="38"/>
-      <c r="Q444" s="38"/>
-      <c r="R444" s="38"/>
-      <c r="S444" s="38"/>
-      <c r="T444" s="38"/>
-      <c r="U444" s="38"/>
-      <c r="V444" s="39"/>
+      <c r="K444" s="38"/>
+      <c r="L444" s="39"/>
+      <c r="M444" s="39"/>
+      <c r="N444" s="39"/>
+      <c r="O444" s="39"/>
+      <c r="P444" s="39"/>
+      <c r="Q444" s="39"/>
+      <c r="R444" s="39"/>
+      <c r="S444" s="39"/>
+      <c r="T444" s="39"/>
+      <c r="U444" s="39"/>
+      <c r="V444" s="40"/>
     </row>
     <row r="445" ht="20.05" customHeight="1">
-      <c r="A445" s="36"/>
-      <c r="B445" s="34"/>
+      <c r="A445" s="33"/>
+      <c r="B445" s="37"/>
       <c r="C445" s="35"/>
       <c r="D445" s="35"/>
       <c r="E445" s="35"/>
@@ -26348,22 +27006,22 @@
       <c r="H445" s="35"/>
       <c r="I445" s="35"/>
       <c r="J445" s="35"/>
-      <c r="K445" s="37"/>
-      <c r="L445" s="38"/>
-      <c r="M445" s="38"/>
-      <c r="N445" s="38"/>
-      <c r="O445" s="38"/>
-      <c r="P445" s="38"/>
-      <c r="Q445" s="38"/>
-      <c r="R445" s="38"/>
-      <c r="S445" s="38"/>
-      <c r="T445" s="38"/>
-      <c r="U445" s="38"/>
-      <c r="V445" s="39"/>
+      <c r="K445" s="38"/>
+      <c r="L445" s="39"/>
+      <c r="M445" s="39"/>
+      <c r="N445" s="39"/>
+      <c r="O445" s="39"/>
+      <c r="P445" s="39"/>
+      <c r="Q445" s="39"/>
+      <c r="R445" s="39"/>
+      <c r="S445" s="39"/>
+      <c r="T445" s="39"/>
+      <c r="U445" s="39"/>
+      <c r="V445" s="40"/>
     </row>
     <row r="446" ht="20.05" customHeight="1">
-      <c r="A446" s="36"/>
-      <c r="B446" s="34"/>
+      <c r="A446" s="33"/>
+      <c r="B446" s="37"/>
       <c r="C446" s="35"/>
       <c r="D446" s="35"/>
       <c r="E446" s="35"/>
@@ -26372,22 +27030,22 @@
       <c r="H446" s="35"/>
       <c r="I446" s="35"/>
       <c r="J446" s="35"/>
-      <c r="K446" s="37"/>
-      <c r="L446" s="38"/>
-      <c r="M446" s="38"/>
-      <c r="N446" s="38"/>
-      <c r="O446" s="38"/>
-      <c r="P446" s="38"/>
-      <c r="Q446" s="38"/>
-      <c r="R446" s="38"/>
-      <c r="S446" s="38"/>
-      <c r="T446" s="38"/>
-      <c r="U446" s="38"/>
-      <c r="V446" s="39"/>
+      <c r="K446" s="38"/>
+      <c r="L446" s="39"/>
+      <c r="M446" s="39"/>
+      <c r="N446" s="39"/>
+      <c r="O446" s="39"/>
+      <c r="P446" s="39"/>
+      <c r="Q446" s="39"/>
+      <c r="R446" s="39"/>
+      <c r="S446" s="39"/>
+      <c r="T446" s="39"/>
+      <c r="U446" s="39"/>
+      <c r="V446" s="40"/>
     </row>
     <row r="447" ht="20.05" customHeight="1">
-      <c r="A447" s="36"/>
-      <c r="B447" s="34"/>
+      <c r="A447" s="33"/>
+      <c r="B447" s="37"/>
       <c r="C447" s="35"/>
       <c r="D447" s="35"/>
       <c r="E447" s="35"/>
@@ -26396,22 +27054,22 @@
       <c r="H447" s="35"/>
       <c r="I447" s="35"/>
       <c r="J447" s="35"/>
-      <c r="K447" s="37"/>
-      <c r="L447" s="38"/>
-      <c r="M447" s="38"/>
-      <c r="N447" s="38"/>
-      <c r="O447" s="38"/>
-      <c r="P447" s="38"/>
-      <c r="Q447" s="38"/>
-      <c r="R447" s="38"/>
-      <c r="S447" s="38"/>
-      <c r="T447" s="38"/>
-      <c r="U447" s="38"/>
-      <c r="V447" s="39"/>
+      <c r="K447" s="38"/>
+      <c r="L447" s="39"/>
+      <c r="M447" s="39"/>
+      <c r="N447" s="39"/>
+      <c r="O447" s="39"/>
+      <c r="P447" s="39"/>
+      <c r="Q447" s="39"/>
+      <c r="R447" s="39"/>
+      <c r="S447" s="39"/>
+      <c r="T447" s="39"/>
+      <c r="U447" s="39"/>
+      <c r="V447" s="40"/>
     </row>
     <row r="448" ht="20.05" customHeight="1">
-      <c r="A448" s="36"/>
-      <c r="B448" s="34"/>
+      <c r="A448" s="33"/>
+      <c r="B448" s="37"/>
       <c r="C448" s="35"/>
       <c r="D448" s="35"/>
       <c r="E448" s="35"/>
@@ -26420,22 +27078,22 @@
       <c r="H448" s="35"/>
       <c r="I448" s="35"/>
       <c r="J448" s="35"/>
-      <c r="K448" s="37"/>
-      <c r="L448" s="38"/>
-      <c r="M448" s="38"/>
-      <c r="N448" s="38"/>
-      <c r="O448" s="38"/>
-      <c r="P448" s="38"/>
-      <c r="Q448" s="38"/>
-      <c r="R448" s="38"/>
-      <c r="S448" s="38"/>
-      <c r="T448" s="38"/>
-      <c r="U448" s="38"/>
-      <c r="V448" s="39"/>
+      <c r="K448" s="38"/>
+      <c r="L448" s="39"/>
+      <c r="M448" s="39"/>
+      <c r="N448" s="39"/>
+      <c r="O448" s="39"/>
+      <c r="P448" s="39"/>
+      <c r="Q448" s="39"/>
+      <c r="R448" s="39"/>
+      <c r="S448" s="39"/>
+      <c r="T448" s="39"/>
+      <c r="U448" s="39"/>
+      <c r="V448" s="40"/>
     </row>
     <row r="449" ht="20.05" customHeight="1">
-      <c r="A449" s="36"/>
-      <c r="B449" s="34"/>
+      <c r="A449" s="33"/>
+      <c r="B449" s="37"/>
       <c r="C449" s="35"/>
       <c r="D449" s="35"/>
       <c r="E449" s="35"/>
@@ -26444,22 +27102,22 @@
       <c r="H449" s="35"/>
       <c r="I449" s="35"/>
       <c r="J449" s="35"/>
-      <c r="K449" s="37"/>
-      <c r="L449" s="38"/>
-      <c r="M449" s="38"/>
-      <c r="N449" s="38"/>
-      <c r="O449" s="38"/>
-      <c r="P449" s="38"/>
-      <c r="Q449" s="38"/>
-      <c r="R449" s="38"/>
-      <c r="S449" s="38"/>
-      <c r="T449" s="38"/>
-      <c r="U449" s="38"/>
-      <c r="V449" s="39"/>
+      <c r="K449" s="38"/>
+      <c r="L449" s="39"/>
+      <c r="M449" s="39"/>
+      <c r="N449" s="39"/>
+      <c r="O449" s="39"/>
+      <c r="P449" s="39"/>
+      <c r="Q449" s="39"/>
+      <c r="R449" s="39"/>
+      <c r="S449" s="39"/>
+      <c r="T449" s="39"/>
+      <c r="U449" s="39"/>
+      <c r="V449" s="40"/>
     </row>
     <row r="450" ht="20.05" customHeight="1">
-      <c r="A450" s="36"/>
-      <c r="B450" s="34"/>
+      <c r="A450" s="33"/>
+      <c r="B450" s="37"/>
       <c r="C450" s="35"/>
       <c r="D450" s="35"/>
       <c r="E450" s="35"/>
@@ -26468,22 +27126,22 @@
       <c r="H450" s="35"/>
       <c r="I450" s="35"/>
       <c r="J450" s="35"/>
-      <c r="K450" s="37"/>
-      <c r="L450" s="38"/>
-      <c r="M450" s="38"/>
-      <c r="N450" s="38"/>
-      <c r="O450" s="38"/>
-      <c r="P450" s="38"/>
-      <c r="Q450" s="38"/>
-      <c r="R450" s="38"/>
-      <c r="S450" s="38"/>
-      <c r="T450" s="38"/>
-      <c r="U450" s="38"/>
-      <c r="V450" s="39"/>
+      <c r="K450" s="38"/>
+      <c r="L450" s="39"/>
+      <c r="M450" s="39"/>
+      <c r="N450" s="39"/>
+      <c r="O450" s="39"/>
+      <c r="P450" s="39"/>
+      <c r="Q450" s="39"/>
+      <c r="R450" s="39"/>
+      <c r="S450" s="39"/>
+      <c r="T450" s="39"/>
+      <c r="U450" s="39"/>
+      <c r="V450" s="40"/>
     </row>
     <row r="451" ht="20.05" customHeight="1">
-      <c r="A451" s="36"/>
-      <c r="B451" s="34"/>
+      <c r="A451" s="33"/>
+      <c r="B451" s="37"/>
       <c r="C451" s="35"/>
       <c r="D451" s="35"/>
       <c r="E451" s="35"/>
@@ -26492,22 +27150,22 @@
       <c r="H451" s="35"/>
       <c r="I451" s="35"/>
       <c r="J451" s="35"/>
-      <c r="K451" s="37"/>
-      <c r="L451" s="38"/>
-      <c r="M451" s="38"/>
-      <c r="N451" s="38"/>
-      <c r="O451" s="38"/>
-      <c r="P451" s="38"/>
-      <c r="Q451" s="38"/>
-      <c r="R451" s="38"/>
-      <c r="S451" s="38"/>
-      <c r="T451" s="38"/>
-      <c r="U451" s="38"/>
-      <c r="V451" s="39"/>
+      <c r="K451" s="38"/>
+      <c r="L451" s="39"/>
+      <c r="M451" s="39"/>
+      <c r="N451" s="39"/>
+      <c r="O451" s="39"/>
+      <c r="P451" s="39"/>
+      <c r="Q451" s="39"/>
+      <c r="R451" s="39"/>
+      <c r="S451" s="39"/>
+      <c r="T451" s="39"/>
+      <c r="U451" s="39"/>
+      <c r="V451" s="40"/>
     </row>
     <row r="452" ht="20.05" customHeight="1">
-      <c r="A452" s="36"/>
-      <c r="B452" s="34"/>
+      <c r="A452" s="33"/>
+      <c r="B452" s="37"/>
       <c r="C452" s="35"/>
       <c r="D452" s="35"/>
       <c r="E452" s="35"/>
@@ -26516,22 +27174,22 @@
       <c r="H452" s="35"/>
       <c r="I452" s="35"/>
       <c r="J452" s="35"/>
-      <c r="K452" s="37"/>
-      <c r="L452" s="38"/>
-      <c r="M452" s="38"/>
-      <c r="N452" s="38"/>
-      <c r="O452" s="38"/>
-      <c r="P452" s="38"/>
-      <c r="Q452" s="38"/>
-      <c r="R452" s="38"/>
-      <c r="S452" s="38"/>
-      <c r="T452" s="38"/>
-      <c r="U452" s="38"/>
-      <c r="V452" s="39"/>
+      <c r="K452" s="38"/>
+      <c r="L452" s="39"/>
+      <c r="M452" s="39"/>
+      <c r="N452" s="39"/>
+      <c r="O452" s="39"/>
+      <c r="P452" s="39"/>
+      <c r="Q452" s="39"/>
+      <c r="R452" s="39"/>
+      <c r="S452" s="39"/>
+      <c r="T452" s="39"/>
+      <c r="U452" s="39"/>
+      <c r="V452" s="40"/>
     </row>
     <row r="453" ht="20.05" customHeight="1">
-      <c r="A453" s="36"/>
-      <c r="B453" s="34"/>
+      <c r="A453" s="33"/>
+      <c r="B453" s="37"/>
       <c r="C453" s="35"/>
       <c r="D453" s="35"/>
       <c r="E453" s="35"/>
@@ -26540,22 +27198,22 @@
       <c r="H453" s="35"/>
       <c r="I453" s="35"/>
       <c r="J453" s="35"/>
-      <c r="K453" s="37"/>
-      <c r="L453" s="38"/>
-      <c r="M453" s="38"/>
-      <c r="N453" s="38"/>
-      <c r="O453" s="38"/>
-      <c r="P453" s="38"/>
-      <c r="Q453" s="38"/>
-      <c r="R453" s="38"/>
-      <c r="S453" s="38"/>
-      <c r="T453" s="38"/>
-      <c r="U453" s="38"/>
-      <c r="V453" s="39"/>
+      <c r="K453" s="38"/>
+      <c r="L453" s="39"/>
+      <c r="M453" s="39"/>
+      <c r="N453" s="39"/>
+      <c r="O453" s="39"/>
+      <c r="P453" s="39"/>
+      <c r="Q453" s="39"/>
+      <c r="R453" s="39"/>
+      <c r="S453" s="39"/>
+      <c r="T453" s="39"/>
+      <c r="U453" s="39"/>
+      <c r="V453" s="40"/>
     </row>
     <row r="454" ht="20.05" customHeight="1">
-      <c r="A454" s="36"/>
-      <c r="B454" s="34"/>
+      <c r="A454" s="33"/>
+      <c r="B454" s="37"/>
       <c r="C454" s="35"/>
       <c r="D454" s="35"/>
       <c r="E454" s="35"/>
@@ -26564,22 +27222,22 @@
       <c r="H454" s="35"/>
       <c r="I454" s="35"/>
       <c r="J454" s="35"/>
-      <c r="K454" s="37"/>
-      <c r="L454" s="38"/>
-      <c r="M454" s="38"/>
-      <c r="N454" s="38"/>
-      <c r="O454" s="38"/>
-      <c r="P454" s="38"/>
-      <c r="Q454" s="38"/>
-      <c r="R454" s="38"/>
-      <c r="S454" s="38"/>
-      <c r="T454" s="38"/>
-      <c r="U454" s="38"/>
-      <c r="V454" s="39"/>
+      <c r="K454" s="38"/>
+      <c r="L454" s="39"/>
+      <c r="M454" s="39"/>
+      <c r="N454" s="39"/>
+      <c r="O454" s="39"/>
+      <c r="P454" s="39"/>
+      <c r="Q454" s="39"/>
+      <c r="R454" s="39"/>
+      <c r="S454" s="39"/>
+      <c r="T454" s="39"/>
+      <c r="U454" s="39"/>
+      <c r="V454" s="40"/>
     </row>
     <row r="455" ht="20.05" customHeight="1">
-      <c r="A455" s="36"/>
-      <c r="B455" s="34"/>
+      <c r="A455" s="33"/>
+      <c r="B455" s="37"/>
       <c r="C455" s="35"/>
       <c r="D455" s="35"/>
       <c r="E455" s="35"/>
@@ -26588,22 +27246,22 @@
       <c r="H455" s="35"/>
       <c r="I455" s="35"/>
       <c r="J455" s="35"/>
-      <c r="K455" s="37"/>
-      <c r="L455" s="38"/>
-      <c r="M455" s="38"/>
-      <c r="N455" s="38"/>
-      <c r="O455" s="38"/>
-      <c r="P455" s="38"/>
-      <c r="Q455" s="38"/>
-      <c r="R455" s="38"/>
-      <c r="S455" s="38"/>
-      <c r="T455" s="38"/>
-      <c r="U455" s="38"/>
-      <c r="V455" s="39"/>
+      <c r="K455" s="38"/>
+      <c r="L455" s="39"/>
+      <c r="M455" s="39"/>
+      <c r="N455" s="39"/>
+      <c r="O455" s="39"/>
+      <c r="P455" s="39"/>
+      <c r="Q455" s="39"/>
+      <c r="R455" s="39"/>
+      <c r="S455" s="39"/>
+      <c r="T455" s="39"/>
+      <c r="U455" s="39"/>
+      <c r="V455" s="40"/>
     </row>
     <row r="456" ht="20.05" customHeight="1">
-      <c r="A456" s="36"/>
-      <c r="B456" s="34"/>
+      <c r="A456" s="33"/>
+      <c r="B456" s="37"/>
       <c r="C456" s="35"/>
       <c r="D456" s="35"/>
       <c r="E456" s="35"/>
@@ -26612,22 +27270,22 @@
       <c r="H456" s="35"/>
       <c r="I456" s="35"/>
       <c r="J456" s="35"/>
-      <c r="K456" s="37"/>
-      <c r="L456" s="38"/>
-      <c r="M456" s="38"/>
-      <c r="N456" s="38"/>
-      <c r="O456" s="38"/>
-      <c r="P456" s="38"/>
-      <c r="Q456" s="38"/>
-      <c r="R456" s="38"/>
-      <c r="S456" s="38"/>
-      <c r="T456" s="38"/>
-      <c r="U456" s="38"/>
-      <c r="V456" s="39"/>
+      <c r="K456" s="38"/>
+      <c r="L456" s="39"/>
+      <c r="M456" s="39"/>
+      <c r="N456" s="39"/>
+      <c r="O456" s="39"/>
+      <c r="P456" s="39"/>
+      <c r="Q456" s="39"/>
+      <c r="R456" s="39"/>
+      <c r="S456" s="39"/>
+      <c r="T456" s="39"/>
+      <c r="U456" s="39"/>
+      <c r="V456" s="40"/>
     </row>
     <row r="457" ht="20.05" customHeight="1">
-      <c r="A457" s="36"/>
-      <c r="B457" s="34"/>
+      <c r="A457" s="33"/>
+      <c r="B457" s="37"/>
       <c r="C457" s="35"/>
       <c r="D457" s="35"/>
       <c r="E457" s="35"/>
@@ -26636,22 +27294,22 @@
       <c r="H457" s="35"/>
       <c r="I457" s="35"/>
       <c r="J457" s="35"/>
-      <c r="K457" s="37"/>
-      <c r="L457" s="38"/>
-      <c r="M457" s="38"/>
-      <c r="N457" s="38"/>
-      <c r="O457" s="38"/>
-      <c r="P457" s="38"/>
-      <c r="Q457" s="38"/>
-      <c r="R457" s="38"/>
-      <c r="S457" s="38"/>
-      <c r="T457" s="38"/>
-      <c r="U457" s="38"/>
-      <c r="V457" s="39"/>
+      <c r="K457" s="38"/>
+      <c r="L457" s="39"/>
+      <c r="M457" s="39"/>
+      <c r="N457" s="39"/>
+      <c r="O457" s="39"/>
+      <c r="P457" s="39"/>
+      <c r="Q457" s="39"/>
+      <c r="R457" s="39"/>
+      <c r="S457" s="39"/>
+      <c r="T457" s="39"/>
+      <c r="U457" s="39"/>
+      <c r="V457" s="40"/>
     </row>
     <row r="458" ht="20.05" customHeight="1">
-      <c r="A458" s="36"/>
-      <c r="B458" s="34"/>
+      <c r="A458" s="33"/>
+      <c r="B458" s="37"/>
       <c r="C458" s="35"/>
       <c r="D458" s="35"/>
       <c r="E458" s="35"/>
@@ -26660,22 +27318,22 @@
       <c r="H458" s="35"/>
       <c r="I458" s="35"/>
       <c r="J458" s="35"/>
-      <c r="K458" s="37"/>
-      <c r="L458" s="38"/>
-      <c r="M458" s="38"/>
-      <c r="N458" s="38"/>
-      <c r="O458" s="38"/>
-      <c r="P458" s="38"/>
-      <c r="Q458" s="38"/>
-      <c r="R458" s="38"/>
-      <c r="S458" s="38"/>
-      <c r="T458" s="38"/>
-      <c r="U458" s="38"/>
-      <c r="V458" s="39"/>
+      <c r="K458" s="38"/>
+      <c r="L458" s="39"/>
+      <c r="M458" s="39"/>
+      <c r="N458" s="39"/>
+      <c r="O458" s="39"/>
+      <c r="P458" s="39"/>
+      <c r="Q458" s="39"/>
+      <c r="R458" s="39"/>
+      <c r="S458" s="39"/>
+      <c r="T458" s="39"/>
+      <c r="U458" s="39"/>
+      <c r="V458" s="40"/>
     </row>
     <row r="459" ht="20.05" customHeight="1">
-      <c r="A459" s="36"/>
-      <c r="B459" s="34"/>
+      <c r="A459" s="33"/>
+      <c r="B459" s="37"/>
       <c r="C459" s="35"/>
       <c r="D459" s="35"/>
       <c r="E459" s="35"/>
@@ -26684,22 +27342,22 @@
       <c r="H459" s="35"/>
       <c r="I459" s="35"/>
       <c r="J459" s="35"/>
-      <c r="K459" s="37"/>
-      <c r="L459" s="38"/>
-      <c r="M459" s="38"/>
-      <c r="N459" s="38"/>
-      <c r="O459" s="38"/>
-      <c r="P459" s="38"/>
-      <c r="Q459" s="38"/>
-      <c r="R459" s="38"/>
-      <c r="S459" s="38"/>
-      <c r="T459" s="38"/>
-      <c r="U459" s="38"/>
-      <c r="V459" s="39"/>
+      <c r="K459" s="38"/>
+      <c r="L459" s="39"/>
+      <c r="M459" s="39"/>
+      <c r="N459" s="39"/>
+      <c r="O459" s="39"/>
+      <c r="P459" s="39"/>
+      <c r="Q459" s="39"/>
+      <c r="R459" s="39"/>
+      <c r="S459" s="39"/>
+      <c r="T459" s="39"/>
+      <c r="U459" s="39"/>
+      <c r="V459" s="40"/>
     </row>
     <row r="460" ht="20.05" customHeight="1">
-      <c r="A460" s="36"/>
-      <c r="B460" s="34"/>
+      <c r="A460" s="33"/>
+      <c r="B460" s="37"/>
       <c r="C460" s="35"/>
       <c r="D460" s="35"/>
       <c r="E460" s="35"/>
@@ -26708,22 +27366,22 @@
       <c r="H460" s="35"/>
       <c r="I460" s="35"/>
       <c r="J460" s="35"/>
-      <c r="K460" s="37"/>
-      <c r="L460" s="38"/>
-      <c r="M460" s="38"/>
-      <c r="N460" s="38"/>
-      <c r="O460" s="38"/>
-      <c r="P460" s="38"/>
-      <c r="Q460" s="38"/>
-      <c r="R460" s="38"/>
-      <c r="S460" s="38"/>
-      <c r="T460" s="38"/>
-      <c r="U460" s="38"/>
-      <c r="V460" s="39"/>
+      <c r="K460" s="38"/>
+      <c r="L460" s="39"/>
+      <c r="M460" s="39"/>
+      <c r="N460" s="39"/>
+      <c r="O460" s="39"/>
+      <c r="P460" s="39"/>
+      <c r="Q460" s="39"/>
+      <c r="R460" s="39"/>
+      <c r="S460" s="39"/>
+      <c r="T460" s="39"/>
+      <c r="U460" s="39"/>
+      <c r="V460" s="40"/>
     </row>
     <row r="461" ht="20.05" customHeight="1">
-      <c r="A461" s="36"/>
-      <c r="B461" s="34"/>
+      <c r="A461" s="33"/>
+      <c r="B461" s="37"/>
       <c r="C461" s="35"/>
       <c r="D461" s="35"/>
       <c r="E461" s="35"/>
@@ -26732,22 +27390,22 @@
       <c r="H461" s="35"/>
       <c r="I461" s="35"/>
       <c r="J461" s="35"/>
-      <c r="K461" s="37"/>
-      <c r="L461" s="38"/>
-      <c r="M461" s="38"/>
-      <c r="N461" s="38"/>
-      <c r="O461" s="38"/>
-      <c r="P461" s="38"/>
-      <c r="Q461" s="38"/>
-      <c r="R461" s="38"/>
-      <c r="S461" s="38"/>
-      <c r="T461" s="38"/>
-      <c r="U461" s="38"/>
-      <c r="V461" s="39"/>
+      <c r="K461" s="38"/>
+      <c r="L461" s="39"/>
+      <c r="M461" s="39"/>
+      <c r="N461" s="39"/>
+      <c r="O461" s="39"/>
+      <c r="P461" s="39"/>
+      <c r="Q461" s="39"/>
+      <c r="R461" s="39"/>
+      <c r="S461" s="39"/>
+      <c r="T461" s="39"/>
+      <c r="U461" s="39"/>
+      <c r="V461" s="40"/>
     </row>
     <row r="462" ht="20.05" customHeight="1">
-      <c r="A462" s="36"/>
-      <c r="B462" s="34"/>
+      <c r="A462" s="33"/>
+      <c r="B462" s="37"/>
       <c r="C462" s="35"/>
       <c r="D462" s="35"/>
       <c r="E462" s="35"/>
@@ -26756,22 +27414,22 @@
       <c r="H462" s="35"/>
       <c r="I462" s="35"/>
       <c r="J462" s="35"/>
-      <c r="K462" s="37"/>
-      <c r="L462" s="38"/>
-      <c r="M462" s="38"/>
-      <c r="N462" s="38"/>
-      <c r="O462" s="38"/>
-      <c r="P462" s="38"/>
-      <c r="Q462" s="38"/>
-      <c r="R462" s="38"/>
-      <c r="S462" s="38"/>
-      <c r="T462" s="38"/>
-      <c r="U462" s="38"/>
-      <c r="V462" s="39"/>
+      <c r="K462" s="38"/>
+      <c r="L462" s="39"/>
+      <c r="M462" s="39"/>
+      <c r="N462" s="39"/>
+      <c r="O462" s="39"/>
+      <c r="P462" s="39"/>
+      <c r="Q462" s="39"/>
+      <c r="R462" s="39"/>
+      <c r="S462" s="39"/>
+      <c r="T462" s="39"/>
+      <c r="U462" s="39"/>
+      <c r="V462" s="40"/>
     </row>
     <row r="463" ht="20.05" customHeight="1">
-      <c r="A463" s="36"/>
-      <c r="B463" s="34"/>
+      <c r="A463" s="33"/>
+      <c r="B463" s="37"/>
       <c r="C463" s="35"/>
       <c r="D463" s="35"/>
       <c r="E463" s="35"/>
@@ -26780,22 +27438,22 @@
       <c r="H463" s="35"/>
       <c r="I463" s="35"/>
       <c r="J463" s="35"/>
-      <c r="K463" s="37"/>
-      <c r="L463" s="38"/>
-      <c r="M463" s="38"/>
-      <c r="N463" s="38"/>
-      <c r="O463" s="38"/>
-      <c r="P463" s="38"/>
-      <c r="Q463" s="38"/>
-      <c r="R463" s="38"/>
-      <c r="S463" s="38"/>
-      <c r="T463" s="38"/>
-      <c r="U463" s="38"/>
-      <c r="V463" s="39"/>
+      <c r="K463" s="38"/>
+      <c r="L463" s="39"/>
+      <c r="M463" s="39"/>
+      <c r="N463" s="39"/>
+      <c r="O463" s="39"/>
+      <c r="P463" s="39"/>
+      <c r="Q463" s="39"/>
+      <c r="R463" s="39"/>
+      <c r="S463" s="39"/>
+      <c r="T463" s="39"/>
+      <c r="U463" s="39"/>
+      <c r="V463" s="40"/>
     </row>
     <row r="464" ht="20.05" customHeight="1">
-      <c r="A464" s="36"/>
-      <c r="B464" s="34"/>
+      <c r="A464" s="33"/>
+      <c r="B464" s="37"/>
       <c r="C464" s="35"/>
       <c r="D464" s="35"/>
       <c r="E464" s="35"/>
@@ -26804,22 +27462,22 @@
       <c r="H464" s="35"/>
       <c r="I464" s="35"/>
       <c r="J464" s="35"/>
-      <c r="K464" s="37"/>
-      <c r="L464" s="38"/>
-      <c r="M464" s="38"/>
-      <c r="N464" s="38"/>
-      <c r="O464" s="38"/>
-      <c r="P464" s="38"/>
-      <c r="Q464" s="38"/>
-      <c r="R464" s="38"/>
-      <c r="S464" s="38"/>
-      <c r="T464" s="38"/>
-      <c r="U464" s="38"/>
-      <c r="V464" s="39"/>
+      <c r="K464" s="38"/>
+      <c r="L464" s="39"/>
+      <c r="M464" s="39"/>
+      <c r="N464" s="39"/>
+      <c r="O464" s="39"/>
+      <c r="P464" s="39"/>
+      <c r="Q464" s="39"/>
+      <c r="R464" s="39"/>
+      <c r="S464" s="39"/>
+      <c r="T464" s="39"/>
+      <c r="U464" s="39"/>
+      <c r="V464" s="40"/>
     </row>
     <row r="465" ht="20.05" customHeight="1">
-      <c r="A465" s="36"/>
-      <c r="B465" s="34"/>
+      <c r="A465" s="33"/>
+      <c r="B465" s="37"/>
       <c r="C465" s="35"/>
       <c r="D465" s="35"/>
       <c r="E465" s="35"/>
@@ -26828,22 +27486,22 @@
       <c r="H465" s="35"/>
       <c r="I465" s="35"/>
       <c r="J465" s="35"/>
-      <c r="K465" s="37"/>
-      <c r="L465" s="38"/>
-      <c r="M465" s="38"/>
-      <c r="N465" s="38"/>
-      <c r="O465" s="38"/>
-      <c r="P465" s="38"/>
-      <c r="Q465" s="38"/>
-      <c r="R465" s="38"/>
-      <c r="S465" s="38"/>
-      <c r="T465" s="38"/>
-      <c r="U465" s="38"/>
-      <c r="V465" s="39"/>
+      <c r="K465" s="38"/>
+      <c r="L465" s="39"/>
+      <c r="M465" s="39"/>
+      <c r="N465" s="39"/>
+      <c r="O465" s="39"/>
+      <c r="P465" s="39"/>
+      <c r="Q465" s="39"/>
+      <c r="R465" s="39"/>
+      <c r="S465" s="39"/>
+      <c r="T465" s="39"/>
+      <c r="U465" s="39"/>
+      <c r="V465" s="40"/>
     </row>
     <row r="466" ht="20.05" customHeight="1">
-      <c r="A466" s="36"/>
-      <c r="B466" s="34"/>
+      <c r="A466" s="33"/>
+      <c r="B466" s="37"/>
       <c r="C466" s="35"/>
       <c r="D466" s="35"/>
       <c r="E466" s="35"/>
@@ -26852,90 +27510,18 @@
       <c r="H466" s="35"/>
       <c r="I466" s="35"/>
       <c r="J466" s="35"/>
-      <c r="K466" s="37"/>
-      <c r="L466" s="38"/>
-      <c r="M466" s="38"/>
-      <c r="N466" s="38"/>
-      <c r="O466" s="38"/>
-      <c r="P466" s="38"/>
-      <c r="Q466" s="38"/>
-      <c r="R466" s="38"/>
-      <c r="S466" s="38"/>
-      <c r="T466" s="38"/>
-      <c r="U466" s="38"/>
-      <c r="V466" s="39"/>
-    </row>
-    <row r="467" ht="20.05" customHeight="1">
-      <c r="A467" s="36"/>
-      <c r="B467" s="34"/>
-      <c r="C467" s="35"/>
-      <c r="D467" s="35"/>
-      <c r="E467" s="35"/>
-      <c r="F467" s="35"/>
-      <c r="G467" s="35"/>
-      <c r="H467" s="35"/>
-      <c r="I467" s="35"/>
-      <c r="J467" s="35"/>
-      <c r="K467" s="37"/>
-      <c r="L467" s="38"/>
-      <c r="M467" s="38"/>
-      <c r="N467" s="38"/>
-      <c r="O467" s="38"/>
-      <c r="P467" s="38"/>
-      <c r="Q467" s="38"/>
-      <c r="R467" s="38"/>
-      <c r="S467" s="38"/>
-      <c r="T467" s="38"/>
-      <c r="U467" s="38"/>
-      <c r="V467" s="39"/>
-    </row>
-    <row r="468" ht="20.05" customHeight="1">
-      <c r="A468" s="36"/>
-      <c r="B468" s="34"/>
-      <c r="C468" s="35"/>
-      <c r="D468" s="35"/>
-      <c r="E468" s="35"/>
-      <c r="F468" s="35"/>
-      <c r="G468" s="35"/>
-      <c r="H468" s="35"/>
-      <c r="I468" s="35"/>
-      <c r="J468" s="35"/>
-      <c r="K468" s="37"/>
-      <c r="L468" s="38"/>
-      <c r="M468" s="38"/>
-      <c r="N468" s="38"/>
-      <c r="O468" s="38"/>
-      <c r="P468" s="38"/>
-      <c r="Q468" s="38"/>
-      <c r="R468" s="38"/>
-      <c r="S468" s="38"/>
-      <c r="T468" s="38"/>
-      <c r="U468" s="38"/>
-      <c r="V468" s="39"/>
-    </row>
-    <row r="469" ht="20.05" customHeight="1">
-      <c r="A469" s="36"/>
-      <c r="B469" s="34"/>
-      <c r="C469" s="35"/>
-      <c r="D469" s="35"/>
-      <c r="E469" s="35"/>
-      <c r="F469" s="35"/>
-      <c r="G469" s="35"/>
-      <c r="H469" s="35"/>
-      <c r="I469" s="35"/>
-      <c r="J469" s="35"/>
-      <c r="K469" s="40"/>
-      <c r="L469" s="41"/>
-      <c r="M469" s="41"/>
-      <c r="N469" s="41"/>
-      <c r="O469" s="41"/>
-      <c r="P469" s="41"/>
-      <c r="Q469" s="41"/>
-      <c r="R469" s="41"/>
-      <c r="S469" s="41"/>
-      <c r="T469" s="41"/>
-      <c r="U469" s="41"/>
-      <c r="V469" s="42"/>
+      <c r="K466" s="41"/>
+      <c r="L466" s="42"/>
+      <c r="M466" s="42"/>
+      <c r="N466" s="42"/>
+      <c r="O466" s="42"/>
+      <c r="P466" s="42"/>
+      <c r="Q466" s="42"/>
+      <c r="R466" s="42"/>
+      <c r="S466" s="42"/>
+      <c r="T466" s="42"/>
+      <c r="U466" s="42"/>
+      <c r="V466" s="43"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -26957,12 +27543,12 @@
   <dimension ref="A1:X68"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="12" style="43" customWidth="1"/>
-    <col min="2" max="2" width="12.5" style="43" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="43" customWidth="1"/>
-    <col min="4" max="4" width="13" style="43" customWidth="1"/>
-    <col min="5" max="24" width="16.3516" style="43" customWidth="1"/>
-    <col min="25" max="16384" width="16.3516" style="43" customWidth="1"/>
+    <col min="1" max="1" width="12" style="44" customWidth="1"/>
+    <col min="2" max="2" width="12.5" style="44" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="44" customWidth="1"/>
+    <col min="4" max="4" width="13" style="44" customWidth="1"/>
+    <col min="5" max="24" width="16.3516" style="44" customWidth="1"/>
+    <col min="25" max="16384" width="16.3516" style="44" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="27.65" customHeight="1">
@@ -26994,85 +27580,85 @@
       <c r="X1" s="5"/>
     </row>
     <row r="2" ht="20.25" customHeight="1">
-      <c r="A2" t="s" s="44">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s" s="44">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s" s="44">
+      <c r="A2" t="s" s="45">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="45">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s" s="45">
         <v>6</v>
       </c>
-      <c r="D2" t="s" s="44">
+      <c r="D2" t="s" s="45">
         <v>7</v>
       </c>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="45"/>
-      <c r="I2" s="45"/>
-      <c r="J2" s="45"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="45"/>
-      <c r="M2" s="45"/>
-      <c r="N2" s="45"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="45"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="45"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="45"/>
-      <c r="U2" s="45"/>
-      <c r="V2" s="45"/>
-      <c r="W2" s="45"/>
-      <c r="X2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="46"/>
+      <c r="L2" s="46"/>
+      <c r="M2" s="46"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="46"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="46"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="46"/>
+      <c r="T2" s="46"/>
+      <c r="U2" s="46"/>
+      <c r="V2" s="46"/>
+      <c r="W2" s="46"/>
+      <c r="X2" s="46"/>
     </row>
     <row r="3" ht="20.25" customHeight="1">
       <c r="A3" t="s" s="13">
         <v>23</v>
       </c>
-      <c r="B3" t="s" s="46">
-        <v>242</v>
-      </c>
-      <c r="C3" t="s" s="47">
-        <v>243</v>
+      <c r="B3" t="s" s="47">
+        <v>272</v>
+      </c>
+      <c r="C3" t="s" s="48">
+        <v>273</v>
       </c>
       <c r="D3" t="s" s="16">
-        <v>244</v>
-      </c>
-      <c r="E3" s="48"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="48"/>
-      <c r="I3" s="48"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="48"/>
-      <c r="L3" s="48"/>
-      <c r="M3" s="48"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="48"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="48"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="48"/>
-      <c r="T3" s="48"/>
-      <c r="U3" s="48"/>
-      <c r="V3" s="48"/>
-      <c r="W3" s="48"/>
-      <c r="X3" s="48"/>
+        <v>274</v>
+      </c>
+      <c r="E3" s="36"/>
+      <c r="F3" s="36"/>
+      <c r="G3" s="36"/>
+      <c r="H3" s="36"/>
+      <c r="I3" s="36"/>
+      <c r="J3" s="36"/>
+      <c r="K3" s="36"/>
+      <c r="L3" s="36"/>
+      <c r="M3" s="36"/>
+      <c r="N3" s="36"/>
+      <c r="O3" s="36"/>
+      <c r="P3" s="36"/>
+      <c r="Q3" s="36"/>
+      <c r="R3" s="36"/>
+      <c r="S3" s="36"/>
+      <c r="T3" s="36"/>
+      <c r="U3" s="36"/>
+      <c r="V3" s="36"/>
+      <c r="W3" s="36"/>
+      <c r="X3" s="36"/>
     </row>
     <row r="4" ht="20.05" customHeight="1">
       <c r="A4" t="s" s="20">
         <v>23</v>
       </c>
       <c r="B4" t="s" s="49">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C4" t="s" s="50">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D4" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E4" s="35"/>
       <c r="F4" s="35"/>
@@ -27100,13 +27686,13 @@
         <v>23</v>
       </c>
       <c r="B5" t="s" s="49">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C5" t="s" s="50">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D5" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E5" s="35"/>
       <c r="F5" s="35"/>
@@ -27134,13 +27720,13 @@
         <v>23</v>
       </c>
       <c r="B6" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C6" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D6" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E6" s="35"/>
       <c r="F6" s="35"/>
@@ -27168,13 +27754,13 @@
         <v>23</v>
       </c>
       <c r="B7" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C7" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D7" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E7" s="35"/>
       <c r="F7" s="35"/>
@@ -27202,13 +27788,13 @@
         <v>23</v>
       </c>
       <c r="B8" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C8" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D8" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E8" s="35"/>
       <c r="F8" s="35"/>
@@ -27236,13 +27822,13 @@
         <v>23</v>
       </c>
       <c r="B9" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C9" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D9" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E9" s="35"/>
       <c r="F9" s="35"/>
@@ -27270,13 +27856,13 @@
         <v>23</v>
       </c>
       <c r="B10" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C10" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D10" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E10" s="35"/>
       <c r="F10" s="35"/>
@@ -27304,13 +27890,13 @@
         <v>23</v>
       </c>
       <c r="B11" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C11" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D11" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E11" s="35"/>
       <c r="F11" s="35"/>
@@ -27338,13 +27924,13 @@
         <v>23</v>
       </c>
       <c r="B12" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C12" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D12" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E12" s="35"/>
       <c r="F12" s="35"/>
@@ -27372,13 +27958,13 @@
         <v>23</v>
       </c>
       <c r="B13" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C13" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D13" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E13" s="35"/>
       <c r="F13" s="35"/>
@@ -27406,13 +27992,13 @@
         <v>23</v>
       </c>
       <c r="B14" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C14" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D14" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E14" s="35"/>
       <c r="F14" s="35"/>
@@ -27440,13 +28026,13 @@
         <v>23</v>
       </c>
       <c r="B15" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C15" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D15" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E15" s="35"/>
       <c r="F15" s="35"/>
@@ -27474,13 +28060,13 @@
         <v>23</v>
       </c>
       <c r="B16" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C16" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D16" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E16" s="35"/>
       <c r="F16" s="35"/>
@@ -27508,13 +28094,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C17" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E17" s="35"/>
       <c r="F17" s="35"/>
@@ -27542,13 +28128,13 @@
         <v>23</v>
       </c>
       <c r="B18" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D18" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E18" s="35"/>
       <c r="F18" s="35"/>
@@ -27576,13 +28162,13 @@
         <v>23</v>
       </c>
       <c r="B19" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C19" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D19" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E19" s="35"/>
       <c r="F19" s="35"/>
@@ -27610,13 +28196,13 @@
         <v>23</v>
       </c>
       <c r="B20" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C20" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D20" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E20" s="35"/>
       <c r="F20" s="35"/>
@@ -27644,13 +28230,13 @@
         <v>23</v>
       </c>
       <c r="B21" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C21" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D21" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E21" s="35"/>
       <c r="F21" s="35"/>
@@ -27678,13 +28264,13 @@
         <v>23</v>
       </c>
       <c r="B22" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C22" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D22" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E22" s="35"/>
       <c r="F22" s="35"/>
@@ -27712,13 +28298,13 @@
         <v>23</v>
       </c>
       <c r="B23" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C23" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D23" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E23" s="35"/>
       <c r="F23" s="35"/>
@@ -27746,13 +28332,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C24" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E24" s="35"/>
       <c r="F24" s="35"/>
@@ -27780,13 +28366,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C25" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D25" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="E25" s="35"/>
       <c r="F25" s="35"/>
@@ -27814,13 +28400,13 @@
         <v>23</v>
       </c>
       <c r="B26" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C26" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D26" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
@@ -27848,13 +28434,13 @@
         <v>23</v>
       </c>
       <c r="B27" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C27" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="D27" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="E27" s="35"/>
       <c r="F27" s="35"/>
@@ -27882,13 +28468,13 @@
         <v>23</v>
       </c>
       <c r="B28" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C28" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="D28" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E28" s="35"/>
       <c r="F28" s="35"/>
@@ -27916,13 +28502,13 @@
         <v>23</v>
       </c>
       <c r="B29" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C29" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D29" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="E29" s="35"/>
       <c r="F29" s="35"/>
@@ -27950,13 +28536,13 @@
         <v>23</v>
       </c>
       <c r="B30" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C30" t="s" s="23">
-        <v>247</v>
+        <v>277</v>
       </c>
       <c r="D30" t="s" s="23">
-        <v>246</v>
+        <v>276</v>
       </c>
       <c r="E30" s="35"/>
       <c r="F30" s="35"/>
@@ -27984,13 +28570,13 @@
         <v>23</v>
       </c>
       <c r="B31" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C31" t="s" s="23">
-        <v>245</v>
+        <v>275</v>
       </c>
       <c r="D31" t="s" s="23">
-        <v>244</v>
+        <v>274</v>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35"/>
@@ -28018,13 +28604,13 @@
         <v>23</v>
       </c>
       <c r="B32" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C32" t="s" s="23">
-        <v>243</v>
+        <v>273</v>
       </c>
       <c r="D32" t="s" s="23">
-        <v>248</v>
+        <v>278</v>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35"/>
@@ -28052,13 +28638,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s" s="49">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C33" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D33" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E33" s="35"/>
       <c r="F33" s="35"/>
@@ -28086,13 +28672,13 @@
         <v>39</v>
       </c>
       <c r="B34" t="s" s="49">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C34" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D34" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E34" s="35"/>
       <c r="F34" s="35"/>
@@ -28120,13 +28706,13 @@
         <v>39</v>
       </c>
       <c r="B35" t="s" s="49">
-        <v>242</v>
+        <v>272</v>
       </c>
       <c r="C35" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D35" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E35" s="35"/>
       <c r="F35" s="35"/>
@@ -28154,13 +28740,13 @@
         <v>39</v>
       </c>
       <c r="B36" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C36" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D36" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="35"/>
@@ -28188,13 +28774,13 @@
         <v>39</v>
       </c>
       <c r="B37" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C37" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D37" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E37" s="35"/>
       <c r="F37" s="35"/>
@@ -28222,13 +28808,13 @@
         <v>39</v>
       </c>
       <c r="B38" t="s" s="49">
-        <v>249</v>
+        <v>279</v>
       </c>
       <c r="C38" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D38" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E38" s="35"/>
       <c r="F38" s="35"/>
@@ -28256,13 +28842,13 @@
         <v>39</v>
       </c>
       <c r="B39" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C39" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D39" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="35"/>
@@ -28290,13 +28876,13 @@
         <v>39</v>
       </c>
       <c r="B40" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C40" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D40" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E40" s="35"/>
       <c r="F40" s="35"/>
@@ -28324,13 +28910,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s" s="49">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="C41" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D41" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E41" s="35"/>
       <c r="F41" s="35"/>
@@ -28358,13 +28944,13 @@
         <v>39</v>
       </c>
       <c r="B42" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C42" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D42" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E42" s="35"/>
       <c r="F42" s="35"/>
@@ -28392,13 +28978,13 @@
         <v>39</v>
       </c>
       <c r="B43" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C43" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D43" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E43" s="35"/>
       <c r="F43" s="35"/>
@@ -28426,13 +29012,13 @@
         <v>39</v>
       </c>
       <c r="B44" t="s" s="49">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C44" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D44" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E44" s="35"/>
       <c r="F44" s="35"/>
@@ -28460,13 +29046,13 @@
         <v>39</v>
       </c>
       <c r="B45" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C45" t="s" s="50">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D45" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E45" s="35"/>
       <c r="F45" s="35"/>
@@ -28494,13 +29080,13 @@
         <v>39</v>
       </c>
       <c r="B46" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C46" t="s" s="50">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D46" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E46" s="35"/>
       <c r="F46" s="35"/>
@@ -28528,13 +29114,13 @@
         <v>39</v>
       </c>
       <c r="B47" t="s" s="49">
-        <v>252</v>
+        <v>282</v>
       </c>
       <c r="C47" t="s" s="50">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D47" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E47" s="35"/>
       <c r="F47" s="35"/>
@@ -28562,13 +29148,13 @@
         <v>39</v>
       </c>
       <c r="B48" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C48" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D48" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E48" s="35"/>
       <c r="F48" s="35"/>
@@ -28596,13 +29182,13 @@
         <v>39</v>
       </c>
       <c r="B49" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C49" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D49" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E49" s="35"/>
       <c r="F49" s="35"/>
@@ -28630,13 +29216,13 @@
         <v>39</v>
       </c>
       <c r="B50" t="s" s="49">
-        <v>253</v>
+        <v>283</v>
       </c>
       <c r="C50" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D50" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E50" s="35"/>
       <c r="F50" s="35"/>
@@ -28664,13 +29250,13 @@
         <v>39</v>
       </c>
       <c r="B51" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C51" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D51" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="E51" s="35"/>
       <c r="F51" s="35"/>
@@ -28698,13 +29284,13 @@
         <v>39</v>
       </c>
       <c r="B52" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C52" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D52" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E52" s="35"/>
       <c r="F52" s="35"/>
@@ -28732,13 +29318,13 @@
         <v>39</v>
       </c>
       <c r="B53" t="s" s="49">
-        <v>254</v>
+        <v>284</v>
       </c>
       <c r="C53" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D53" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E53" s="35"/>
       <c r="F53" s="35"/>
@@ -28766,13 +29352,13 @@
         <v>39</v>
       </c>
       <c r="B54" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C54" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D54" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E54" s="35"/>
       <c r="F54" s="35"/>
@@ -28800,13 +29386,13 @@
         <v>39</v>
       </c>
       <c r="B55" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C55" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="D55" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E55" s="35"/>
       <c r="F55" s="35"/>
@@ -28834,13 +29420,13 @@
         <v>39</v>
       </c>
       <c r="B56" t="s" s="49">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="C56" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D56" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E56" s="35"/>
       <c r="F56" s="35"/>
@@ -28868,13 +29454,13 @@
         <v>39</v>
       </c>
       <c r="B57" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C57" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D57" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="E57" s="35"/>
       <c r="F57" s="35"/>
@@ -28902,13 +29488,13 @@
         <v>39</v>
       </c>
       <c r="B58" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C58" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="D58" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="E58" s="35"/>
       <c r="F58" s="35"/>
@@ -28936,13 +29522,13 @@
         <v>39</v>
       </c>
       <c r="B59" t="s" s="49">
-        <v>256</v>
+        <v>286</v>
       </c>
       <c r="C59" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="D59" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E59" s="35"/>
       <c r="F59" s="35"/>
@@ -28970,13 +29556,13 @@
         <v>39</v>
       </c>
       <c r="B60" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C60" t="s" s="23">
-        <v>260</v>
+        <v>290</v>
       </c>
       <c r="D60" t="s" s="23">
-        <v>258</v>
+        <v>288</v>
       </c>
       <c r="E60" s="35"/>
       <c r="F60" s="35"/>
@@ -29004,13 +29590,13 @@
         <v>39</v>
       </c>
       <c r="B61" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C61" t="s" s="23">
-        <v>263</v>
+        <v>293</v>
       </c>
       <c r="D61" t="s" s="23">
-        <v>259</v>
+        <v>289</v>
       </c>
       <c r="E61" s="35"/>
       <c r="F61" s="35"/>
@@ -29038,13 +29624,13 @@
         <v>39</v>
       </c>
       <c r="B62" t="s" s="49">
-        <v>257</v>
+        <v>287</v>
       </c>
       <c r="C62" t="s" s="23">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="D62" t="s" s="23">
-        <v>262</v>
+        <v>292</v>
       </c>
       <c r="E62" s="35"/>
       <c r="F62" s="35"/>
@@ -29068,8 +29654,8 @@
       <c r="X62" s="35"/>
     </row>
     <row r="63" ht="25.1" customHeight="1">
-      <c r="A63" s="36"/>
-      <c r="B63" s="34"/>
+      <c r="A63" s="33"/>
+      <c r="B63" s="37"/>
       <c r="C63" s="35"/>
       <c r="D63" s="35"/>
       <c r="E63" s="35"/>
@@ -29094,8 +29680,8 @@
       <c r="X63" s="35"/>
     </row>
     <row r="64" ht="25.1" customHeight="1">
-      <c r="A64" s="36"/>
-      <c r="B64" s="34"/>
+      <c r="A64" s="33"/>
+      <c r="B64" s="37"/>
       <c r="C64" s="35"/>
       <c r="D64" s="35"/>
       <c r="E64" s="35"/>
@@ -29120,8 +29706,8 @@
       <c r="X64" s="35"/>
     </row>
     <row r="65" ht="25.1" customHeight="1">
-      <c r="A65" s="36"/>
-      <c r="B65" s="34"/>
+      <c r="A65" s="33"/>
+      <c r="B65" s="37"/>
       <c r="C65" s="35"/>
       <c r="D65" s="35"/>
       <c r="E65" s="35"/>
@@ -29146,8 +29732,8 @@
       <c r="X65" s="35"/>
     </row>
     <row r="66" ht="25.1" customHeight="1">
-      <c r="A66" s="36"/>
-      <c r="B66" s="34"/>
+      <c r="A66" s="33"/>
+      <c r="B66" s="37"/>
       <c r="C66" s="35"/>
       <c r="D66" s="35"/>
       <c r="E66" s="35"/>
@@ -29172,8 +29758,8 @@
       <c r="X66" s="35"/>
     </row>
     <row r="67" ht="25.1" customHeight="1">
-      <c r="A67" s="36"/>
-      <c r="B67" s="34"/>
+      <c r="A67" s="33"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="35"/>
       <c r="D67" s="35"/>
       <c r="E67" s="35"/>
@@ -29198,8 +29784,8 @@
       <c r="X67" s="35"/>
     </row>
     <row r="68" ht="25.1" customHeight="1">
-      <c r="A68" s="36"/>
-      <c r="B68" s="34"/>
+      <c r="A68" s="33"/>
+      <c r="B68" s="37"/>
       <c r="C68" s="35"/>
       <c r="D68" s="35"/>
       <c r="E68" s="35"/>

--- a/datos_liga.xlsx
+++ b/datos_liga.xlsx
@@ -17842,7 +17842,7 @@
         <v>4</v>
       </c>
       <c r="E228" t="s" s="27">
-        <v>24</v>
+        <v>143</v>
       </c>
       <c r="F228" t="s" s="28">
         <v>26</v>

--- a/datos_liga.xlsx
+++ b/datos_liga.xlsx
@@ -17289,7 +17289,7 @@
         <v>23</v>
       </c>
       <c r="B220" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C220" s="15">
         <v>1</v>
@@ -17357,7 +17357,7 @@
         <v>23</v>
       </c>
       <c r="B221" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C221" s="22">
         <v>1</v>
@@ -17425,7 +17425,7 @@
         <v>23</v>
       </c>
       <c r="B222" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C222" s="26">
         <v>1</v>
@@ -17493,7 +17493,7 @@
         <v>23</v>
       </c>
       <c r="B223" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C223" s="15">
         <v>1</v>
@@ -17561,7 +17561,7 @@
         <v>23</v>
       </c>
       <c r="B224" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C224" s="22">
         <v>1</v>
@@ -17629,7 +17629,7 @@
         <v>23</v>
       </c>
       <c r="B225" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C225" s="22">
         <v>2</v>
@@ -17697,7 +17697,7 @@
         <v>23</v>
       </c>
       <c r="B226" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C226" s="22">
         <v>2</v>
@@ -17765,7 +17765,7 @@
         <v>23</v>
       </c>
       <c r="B227" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C227" s="22">
         <v>2</v>
@@ -17833,7 +17833,7 @@
         <v>23</v>
       </c>
       <c r="B228" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C228" s="22">
         <v>2</v>
@@ -17901,7 +17901,7 @@
         <v>23</v>
       </c>
       <c r="B229" s="25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C229" s="22">
         <v>3</v>
@@ -17969,7 +17969,7 @@
         <v>23</v>
       </c>
       <c r="B230" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C230" s="22">
         <v>3</v>
@@ -18037,7 +18037,7 @@
         <v>23</v>
       </c>
       <c r="B231" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C231" s="22">
         <v>3</v>
@@ -18105,7 +18105,7 @@
         <v>23</v>
       </c>
       <c r="B232" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C232" s="22">
         <v>3</v>
@@ -18173,7 +18173,7 @@
         <v>23</v>
       </c>
       <c r="B233" s="30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C233" s="26">
         <v>3</v>
@@ -18241,7 +18241,7 @@
         <v>23</v>
       </c>
       <c r="B234" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C234" s="15">
         <v>1</v>
@@ -18309,7 +18309,7 @@
         <v>23</v>
       </c>
       <c r="B235" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C235" s="22">
         <v>1</v>
@@ -18377,7 +18377,7 @@
         <v>23</v>
       </c>
       <c r="B236" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C236" s="22">
         <v>1</v>
@@ -18445,7 +18445,7 @@
         <v>23</v>
       </c>
       <c r="B237" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C237" s="22">
         <v>1</v>
@@ -18513,7 +18513,7 @@
         <v>23</v>
       </c>
       <c r="B238" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C238" s="22">
         <v>2</v>
@@ -18581,7 +18581,7 @@
         <v>23</v>
       </c>
       <c r="B239" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C239" s="22">
         <v>2</v>
@@ -18649,7 +18649,7 @@
         <v>23</v>
       </c>
       <c r="B240" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C240" s="22">
         <v>2</v>
@@ -18717,7 +18717,7 @@
         <v>23</v>
       </c>
       <c r="B241" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C241" s="22">
         <v>2</v>
@@ -18785,7 +18785,7 @@
         <v>23</v>
       </c>
       <c r="B242" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C242" s="22">
         <v>2</v>
@@ -18853,7 +18853,7 @@
         <v>23</v>
       </c>
       <c r="B243" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C243" s="22">
         <v>3</v>
@@ -18921,7 +18921,7 @@
         <v>23</v>
       </c>
       <c r="B244" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C244" s="22">
         <v>3</v>
@@ -18989,7 +18989,7 @@
         <v>23</v>
       </c>
       <c r="B245" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C245" s="22">
         <v>3</v>
@@ -19057,7 +19057,7 @@
         <v>23</v>
       </c>
       <c r="B246" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C246" s="22">
         <v>3</v>
@@ -19125,7 +19125,7 @@
         <v>23</v>
       </c>
       <c r="B247" s="30">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C247" s="26">
         <v>3</v>
